--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -12,15 +12,17 @@
     <sheet name="UnitedHealthcare" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Medicare" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Humana" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AHCCCS FFS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Change Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BCBS'!$A$1:$V$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Optum'!$A$1:$V$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UnitedHealthcare'!$A$1:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UnitedHealthcare'!$A$1:$V$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Medicare'!$A$1:$U$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Humana'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHCCCS FFS'!$A$1:$V$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,6 +202,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -586,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -593,48 +610,49 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>1. No payer reviewed puts 64772 on a prior-auth list, and none publishes criteria that name 64772. 'No PA' is NOT 'covered': every claim can be reviewed after payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+          <t>1. No payer list reviewed puts 64772 itself on a prior-auth list, and none publishes criteria that name 64772 - EXCEPT AHCCCS fee-for-service (AIHP etc.), where every elective outpatient surgery needs a surgeon PA and a separate facility PA (AMPM 820). 'No PA' is NOT 'covered': every claim can be reviewed after payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2. The real risk is the TECHNIQUE. UHC (commercial, Exchange and Community Plan) says endoscopic RFA / endoscopic rhizotomy is unproven. Humana MA policy HUM-1168-008 (eff. 08/06/2026) says it is not reasonable and necessary for any indication, including the facet nerve. AZ Blue's MCG A-0218 describes percutaneous RF only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+          <t>2. The real risk is the TECHNIQUE. Medicare's own LCD L38801 says there is "insufficient evidence ... to determine the safety and efficacy" of endoscopic dorsal ramus rhizotomy compared with thermal RF. UHC (commercial, Exchange, Community Plan) calls endoscopic RFA / rhizotomy unproven; Humana MA (HUM-1168-008) says it is not reasonable and necessary for any indication; AHCCCS plans do not cover experimental services; SCAN denies E/I services (BCG0111); AZ Blue's MCG A-0218 describes percutaneous RF only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>3. Coding: AMA CPT Knowledge Base entries (Nov 2019) point endoscopic medial branch rhizotomy to 64999 (unlisted). Industry sources read CMS's Jan 2026 MUE increase for 64772 (2 -&gt; 6 units) as acceptance of the code for MBT, but no CMS or AMA document on file says so. The operative note must describe an extradural transection or avulsion of a named spinal nerve (the medial branch). 64999 is non-covered on Medicare for non-thermal facet denervation (A58403), needs PA on Humana and cannot be paid in an ASC.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4. Medicare/MA payment mechanics: facility only (ASC or HOPD; office not payable), 090 global, MUE 6 / MAI 3, multiple-procedure reduction (additional units at 50%), no bilateral 150%. Same-session MBBs, ESIs and nerve blocks are bundled (NCCI modifier indicator 0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+          <t>4. Medicare/MA payment mechanics: facility only (ASC or HOPD; office not payable), 090 global, MUE 6 / MAI 3, multiple-procedure reduction (additional units at 50%), no bilateral 150%. Same-session MBBs, ESIs and nerve blocks are bundled (NCCI modifier indicator 0). Routine MAC / general anaesthesia / deep sedation for facet denervation is not reasonable and necessary under L38801 - an endoscopic case done under MAC or GA carries a second denial risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>5. Arizona WISeR does NOT reach 64772 (NCD 160.1 WISeR codes = 64605/64610 only).</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>6. Where a pre-service answer is available, get one: Humana ACD, UHC/Optum voluntary organization determination, AZ Blue written predetermination.</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -842,7 +860,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Follows Medicare</t>
+          <t>None (excluded from Humana PA list); Medicare decides</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -884,7 +902,7 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Follows NCD 160.1 / L38801; commercial Ablative policy (endoscopic = unproven) fills gaps.</t>
+          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); commercial Ablative policy (endoscopic = unproven) may fill gaps. HMO/HMO-POS (incl. D-SNP/C-SNP HMO): PCP referral required.</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
@@ -948,7 +966,7 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service.</t>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service. Gated plans need an electronic PCP referral; the AZ Exchange needs a PCP referral before any PA.</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
@@ -980,7 +998,7 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Endoscopic rhizotomy unproven (CS001.T). AHCCCS fee schedule lists 64772 at $578.79, which is not a coverage decision.</t>
+          <t>E/I services are not AHCCCS benefits; endoscopic rhizotomy unproven (CS001.T). Moderate sedation by the performing physician not covered. The $578.79 fee-schedule rate is not a coverage decision.</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
@@ -1058,141 +1076,263 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS (AIHP, Tribal ALTCS, TRBHA, DDD THP)</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>AMPM 820 (eff. 07/16/2026)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>YES - AUTH REQUIRED</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Elective outpatient surgery: surgeon PA + separate ASC/hospital PA. Experimental services not covered.</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS Online / fax 602-256-6591</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS tab</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>AARP Medicare Supplement (UHC)</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>None - UHC Admin Guide: no PA</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Pays after Medicare; inherits any Medicare denial.</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>UHC West (California)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>PCA-5-24-01315</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Not an Arizona product - round-1 row corrected.</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1"/>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Pre-procedure documentation checklist (all payers)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>[ ] Chronic axial cervical or lumbar pain &gt;=3 months; thoracic and headache indications are poorly supported (MCG A-0218).</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>[ ] Failed conservative care documented (PT/exercise, medication, activity modification) - &gt;=4 weeks for UHC diagnostic blocks, 3 months for MCG.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>[ ] Imaging and exam exclude disc herniation with concordant radiculopathy, stenosis with claudication, fracture, tumor, infection; segment not fused.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>[ ] Two diagnostic medial branch blocks under fluoroscopy/CT, each with &gt;=80% relief of index pain, documented as DIAGNOSTIC (not therapeutic).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>[ ] Two diagnostic medial branch blocks under fluoroscopy/CT, at least 2 weeks apart, each with &gt;=80% relief of index pain (Medicare/MCG; UHC commercial defines a positive block as &gt;=50%), documented as DIAGNOSTIC (not therapeutic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>[ ] Pain/function scale recorded before and after each block and at follow-up (NRS/VAS, ODI) - needed for any repeat (&gt;=50% relief for &gt;=6 months).</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>[ ] Operative note: approach (endoscopic/open), extradural, each nerve transected named and lateralized (one unit per nerve), imaging used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>[ ] Use a diagnosis from the A58403 covered list: M47.812-M47.817, M47.892-M47.897 (spondylosis), M48.12-M48.17, M53.82-M53.87. No M54 (low back pain) code is on it, and M54.5 is a non-billable header.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>[ ] Operative note: approach (endoscopic/open), extradural, each nerve transected named and lateralized (one unit per nerve), imaging used. Record the anaesthesia level: local or moderate sedation with documented need - routine MAC/GA is not reasonable and necessary under L38801.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>[ ] Use a diagnosis from the A58403 list that supports DENERVATION: M47.812-M47.817, M47.892-M47.897 (spondylosis) or M48.12-M48.17. M53.82-M53.87 are on the article only for facet-cyst procedures, not ablation. No M54 (low back pain) code is on it, and M54.5 is a non-billable header.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>[ ] Keep the payer PA-lookup result (screenshot, reference #, date, rep name) in the chart for every "no PA required" answer.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>[ ] Referral on file where the plan requires one (UHC MA HMO/HMO-POS incl. D-SNP/C-SNP, Optum-delegated HMO - PCP submits it; UHC gated commercial; UHC AZ Exchange; Dual Complete).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1"/>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Open items</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>- Optum SCAN PA list and Optum AZ web pages (business.optum.com is blocked from this environment) - confirm SCAN rows with Optum 877-370-2845.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>- AZ Blue: resolve the IVR prefix conflict (Strategic Hub vs Standard list); get a written predetermination for the first case.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: call and record.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository - their rows were not re-verified.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>- AMA CPT Knowledge Base answers on endoscopic rhizotomy (Nov 2019) are paywalled - pull the full text (AMA CPT Network) before finalizing the code.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>- Confirm whether Dr. Luke is Optum-direct contracted (the Optum lists apply only to direct contracts).</t>
         </is>
       </c>
     </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>- Dr. Luke's procedure claims in 2026 S1 were billed at ASAP Surgery Centers North Valley LLC (ASC); confirm the ASC is contracted with each payer and obtain the ASC's own authorization where the payer requires a facility PA (AHCCCS FFS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>- No 64772, 64999 or facet (64490-64495 / 64633-64636) claims appear in the 2026 S1 claims files - there is no payment history yet; track the first claims per payer closely.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="24">
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1385,12 +1525,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Updated 09/01/2026</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>NO - absent (1,909 rows)</t>
+          <t>NO - absent (1,909 rows). Facet RFA 64633-64636 ARE on it (AZ Blue PA); 64490-64495 are NOT on the Standard list</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
@@ -1400,17 +1540,17 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks). AZ Blue O983 Ablation of Peripheral Nerves does NOT apply - it covers sites distant from the spine</t>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks)</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>A-0218; A-0695; O983.11</t>
+          <t>A-0218; A-0695</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>MCG accessed 09/22/2026; O983 eff. 06/03/2026</t>
+          <t>MCG edition not stated - accessed 09/22/2026 via AZ Blue MCG portal</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
@@ -1423,6 +1563,7 @@
           <t>64772 is not on the 2026 STANDARD Code List (1,909 rows, updated 09/01/2026). BUT on the same list facet RFA 64633/64635 DOES require AZ Blue PA (Gold Card eligible for cervical/lumbar). eviCore MSK/interventional pain is Medicare Advantage only (AZ Blue eviCore FAQ 01-2024) - commercial pain PA is requested from AZ Blue directly.
 Since 7/1/2026: a required PA that is not obtained = claim line not reimbursed and the member cannot be billed. AZ Blue also 'reserves the right to require prior authorization for ... newly released and changed items even though the lists have not yet been updated'.
 Hidden legacy tabs in the AZ Blue workbook: 'CommercialMR' flags 64772 ON and 'Denied2019' shows 20 denials for 64772 - undated/historical, but a sign 64772 has been routed to medical review before.
+NOT GOVERNING: AZ Blue O983.11 Ablation of Peripheral Nerves (eff. 06/03/2026) covers peripheral sites distant from the spine, lists only 64624/64640/64628/64629/C9809/G0571 and expressly carves out facet joint pain - it does not govern 64772. No AZ Blue facet-denervation medical policy is in the repository. MCG A-0218 allows a repeat neurotomy after &gt;=50% relief for &gt;=3 months (Medicare LCD: &gt;=6 months).
 RECOMMEND: written predetermination before scheduling; build the chart to MCG A-0218 / A-0695 (dual MBB &gt;=80%, 3+ months pain, failed conservative care, imaging excluding other causes).</t>
         </is>
       </c>
@@ -1674,12 +1815,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>SPD (benefit) + MCG / Carelon (medical necessity)</t>
+          <t>The group's Summary Plan Description (benefit) + AmeriBen's UM criteria (medical necessity)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1719,7 +1860,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Note: the MCG document reference in L was not verified from files in this repository.</t>
+          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Round 2: the MCG reference previously in L ("MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG") could not be found in any repository document and was removed - ask AmeriBen which criteria set it applies.</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1861,7 +2002,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Evicore - AZ Blue PA Lookup / Availity Auth tool</t>
+          <t>AZ Blue PA Lookup / Availity auth tool (eviCore handles only the MSK/pain codes on the MA list; 64772 is not one)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1876,12 +2017,12 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>NO - absent</t>
+          <t>NO - absent. 64490-64495, 64625 and 64633-64636 ARE on it with eviCore as PA administrator</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -1891,27 +2032,27 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the list. On the same list 64490/64493/64625/64633/64635 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch.</t>
+          <t>64772 is not on the list. On the same list 64490-64495, 64625 and 64633-64636 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1987,22 +2128,22 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -2083,22 +2224,22 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2191,22 +2332,22 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2299,22 +2440,22 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2375,12 +2516,12 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026 FEP List (updated 09/01/2026); FEP Blue Focus list</t>
+          <t>2026 FEP List (updated 09/01/2026); FEPBluefocusList (hidden tab, undated)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Updated 09/01/2026</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2395,7 +2536,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FEP Service Benefit Plan medical policy (not in this repository)</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2410,12 +2551,12 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Not checked - document not on file</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool.</t>
+          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool. Related codes that ARE on the 2026 FEP List: 63185 / 63190 (laminectomy with rhizotomy) - AZ Blue PA, FEP Standard and Basic only.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -2466,47 +2607,47 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Follows Medicare - NCD 160.1</t>
+          <t>None - Medicare Supplement has no prior authorization; it pays after Medicare</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Longstanding</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>YES via Medicare</t>
+          <t>n/a - no PA document exists</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -2525,7 +2666,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ACA StandardHealth with Health Choice</t>
@@ -2607,7 +2748,7 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Not on the grid. An auth was filed on the portal and none was required.</t>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2621,7 +2762,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Health Choice Pathway</t>
@@ -2683,27 +2824,27 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Not on the grid. An auth was filed on the portal and none was required.</t>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -2779,22 +2920,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AHCCCS AMPM 320-B (experimental services not covered); AMPM Exhibit 300-1 (moderate sedation by the performing physician not covered); AHCCCS FFS Physician Fee Schedule</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AMPM 320-B; AMPM Exhibit 300-1; FY26 FFS Physician Fee Schedule</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026; fee schedule eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named in the AMPM. It IS on the fee schedule ($578.79), which AHCCCS says is not a coverage decision</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2965,7 +3106,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>NO - absent (1,973 rows)</t>
+          <t>NO - absent (1,973 rows). 64490-64495 and 64633-64636 ARE on it (AZ Blue PA)</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2995,7 +3136,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the list. 64490, 64493, 64633 and 64635 DO require AZ Blue PA for this group. All non-emergency admissions (except maternity) need PA.</t>
+          <t>64772 is not on the list. 64490-64495 and 64633-64636 DO require AZ Blue PA for this group (site-of-service review: No). All non-emergency admissions (except maternity) need PA. Group is delegated for eviCore (imaging, lab, oncology, radiation - not MSK on commercial).</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3334,27 +3475,27 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -3446,27 +3587,27 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -3558,27 +3699,27 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -3670,27 +3811,27 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -3782,27 +3923,27 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -3894,27 +4035,27 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -4006,27 +4147,27 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -4118,27 +4259,27 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -4230,27 +4371,27 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -4342,27 +4483,27 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -4454,27 +4595,27 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -4566,27 +4707,27 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -4678,27 +4819,27 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; L38801; A58403</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -4790,22 +4931,22 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -4902,22 +5043,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -4994,17 +5135,17 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -5014,27 +5155,27 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>BCG0100; CCP0207; CRP0420</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -5106,17 +5247,17 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -5126,27 +5267,27 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>BCG0100; CCP0207; CRP0420</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -5218,17 +5359,17 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -5238,27 +5379,27 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>BCG0100; CCP0207; CRP0420</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -5330,17 +5471,17 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -5350,27 +5491,27 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>BCG0100; CCP0207; CRP0420</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -5442,17 +5583,17 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -5462,27 +5603,27 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>BCG0100; CCP0207; CRP0420</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -5940,7 +6081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6139,27 +6280,27 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -6235,27 +6376,27 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -6331,27 +6472,27 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -6427,27 +6568,27 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -6523,27 +6664,27 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -6619,27 +6760,27 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). ERICKSON: the UHC MA PA list requires Erickson PA for experimental and investigational services - if the MBT is endoscopic, obtain Erickson PA. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -6715,27 +6856,27 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Arizona UHC Dual Complete / Dual Complete One (HMO SNP) Provider Manual</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403) (Medicare benefit); AHCCCS AMPM 320-B for the Medicaid wrap (experimental services not covered)</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; AMPM 320-B</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; 320-B eff. 10/01/2022</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>The manual points to the PA list on UHCprovider.com; 64772 is not on it</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted.</t>
+          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted. The Dual Complete provider manual (2026) is the source of these rules but is not a coverage policy. Members must coordinate with their PCP before seeing a specialist; non-contracted providers need a referral form and PA. QMB members: $0 cost share - do not bill the member. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -6811,27 +6952,27 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MMP070.12; 2026T0107II</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>1 Sep 2026; 1 Feb 2026</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from both</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab.</t>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -6912,7 +7053,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -6927,7 +7068,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage.</t>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. REFERRAL: gated plans need an ELECTRONIC PCP referral before the specialist visit (2026 UHC Administrative Guide, commercial chapter). UHC Complete has its own PA list (PCA-1-25-02057, eff. 1 Sep 2026): 64772 absent, but ALL unlisted codes incl. 64999 need PA and there is no non-emergent out-of-network coverage. Commercial "positive block" = &gt;=50% relief (2026T0004WW), not 80%.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -7008,7 +7149,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -7023,7 +7164,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage.</t>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. Open-access plans: no PCP referral. Commercial "positive block" = &gt;=50% relief (2026T0004WW).</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -7112,7 +7253,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -7127,7 +7268,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage.</t>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. ARIZONA EXCHANGE REQUIRES PCP REFERRALS - UHC will not accept a PA without a referral on file (2026 Individual Exchange QRG / Administrative Guide ch. 4). No out-of-network or out-of-area coverage. Unlisted codes incl. 64999 require PA on the Exchange list.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -7203,27 +7344,27 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM; AHCCCS FFY26 Physician Fee Schedule; UHC Community Plan Ablative Treatment for Spinal Pain</t>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>FY26_Final_PhysicianFeeSchedule.xlsx; CS001.T</t>
+          <t>CS001.T; AMPM 320-B; AMPM Exhibit 300-1</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>rate date 1 Oct 2025; CS001.T eff. 1 Mar 2026</t>
+          <t>CS001.T eff. 03/01/2026; 320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>YES - on the fee schedule</t>
+          <t>NO - 64772 is not named in CS001.T or the AMPM (it appears only on the AHCCCS FFS fee schedule, which is not a coverage document)</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section addressing 64772 was located. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -7336,7 +7477,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>UnitedHealthcare West commercial plans (list names UnitedHealthcare of Arizona, Inc. among its issuers)</t>
+          <t>UnitedHealthcare West commercial plans (California - not an Arizona product)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7358,9 +7499,9 @@
           <t>UnitedHealthcare West</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>NO - not on list</t>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>N/A - NOT AN AZ PRODUCT</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -7415,7 +7556,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Confirm from the ID card/portal that the member is on a West product before using this row. The list is dated 1 Apr 2026 - check for a newer edition.</t>
+          <t>CORRECTION (round 2): this row was added in round 1 because the West list footer names "UnitedHealthcare of Arizona, Inc." - but that footer is the standard multi-entity footer that also appears on the national Commercial list, so it is not evidence. The 2026 UHC Administrative Guide (Others, ch. 1) defines UHC West as UnitedHealthcare of California (CA), and states PacifiCare of Arizona is now UnitedHealthcare Benefits of Texas. Arizona commercial members use the national Commercial rows above. Kept only as a routing guard: if a card shows a West/California product, verify on the portal. 64772 is not on the West list.</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -7429,8 +7570,120 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AARP Medicare Supplement / Medicare Select (insured by UnitedHealthcare)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Medicare Supplement</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Medicare Supplement / Medicare Select (Plans C, F, G, N)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>36273</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>None - Medicare decides; the supplement pays after Medicare</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>n/a - no PA. Claims: payer ID 36273; P.O. Box 1878, Southampton PA; 1-800-523-5800</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2026 UHC Care Provider Administrative Guide - AARP Medicare Supplement section</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>n/a - the guide states "No prior authorization for medical services is required"</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply)</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>No PA. The supplement follows Medicare's determination: if Medicare denies 64772 on medical review (see the Medicare tab, incl. the L38801 endoscopic-evidence statement), the supplement pays nothing. Medicare Select plans may require use of network hospitals for Part A services.</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 (date-of-service, clinical) - CMS practitioner MUE eff. 1 Oct 2026 (raised from 2 in Jan 2026)</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Per Medicare Part B - see the Medicare tab.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
+  <autoFilter ref="A1:V16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7661,13 +7914,13 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 only. 64772 is NOT in L38801 or A58403 (A58403 Group 1 = 64490, 64491, 64493, 64494, 64633-64636).</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
-L38801 / A58403 (Noridian JF, Arizona contracts 03101/03102) do not list 64772, but they govern facet denervation and a reviewer can apply them by analogy - DOCUMENT TO THEM: two diagnostic MBBs each with &gt;=80% relief of index pain; &gt;=3 months pain; failed conservative care; max 2 RF sessions per spinal region per rolling 12 months; repeat only after &gt;=50% relief for &gt;=6 months. L38801 lists as NOT reasonable &amp; necessary: non-thermal denervation (chemical, &lt;80 C, laser, cryoablation), prolotherapy, intra-facet implants. Mechanical/endoscopic transection is neither listed as covered nor as non-covered. A58403: non-thermal denervation is reported with 64999 and is non-covered.
+L38801 / A58403 (Noridian JF, Arizona contracts 03101/03102) do not list 64772, but they govern facet denervation and a reviewer can apply them by analogy - DOCUMENT TO THEM: two diagnostic MBBs each with &gt;=80% relief of index pain; &gt;=3 months pain; failed conservative care; second block &gt;=2 weeks after the first; CT or fluoroscopic guidance only; one spinal region and 1-2 levels per session; max 2 RF sessions per spinal region per rolling 12 months; repeat only after &gt;=50% relief for &gt;=6 months; if &gt;=2 years since the last RFA, repeat the diagnostic blocks. Sedation (L38801 / A58403): routine moderate sedation, MAC, deep sedation or general anaesthesia for facet denervation is NOT reasonable and necessary; moderate sedation only case by case with documented necessity. L38801 lists as NOT reasonable &amp; necessary: non-thermal denervation (chemical, &lt;80 C, laser, cryoablation), prolotherapy, intra-facet implants. CORRECTION (round 2): the LCD is NOT silent on the endoscopic technique - L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation." Endoscopic MBT is therefore outside the LCD's covered indications (thermal RF only) and is exposed to a not-reasonable-and-necessary denial on review. A58403: non-thermal denervation is reported with 64999 and is non-covered. A58403 ICD-10 list: for DENERVATION use M47.812-M47.817, M47.892-M47.897 or M48.12-M48.17 only - M53.82-M53.87 are flagged for facet cyst procedures, not ablation.
 NCCI (PTP v323r0, eff. 1 Oct 2026): 64772 is column 1 over 64490-64495, 62320-62327, 64479-64484 and 64400-64505 nerve blocks with modifier indicator 0 (no bypass) - same-session blocks are not separately payable. No PTP edit with 64633-64636 or 64625.
 RVU indicators: mult proc 2 (100/50/50 reduction for additional units/procedures), bilateral 0 (no 150% - report each nerve as a unit, RT/LT), assistant surgeon 2 (payable), co-surgeon 1 (with documentation), team 0.
 WISeR: 64772 is NOT a WISeR code (see N).</t>
@@ -7722,14 +7975,26 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Palmetto GBA Railroad Medicare (no PA program for 64772)</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>No PA program. WISeR does not apply: the WISeR Guide states Railroad Medicare and Medicare Advantage beneficiaries are not impacted.</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>n/a - no PA list applies</t>
@@ -7742,22 +8007,22 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; local coverage per the MAC where the service is rendered</t>
+          <t>NCD 160.1; L38801 / A58403 (Railroad Medicare applies the LCD/LCA of the MAC where the service is rendered)</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-3</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Longstanding</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>YES via NCD 160.1</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -8003,17 +8268,17 @@
       </c>
       <c r="P2" s="10" t="inlineStr">
         <is>
-          <t>Neuroablative Techniques for Chronic Pain (MA medical coverage policy)</t>
+          <t>Neuroablative Techniques for Chronic Pain (MA); Injections for Pain Conditions (MA) for the diagnostic blocks; NCD 160.1 and Noridian L38801 / A58403 (referenced by both)</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>HUM-1168-008</t>
+          <t>HUM-1168-008; HUM-1137-010; L38801; A58403</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr">
         <is>
-          <t>Eff. 08/06/2026 (review 02/10/2026)</t>
+          <t>HUM-1168-008 eff. 08/06/2026 (review 02/10/2026); HUM-1137-010 eff. 09/01/2026; L38801 04/16/2026; A58403 09/17/2026</t>
         </is>
       </c>
       <c r="S2" s="10" t="inlineStr">
@@ -8025,7 +8290,8 @@
         <is>
           <t>CORRECTION - a Humana policy DOES address this procedure. HUM-1168-008 Coverage Limitations: 'Endoscopic radiofrequency ablation/rhizotomy for any indication including, but not limited to, the facet joint/nerve' will not be considered medically reasonable and necessary (Hayes brief, 10 Jun 2024). It also excludes cooled RF, pulsed RF, laser, cryoneurolysis, SI-joint (64625) and DRG ablation 'regardless of the type of neuroablative technique used'. For facet denervation 64633-64636 it defers to NCD 160.1 and, in Arizona, Noridian L38801 / A58403.
 PA list (eff. 1 Jul 2026, rev. 1 Sep 2026): the facet family (64490-64495, 64633-64636, 64999, 0213T-0218T), epidural codes and 64625 need PA through Cohere - 64772 does not. Services without PA remain 'subject to retrospective medical necessity review'.
-RISK: an endoscopic MBT billed as 64772 will likely be denied on post-payment review under HUM-1168-008, and a contracted provider cannot bill the member without a pre-service denial. Get an ACD first. If the procedure is coded 64999 instead, PA through Cohere IS required.</t>
+RISK: an endoscopic MBT billed as 64772 will likely be denied on post-payment review under HUM-1168-008, and a contracted provider cannot bill the member without a pre-service denial. Get an ACD first. If the procedure is coded 64999 instead, PA through Cohere IS required.
+OTHER PA-LIST RULES: HMO members assigned to a delegated IPA/risk network follow the IPA's rules; PFFS plans have no PA (ACD available); an ACD is available for any investigational/experimental service. HUM-1137-010: facet injections/MBB follow L38801/A58403; moderate sedation 99152/99153 is in its coding table.</t>
         </is>
       </c>
       <c r="U2" s="10" t="inlineStr">
@@ -8716,7 +8982,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="37.5" customHeight="1">
+    <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Humana Plan F VALUE</t>
@@ -8754,7 +9020,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Medicare / Noridian JF</t>
+          <t>Medicare / Noridian JF (Humana pays after Medicare)</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -8769,52 +9035,52 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Medicare Part B rules govern - see the Medicare tab.</t>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
-          <t>Medicare Part B rules govern - see the Medicare tab.</t>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card.</t>
         </is>
       </c>
       <c r="U9" s="10" t="inlineStr">
@@ -8828,7 +9094,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="37.5" customHeight="1">
+    <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Humana Plan N ACHIEVE</t>
@@ -8881,164 +9147,164 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>As row 9 (name "ACHIEVE" not found in HumanaMS.pdf - confirm against the member card).</t>
+        </is>
+      </c>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t>Ibid</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Other Humana Medicare Supplement letters sold in Maricopa AZ  -  A, B, C, G, High-Deductible F, High-Deductible G, K, L</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Medicare Supplement</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Medicare Supplement</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Ibid</t>
         </is>
       </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Ibid</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Other Humana Medicare Supplement letters sold in Maricopa AZ  -  A, B, C, G, High-Deductible F, High-Deductible G, K, L</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Medicare Supplement</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Medicare Supplement</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Ibid</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Ibid</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Ibid</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Ibid</t>
-        </is>
-      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
         </is>
       </c>
       <c r="R11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
         </is>
       </c>
       <c r="T11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>As row 9. HumanaMS.pdf lists A, B, C, F, G, F-HD, G-HD, K, L and N for Maricopa 85023.</t>
         </is>
       </c>
       <c r="U11" s="10" t="inlineStr">
@@ -9064,7 +9330,271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="13.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="17.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="20.85546875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="37.85546875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="32.140625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="22.5703125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="13.28515625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="17.85546875" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="22" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="16" max="16"/>
+    <col width="22.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="13.28515625" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="17.85546875" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="59.140625" customWidth="1" min="20" max="20"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="16.140625" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="51.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plan name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Line of business</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Plan type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Alpha prefix</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Payer ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CMS contract</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Group number(s)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Who decides prior auth</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PA required for 64772?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where to CHECK PA determination </t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Governing document for PAs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Document number</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Effective</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Is 64772 in it? (PA docs)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Criteria published for 64772?</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governing document for 64772 or related </t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Document number</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Effective</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Is 64772 in it? (Policy docs)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>What the documentation says</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MUE 64772</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>POS 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AHCCCS Fee-for-Service: American Indian Health Program (AIHP), Tribal ALTCS, TRBHA, DDD Tribal Health Program</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Medicaid (AHCCCS FFS)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>FFS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>(AHCCCS ID)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS Division of Fee-for-Service Management (DFSM)</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>YES - AUTH REQUIRED</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS Online provider portal; Medical PA fax 602-256-6591; phone 602-417-4400 / 800-433-0425</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM Policy 820 - Fee-for-Service Prior Authorization Requirements (and FFS PA Guidelines by code)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>AMPM 820 sections L.3.b, T and U; AMPM 810 (FFS UM)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AMPM 820 eff. 07/16/2026; AMPM 810 eff. 06/17/2026</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>YES by category - elective/non-emergency outpatient SURGERY needs a surgeon PA and a separate facility (ASC/hospital) PA</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>NO code-specific criteria; medical necessity per AMPM; experimental services excluded (AMPM 320-B)</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations); FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AMPM 320-B; AMPM Exhibit 300-1; FY26 FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026; fee schedule eff. 07/01/2026</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>NO in the AMPM; YES on the fee schedule (64772 $578.79 facility and non-facility; 64999 "BR" by report)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>NEW ROW (round 2) - this book was missing. AMPM 820 U: FFS surgeons "shall obtain a separate and distinct AHCCCS PA number ... prior to providing elective/non-emergency surgeries"; AMPM 820 T: the ASC must obtain its own PA for all outpatient surgeries; L.3.b: hospital outpatient surgery needs authorization. Assistant surgeons and anaesthesiologists do not need a separate PA. No PA needed when the provider/facility is IHS or a 638 tribal facility, for emergencies, when AHCCCS is not primary, or for retro-eligibility. A PA "does not guarantee payment". Standard decision 14 days, expedited 72 hours. Experimental services are not covered (320-B); moderate sedation by the performing physician is not covered (Exh. 300-1). Put member name/DOB/ID on every page submitted.</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 (CMS practitioner MUE); AHCCCS applies its own edits</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS publishes a facility and a non-facility rate ($578.79); plan for the ASC with its own facility PA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+  </sheetData>
+  <autoFilter ref="A1:V2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9269,7 +9799,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Rates eff. 10/1/2025</t>
+          <t>File eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -9699,7 +10229,7 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>UHC West commercial PA</t>
+          <t>UHC West commercial PA (California product - not applicable in AZ)</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -9869,6 +10399,358 @@
       <c r="D38" s="17" t="inlineStr">
         <is>
           <t>findacode.com/newsletters/ama-cpt-kb/ (previews only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 320-B (experimental services)</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>320-B</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 10/01/2022</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Exhibit 300-1</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Rev. 07/09/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 810 FFS Utilization Management</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 06/17/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 820 FFS Prior Authorization</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 07/16/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>LCD Facet Joint Interventions (retired version)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>L38803</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Rev. eff. 07/17/2025 (retired)</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/.../Medicare - text identical to L38801</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>Response to Comments: Facet Joint Interventions</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>A59795</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Orig. eff. 07/07/2024</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>Code Research/.../Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Plan Guides</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>UHC 2026 Individual Exchange plans - Quick reference guide</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Plan Guides</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan AZ member handbook excerpt</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Plan Guides/AZ_Medicaid_Handbook.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>Network update 09/18/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Plan Guides</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Humana Commercial PA list (stale)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>399806ALL0224-A GCHM8R6EN</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 07/01/2024, rev. 12/10/2024</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>PA Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>UHC Complete PA requirements</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>PCA-1-25-02057</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>PA Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA PA requirements - prior edition</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>PCA-4-26-00416</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>PA Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>BH00798-2-24-QRG_01012025</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>PA Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>Aug-Sep 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>PA Articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>DOS 01/2026-06/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Repository root / Specialty Claims 2026-S1</t>
         </is>
       </c>
     </row>
@@ -9877,13 +10759,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D556"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22054,6 +22936,6647 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="15" t="inlineStr">
+        <is>
+          <t>Round 2 - full-read audit of every repository document, 23 Sep 2026 (previous value -&gt; new value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="16" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B559" s="16" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="C559" s="16" t="inlineStr">
+        <is>
+          <t>Previous value</t>
+        </is>
+      </c>
+      <c r="D559" s="16" t="inlineStr">
+        <is>
+          <t>New value</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B560" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C560" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
+L38801 / A58...</t>
+        </is>
+      </c>
+      <c r="D560" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
+L38801 / A58...</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B561" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C561" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 only. 64772 is NOT in L38801 or A58403 (A58403 Group 1 = 64490, 64491, 64493, 64494, 64633-64636).</t>
+        </is>
+      </c>
+      <c r="D561" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B562" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C562" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; local coverage per the MAC where the service is rendered</t>
+        </is>
+      </c>
+      <c r="D562" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801 / A58403 (Railroad Medicare applies the LCD/LCA of the MAC where the service is rendered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B563" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C563" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-3</t>
+        </is>
+      </c>
+      <c r="D563" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B564" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C564" s="17" t="inlineStr">
+        <is>
+          <t>Longstanding</t>
+        </is>
+      </c>
+      <c r="D564" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B565" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C565" s="17" t="inlineStr">
+        <is>
+          <t>YES via NCD 160.1</t>
+        </is>
+      </c>
+      <c r="D565" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B566" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C566" s="17" t="inlineStr"/>
+      <c r="D566" s="17" t="inlineStr">
+        <is>
+          <t>Palmetto GBA Railroad Medicare (no PA program for 64772)</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B567" s="17" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C567" s="17" t="inlineStr"/>
+      <c r="D567" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B568" s="17" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C568" s="17" t="inlineStr"/>
+      <c r="D568" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B569" s="17" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C569" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D569" s="17" t="inlineStr">
+        <is>
+          <t>Updated 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B570" s="17" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C570" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (1,909 rows)</t>
+        </is>
+      </c>
+      <c r="D570" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (1,909 rows). Facet RFA 64633-64636 ARE on it (AZ Blue PA); 64490-64495 are NOT on the Standard list</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B571" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C571" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks). AZ Blue O983 Ablation of Peripheral Nerves does NOT apply - it covers sites distant from the spine</t>
+        </is>
+      </c>
+      <c r="D571" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B572" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C572" s="17" t="inlineStr">
+        <is>
+          <t>A-0218; A-0695; O983.11</t>
+        </is>
+      </c>
+      <c r="D572" s="17" t="inlineStr">
+        <is>
+          <t>A-0218; A-0695</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B573" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C573" s="17" t="inlineStr">
+        <is>
+          <t>MCG accessed 09/22/2026; O983 eff. 06/03/2026</t>
+        </is>
+      </c>
+      <c r="D573" s="17" t="inlineStr">
+        <is>
+          <t>MCG edition not stated - accessed 09/22/2026 via AZ Blue MCG portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B574" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C574" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the 2026 STANDARD Code List (1,909 rows, updated 09/01/2026). BUT on the same list facet RFA 64633/64635 DOES require AZ Blue PA (Gold Card eligible for cervical/lumbar). eviCore MSK/interventional pain is Medicare Advantage only (AZ Blue eviCore FAQ 01-2024) - commercial pain PA is requested from AZ Blue directly.
+Since 7/1/2026: a required PA that is not obtained = claim line not reimbursed and the member cannot be billed. AZ Blue also 'reserves the right to require prior authorization for ... newly released and changed items even though the lists have not yet been updated...</t>
+        </is>
+      </c>
+      <c r="D574" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the 2026 STANDARD Code List (1,909 rows, updated 09/01/2026). BUT on the same list facet RFA 64633/64635 DOES require AZ Blue PA (Gold Card eligible for cervical/lumbar). eviCore MSK/interventional pain is Medicare Advantage only (AZ Blue eviCore FAQ 01-2024) - commercial pain PA is requested from AZ Blue directly.
+Since 7/1/2026: a required PA that is not obtained = claim line not reimbursed and the member cannot be billed. AZ Blue also 'reserves the right to require prior authorization for ... newly released and changed items even though the lists have not yet been updated...</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B575" s="17" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C575" s="17" t="inlineStr">
+        <is>
+          <t>SPD (benefit) + MCG / Carelon (medical necessity)</t>
+        </is>
+      </c>
+      <c r="D575" s="17" t="inlineStr">
+        <is>
+          <t>The group's Summary Plan Description (benefit) + AmeriBen's UM criteria (medical necessity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B576" s="17" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="C576" s="17" t="inlineStr">
+        <is>
+          <t>MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG</t>
+        </is>
+      </c>
+      <c r="D576" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B577" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C577" s="17" t="inlineStr">
+        <is>
+          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Note: the MCG document reference in L was not verified from files in this repository.</t>
+        </is>
+      </c>
+      <c r="D577" s="17" t="inlineStr">
+        <is>
+          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Round 2: the MCG reference previously in L ("MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG") could not be found in any repository document and was removed - ask AmeriBen which criteria set it applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B578" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C578" s="17" t="inlineStr">
+        <is>
+          <t>Evicore - AZ Blue PA Lookup / Availity Auth tool</t>
+        </is>
+      </c>
+      <c r="D578" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity auth tool (eviCore handles only the MSK/pain codes on the MA list; 64772 is not one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B579" s="17" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C579" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D579" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B580" s="17" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="C580" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+      <c r="D580" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. 64490-64495, 64625 and 64633-64636 ARE on it with eviCore as PA administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B581" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C581" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D581" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B582" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C582" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D582" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B583" s="17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C583" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D583" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B584" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C584" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D584" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B585" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C585" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. On the same list 64490/64493/64625/64633/64635 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch.</t>
+        </is>
+      </c>
+      <c r="D585" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. On the same list 64490-64495, 64625 and 64633-64636 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic do...</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B586" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C586" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D586" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B587" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C587" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D587" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B588" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C588" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D588" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B589" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C589" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D589" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B590" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C590" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D590" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B591" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C591" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D591" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B592" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C592" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D592" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B593" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C593" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D593" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B594" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C594" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D594" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B595" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C595" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D595" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B596" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C596" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D596" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B597" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C597" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D597" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B598" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C598" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D598" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B599" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C599" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D599" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B600" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C600" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D600" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B601" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C601" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D601" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B602" s="17" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="C602" s="17" t="inlineStr">
+        <is>
+          <t>2026 FEP List (updated 09/01/2026); FEP Blue Focus list</t>
+        </is>
+      </c>
+      <c r="D602" s="17" t="inlineStr">
+        <is>
+          <t>2026 FEP List (updated 09/01/2026); FEPBluefocusList (hidden tab, undated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B603" s="17" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="C603" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D603" s="17" t="inlineStr">
+        <is>
+          <t>Updated 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B604" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C604" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D604" s="17" t="inlineStr">
+        <is>
+          <t>FEP Service Benefit Plan medical policy (not in this repository)</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B605" s="17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C605" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D605" s="17" t="inlineStr">
+        <is>
+          <t>Not checked - document not on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B606" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C606" s="17" t="inlineStr">
+        <is>
+          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool.</t>
+        </is>
+      </c>
+      <c r="D606" s="17" t="inlineStr">
+        <is>
+          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool. Related codes that ARE on the 2026 FEP List: 63185 / 63190 (laminectomy with rhizotomy) - AZ Blue PA, FEP Standard and Basic only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B607" s="17" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C607" s="17" t="inlineStr">
+        <is>
+          <t>Follows Medicare - NCD 160.1</t>
+        </is>
+      </c>
+      <c r="D607" s="17" t="inlineStr">
+        <is>
+          <t>None - Medicare Supplement has no prior authorization; it pays after Medicare</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B608" s="17" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="C608" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-3</t>
+        </is>
+      </c>
+      <c r="D608" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B609" s="17" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="C609" s="17" t="inlineStr">
+        <is>
+          <t>Longstanding</t>
+        </is>
+      </c>
+      <c r="D609" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B610" s="17" t="inlineStr">
+        <is>
+          <t>N13</t>
+        </is>
+      </c>
+      <c r="C610" s="17" t="inlineStr">
+        <is>
+          <t>YES via Medicare</t>
+        </is>
+      </c>
+      <c r="D610" s="17" t="inlineStr">
+        <is>
+          <t>n/a - no PA document exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B611" s="17" t="inlineStr">
+        <is>
+          <t>O13</t>
+        </is>
+      </c>
+      <c r="C611" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D611" s="17" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B612" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C612" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D612" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B613" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C613" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D613" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B614" s="17" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C614" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D614" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B615" s="17" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C615" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D615" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B616" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C616" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required.</t>
+        </is>
+      </c>
+      <c r="D616" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B617" s="17" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C617" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required.</t>
+        </is>
+      </c>
+      <c r="D617" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B618" s="17" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C618" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D618" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B619" s="17" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="C619" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D619" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B620" s="17" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="C620" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D620" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B621" s="17" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C621" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D621" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B622" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C622" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D622" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 320-B (experimental services not covered); AMPM Exhibit 300-1 (moderate sedation by the performing physician not covered); AHCCCS FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B623" s="17" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="C623" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D623" s="17" t="inlineStr">
+        <is>
+          <t>AMPM 320-B; AMPM Exhibit 300-1; FY26 FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B624" s="17" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C624" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D624" s="17" t="inlineStr">
+        <is>
+          <t>320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026; fee schedule eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B625" s="17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C625" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D625" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named in the AMPM. It IS on the fee schedule ($578.79), which AHCCCS says is not a coverage decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B626" s="17" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C626" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (1,973 rows)</t>
+        </is>
+      </c>
+      <c r="D626" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (1,973 rows). 64490-64495 and 64633-64636 ARE on it (AZ Blue PA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B627" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C627" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. 64490, 64493, 64633 and 64635 DO require AZ Blue PA for this group. All non-emergency admissions (except maternity) need PA.</t>
+        </is>
+      </c>
+      <c r="D627" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. 64490-64495 and 64633-64636 DO require AZ Blue PA for this group (site-of-service review: No). All non-emergency admissions (except maternity) need PA. Group is delegated for eviCore (imaging, lab, oncology, radiation - not MSK on commercial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B628" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C628" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D628" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B629" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C629" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D629" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B630" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C630" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D630" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B631" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C631" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D631" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B632" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C632" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D632" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B633" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C633" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D633" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B634" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C634" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D634" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B635" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C635" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D635" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B636" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C636" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D636" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B637" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C637" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D637" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B638" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C638" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D638" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B639" s="17" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C639" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D639" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B640" s="17" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C640" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D640" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B641" s="17" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C641" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D641" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B642" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C642" s="17" t="inlineStr">
+        <is>
+          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D642" s="17" t="inlineStr">
+        <is>
+          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B643" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C643" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D643" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B644" s="17" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C644" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D644" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B645" s="17" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C645" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D645" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B646" s="17" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C646" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D646" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B647" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C647" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D647" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B648" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C648" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D648" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B649" s="17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C649" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D649" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B650" s="17" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C650" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D650" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B651" s="17" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C651" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D651" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B652" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C652" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D652" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B653" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C653" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D653" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B654" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C654" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D654" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B655" s="17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C655" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D655" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B656" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C656" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D656" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B657" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C657" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D657" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B658" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C658" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D658" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B659" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C659" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D659" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B660" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C660" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D660" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B661" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C661" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D661" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B662" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C662" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D662" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B663" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C663" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D663" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B664" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C664" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D664" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B665" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C665" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D665" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B666" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C666" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D666" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B667" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C667" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D667" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B668" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C668" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D668" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B669" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C669" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D669" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B670" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C670" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D670" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B671" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C671" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D671" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B672" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C672" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D672" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B673" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C673" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D673" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B674" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C674" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D674" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B675" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C675" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D675" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B676" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C676" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D676" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B677" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C677" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D677" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving n...</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B678" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C678" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D678" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B679" s="17" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="C679" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D679" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B680" s="17" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C680" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D680" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B681" s="17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C681" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D681" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B682" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C682" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D682" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving n...</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B683" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C683" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D683" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B684" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C684" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D684" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B685" s="17" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C685" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D685" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B686" s="17" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C686" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D686" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B687" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C687" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D687" s="17" t="inlineStr">
+        <is>
+          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving n...</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B688" s="17" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C688" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA Pain Management -&gt; NCD 160.1 and Noridian L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D688" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B689" s="17" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C689" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D689" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B690" s="17" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="C690" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 04/16/2026; 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D690" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B691" s="17" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C691" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D691" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B692" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C692" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the orthopaedic/specialist visit; specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D692" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidanc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B693" s="17" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C693" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D693" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B694" s="17" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="C694" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D694" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B695" s="17" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="C695" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D695" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B696" s="17" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C696" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D696" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B697" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C697" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D697" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B698" s="17" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="C698" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D698" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B699" s="17" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C699" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D699" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B700" s="17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C700" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D700" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B701" s="17" t="inlineStr">
+        <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="C701" s="17" t="inlineStr">
+        <is>
+          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="D701" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B702" s="17" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="C702" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D702" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B703" s="17" t="inlineStr">
+        <is>
+          <t>N17</t>
+        </is>
+      </c>
+      <c r="C703" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D703" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B704" s="17" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C704" s="17" t="inlineStr">
+        <is>
+          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D704" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B705" s="17" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C705" s="17" t="inlineStr">
+        <is>
+          <t>BCG0100; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D705" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B706" s="17" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="C706" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+        </is>
+      </c>
+      <c r="D706" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B707" s="17" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C707" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D707" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B708" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C708" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+        </is>
+      </c>
+      <c r="D708" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B709" s="17" t="inlineStr">
+        <is>
+          <t>L18</t>
+        </is>
+      </c>
+      <c r="C709" s="17" t="inlineStr">
+        <is>
+          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="D709" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B710" s="17" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="C710" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D710" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B711" s="17" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C711" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D711" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B712" s="17" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C712" s="17" t="inlineStr">
+        <is>
+          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D712" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B713" s="17" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="C713" s="17" t="inlineStr">
+        <is>
+          <t>BCG0100; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D713" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B714" s="17" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="C714" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+        </is>
+      </c>
+      <c r="D714" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B715" s="17" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C715" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D715" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B716" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C716" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+        </is>
+      </c>
+      <c r="D716" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B717" s="17" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="C717" s="17" t="inlineStr">
+        <is>
+          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="D717" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B718" s="17" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="C718" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D718" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B719" s="17" t="inlineStr">
+        <is>
+          <t>N19</t>
+        </is>
+      </c>
+      <c r="C719" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D719" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B720" s="17" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C720" s="17" t="inlineStr">
+        <is>
+          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D720" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B721" s="17" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="C721" s="17" t="inlineStr">
+        <is>
+          <t>BCG0100; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D721" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B722" s="17" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="C722" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+        </is>
+      </c>
+      <c r="D722" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B723" s="17" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="C723" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D723" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B724" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C724" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+        </is>
+      </c>
+      <c r="D724" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B725" s="17" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C725" s="17" t="inlineStr">
+        <is>
+          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="D725" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B726" s="17" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+      <c r="C726" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D726" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B727" s="17" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="C727" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D727" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B728" s="17" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C728" s="17" t="inlineStr">
+        <is>
+          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D728" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B729" s="17" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C729" s="17" t="inlineStr">
+        <is>
+          <t>BCG0100; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D729" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B730" s="17" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="C730" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+        </is>
+      </c>
+      <c r="D730" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B731" s="17" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C731" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D731" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B732" s="17" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C732" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+        </is>
+      </c>
+      <c r="D732" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B733" s="17" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="C733" s="17" t="inlineStr">
+        <is>
+          <t>SCAN MA PA Requirements (rev. 1 Aug 2026)</t>
+        </is>
+      </c>
+      <c r="D733" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B734" s="17" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="C734" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2024, rev. 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D734" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B735" s="17" t="inlineStr">
+        <is>
+          <t>N21</t>
+        </is>
+      </c>
+      <c r="C735" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is absent from SCAN's list and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D735" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B736" s="17" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="C736" s="17" t="inlineStr">
+        <is>
+          <t>SCAN BCG0100 (hierarchy of guidance); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D736" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B737" s="17" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="C737" s="17" t="inlineStr">
+        <is>
+          <t>BCG0100; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D737" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B738" s="17" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="C738" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026; 11/20/2025; 5/28/2026</t>
+        </is>
+      </c>
+      <c r="D738" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; BCG0100 5/28/2026; BCG0111 upd. 5/6/2026; CCP0207 11/20/2025; CRP0420 5/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B739" s="17" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C739" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D739" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B740" s="17" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="C740" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum.</t>
+        </is>
+      </c>
+      <c r="D740" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B741" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C741" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D741" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B742" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C742" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D742" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B743" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C743" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D743" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B744" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C744" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D744" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B745" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C745" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D745" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B746" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C746" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D746" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B747" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C747" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D747" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B748" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C748" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D748" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B749" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C749" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D749" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B750" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C750" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D750" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B751" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C751" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D751" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B752" s="17" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C752" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D752" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B753" s="17" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C753" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D753" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B754" s="17" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C754" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D754" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B755" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C755" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D755" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B756" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C756" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D756" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B757" s="17" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C757" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D757" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B758" s="17" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C758" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D758" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B759" s="17" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C759" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D759" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B760" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C760" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D760" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B761" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C761" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D761" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B762" s="17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C762" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D762" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B763" s="17" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C763" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D763" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B764" s="17" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C764" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D764" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B765" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C765" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D765" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B766" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C766" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D766" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B767" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C767" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D767" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B768" s="17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C768" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D768" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B769" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C769" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D769" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B770" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C770" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D770" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B771" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C771" s="17" t="inlineStr">
+        <is>
+          <t>Pain Management (MA); where no LCD applies -&gt; commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D771" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B772" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C772" s="17" t="inlineStr">
+        <is>
+          <t>MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D772" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B773" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C773" s="17" t="inlineStr">
+        <is>
+          <t>1 Sep 2026; 1 Feb 2026</t>
+        </is>
+      </c>
+      <c r="D773" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B774" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C774" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both</t>
+        </is>
+      </c>
+      <c r="D774" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B775" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C775" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+      <c r="D775" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a vol...</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B776" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C776" s="17" t="inlineStr">
+        <is>
+          <t>Arizona UHC Dual Complete / Dual Complete One (HMO SNP) Provider Manual</t>
+        </is>
+      </c>
+      <c r="D776" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403) (Medicare benefit); AHCCCS AMPM 320-B for the Medicaid wrap (experimental services not covered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B777" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C777" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D777" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; AMPM 320-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B778" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C778" s="17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D778" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; 320-B eff. 10/01/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B779" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C779" s="17" t="inlineStr">
+        <is>
+          <t>The manual points to the PA list on UHCprovider.com; 64772 is not on it</t>
+        </is>
+      </c>
+      <c r="D779" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B780" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C780" s="17" t="inlineStr">
+        <is>
+          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted.</t>
+        </is>
+      </c>
+      <c r="D780" s="17" t="inlineStr">
+        <is>
+          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted. The Dual Complete provider manual (2026) is the source of these rules but is not a coverage policy. Members must coordinate with their PCP before seeing a specialist; non-contracted pro...</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B781" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C781" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+        </is>
+      </c>
+      <c r="D781" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B782" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C782" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+      <c r="D782" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B783" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C783" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+        </is>
+      </c>
+      <c r="D783" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B784" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C784" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+      <c r="D784" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B785" s="17" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="C785" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22; MP.11.27</t>
+        </is>
+      </c>
+      <c r="D785" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B786" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C786" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+      <c r="D786" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy...</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B787" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C787" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM; AHCCCS FFY26 Physician Fee Schedule; UHC Community Plan Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D787" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B788" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C788" s="17" t="inlineStr">
+        <is>
+          <t>FY26_Final_PhysicianFeeSchedule.xlsx; CS001.T</t>
+        </is>
+      </c>
+      <c r="D788" s="17" t="inlineStr">
+        <is>
+          <t>CS001.T; AMPM 320-B; AMPM Exhibit 300-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B789" s="17" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C789" s="17" t="inlineStr">
+        <is>
+          <t>rate date 1 Oct 2025; CS001.T eff. 1 Mar 2026</t>
+        </is>
+      </c>
+      <c r="D789" s="17" t="inlineStr">
+        <is>
+          <t>CS001.T eff. 03/01/2026; 320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B790" s="17" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C790" s="17" t="inlineStr">
+        <is>
+          <t>YES - on the fee schedule</t>
+        </is>
+      </c>
+      <c r="D790" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named in CS001.T or the AMPM (it appears only on the AHCCCS FFS fee schedule, which is not a coverage document)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B791" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C791" s="17" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section addressing 64772 was located. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotom...</t>
+        </is>
+      </c>
+      <c r="D791" s="17" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for...</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B792" s="17" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="C792" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D792" s="17" t="inlineStr">
+        <is>
+          <t>N/A - NOT AN AZ PRODUCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B793" s="17" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="C793" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare West commercial plans (list names UnitedHealthcare of Arizona, Inc. among its issuers)</t>
+        </is>
+      </c>
+      <c r="D793" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare West commercial plans (California - not an Arizona product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B794" s="17" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C794" s="17" t="inlineStr">
+        <is>
+          <t>Confirm from the ID card/portal that the member is on a West product before using this row. The list is dated 1 Apr 2026 - check for a newer edition.</t>
+        </is>
+      </c>
+      <c r="D794" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION (round 2): this row was added in round 1 because the West list footer names "UnitedHealthcare of Arizona, Inc." - but that footer is the standard multi-entity footer that also appears on the national Commercial list, so it is not evidence. The 2026 UHC Administrative Guide (Others, ch. 1) defines UHC West as UnitedHealthcare of California (CA), and states PacifiCare of Arizona is now UnitedHealthcare Benefits of Texas. Arizona commercial members use the national Commercial rows above. Kept only as a routing guard: if a card shows a West/California product, verify on the portal. 6...</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B795" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C795" s="17" t="inlineStr">
+        <is>
+          <t>Neuroablative Techniques for Chronic Pain (MA medical coverage policy)</t>
+        </is>
+      </c>
+      <c r="D795" s="17" t="inlineStr">
+        <is>
+          <t>Neuroablative Techniques for Chronic Pain (MA); Injections for Pain Conditions (MA) for the diagnostic blocks; NCD 160.1 and Noridian L38801 / A58403 (referenced by both)</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B796" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C796" s="17" t="inlineStr">
+        <is>
+          <t>HUM-1168-008</t>
+        </is>
+      </c>
+      <c r="D796" s="17" t="inlineStr">
+        <is>
+          <t>HUM-1168-008; HUM-1137-010; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B797" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C797" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 08/06/2026 (review 02/10/2026)</t>
+        </is>
+      </c>
+      <c r="D797" s="17" t="inlineStr">
+        <is>
+          <t>HUM-1168-008 eff. 08/06/2026 (review 02/10/2026); HUM-1137-010 eff. 09/01/2026; L38801 04/16/2026; A58403 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B798" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C798" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION - a Humana policy DOES address this procedure. HUM-1168-008 Coverage Limitations: 'Endoscopic radiofrequency ablation/rhizotomy for any indication including, but not limited to, the facet joint/nerve' will not be considered medically reasonable and necessary (Hayes brief, 10 Jun 2024). It also excludes cooled RF, pulsed RF, laser, cryoneurolysis, SI-joint (64625) and DRG ablation 'regardless of the type of neuroablative technique used'. For facet denervation 64633-64636 it defers to NCD 160.1 and, in Arizona, Noridian L38801 / A58403.
+PA list (eff. 1 Jul 2026, rev. 1 Sep 2026): t...</t>
+        </is>
+      </c>
+      <c r="D798" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION - a Humana policy DOES address this procedure. HUM-1168-008 Coverage Limitations: 'Endoscopic radiofrequency ablation/rhizotomy for any indication including, but not limited to, the facet joint/nerve' will not be considered medically reasonable and necessary (Hayes brief, 10 Jun 2024). It also excludes cooled RF, pulsed RF, laser, cryoneurolysis, SI-joint (64625) and DRG ablation 'regardless of the type of neuroablative technique used'. For facet denervation 64633-64636 it defers to NCD 160.1 and, in Arizona, Noridian L38801 / A58403.
+PA list (eff. 1 Jul 2026, rev. 1 Sep 2026): t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B799" s="17" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="C799" s="17" t="inlineStr">
+        <is>
+          <t>Medicare / Noridian JF</t>
+        </is>
+      </c>
+      <c r="D799" s="17" t="inlineStr">
+        <is>
+          <t>Medicare / Noridian JF (Humana pays after Medicare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B800" s="17" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C800" s="17" t="inlineStr">
+        <is>
+          <t>Medicare Part B rules govern - see the Medicare tab.</t>
+        </is>
+      </c>
+      <c r="D800" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B801" s="17" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="C801" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D801" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B802" s="17" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="C802" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D802" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B803" s="17" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="C803" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D803" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B804" s="17" t="inlineStr">
+        <is>
+          <t>O9</t>
+        </is>
+      </c>
+      <c r="C804" s="17" t="inlineStr">
+        <is>
+          <t>Medicare Part B rules govern - see the Medicare tab.</t>
+        </is>
+      </c>
+      <c r="D804" s="17" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B805" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C805" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D805" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B806" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C806" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D806" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B807" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C807" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D807" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B808" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C808" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D808" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B809" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C809" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D809" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B810" s="17" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="C810" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D810" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B811" s="17" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C811" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D811" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B812" s="17" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="C812" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D812" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B813" s="17" t="inlineStr">
+        <is>
+          <t>O10</t>
+        </is>
+      </c>
+      <c r="C813" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D813" s="17" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B814" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C814" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D814" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B815" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C815" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D815" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B816" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C816" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D816" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B817" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C817" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D817" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B818" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C818" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D818" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B819" s="17" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="C819" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D819" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B820" s="17" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C820" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D820" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B821" s="17" t="inlineStr">
+        <is>
+          <t>N11</t>
+        </is>
+      </c>
+      <c r="C821" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D821" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B822" s="17" t="inlineStr">
+        <is>
+          <t>O11</t>
+        </is>
+      </c>
+      <c r="C822" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D822" s="17" t="inlineStr">
+        <is>
+          <t>NO (Medicare criteria apply - see the Medicare tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B823" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C823" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D823" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B824" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C824" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D824" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B825" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C825" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D825" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B826" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C826" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D826" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B827" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C827" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D827" s="17" t="inlineStr">
+        <is>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B828" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C828" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D828" s="17" t="inlineStr">
+        <is>
+          <t>As row 9 (name "ACHIEVE" not found in HumanaMS.pdf - confirm against the member card).</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B829" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C829" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D829" s="17" t="inlineStr">
+        <is>
+          <t>As row 9. HumanaMS.pdf lists A, B, C, F, G, F-HD, G-HD, K, L and N for Maricopa 85023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B830" s="17" t="inlineStr">
+        <is>
+          <t>A2:V2</t>
+        </is>
+      </c>
+      <c r="C830" s="17" t="inlineStr"/>
+      <c r="D830" s="17" t="inlineStr">
+        <is>
+          <t>NEW TAB + ROW: AHCCCS Fee-for-Service: American Indian Health Program (AIHP), Tribal ALTCS, TRBHA, DDD Tribal Health Program</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B831" s="17" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C831" s="17" t="inlineStr">
+        <is>
+          <t>1. No payer reviewed puts 64772 on a prior-auth list, and none publishes criteria that name 64772. 'No PA' is NOT 'covered': every claim can be reviewed after payment.</t>
+        </is>
+      </c>
+      <c r="D831" s="17" t="inlineStr">
+        <is>
+          <t>1. No payer list reviewed puts 64772 itself on a prior-auth list, and none publishes criteria that name 64772 - EXCEPT AHCCCS fee-for-service (AIHP etc.), where every elective outpatient surgery needs a surgeon PA and a separate facility PA (AMPM 820). 'No PA' is NOT 'covered': every claim can be reviewed after payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B832" s="17" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C832" s="17" t="inlineStr">
+        <is>
+          <t>2. The real risk is the TECHNIQUE. UHC (commercial, Exchange and Community Plan) says endoscopic RFA / endoscopic rhizotomy is unproven. Humana MA policy HUM-1168-008 (eff. 08/06/2026) says it is not reasonable and necessary for any indication, including the facet nerve. AZ Blue's MCG A-0218 describes percutaneous RF only.</t>
+        </is>
+      </c>
+      <c r="D832" s="17" t="inlineStr">
+        <is>
+          <t>2. The real risk is the TECHNIQUE. Medicare's own LCD L38801 says there is "insufficient evidence ... to determine the safety and efficacy" of endoscopic dorsal ramus rhizotomy compared with thermal RF. UHC (commercial, Exchange, Community Plan) calls endoscopic RFA / rhizotomy unproven; Humana MA (HUM-1168-008) says it is not reasonable and necessary for any indication; AHCCCS plans do not cover experimental services; SCAN denies E/I services (BCG0111); AZ Blue's MCG A-0218 describes percutaneous RF only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B833" s="17" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C833" s="17" t="inlineStr">
+        <is>
+          <t>4. Medicare/MA payment mechanics: facility only (ASC or HOPD; office not payable), 090 global, MUE 6 / MAI 3, multiple-procedure reduction (additional units at 50%), no bilateral 150%. Same-session MBBs, ESIs and nerve blocks are bundled (NCCI modifier indicator 0).</t>
+        </is>
+      </c>
+      <c r="D833" s="17" t="inlineStr">
+        <is>
+          <t>4. Medicare/MA payment mechanics: facility only (ASC or HOPD; office not payable), 090 global, MUE 6 / MAI 3, multiple-procedure reduction (additional units at 50%), no bilateral 150%. Same-session MBBs, ESIs and nerve blocks are bundled (NCCI modifier indicator 0). Routine MAC / general anaesthesia / deep sedation for facet denervation is not reasonable and necessary under L38801 - an endoscopic case done under MAC or GA carries a second denial risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B834" s="17" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C834" s="17" t="inlineStr">
+        <is>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service.</t>
+        </is>
+      </c>
+      <c r="D834" s="17" t="inlineStr">
+        <is>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service. Gated plans need an electronic PCP referral; the AZ Exchange needs a PCP referral before any PA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B835" s="17" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="C835" s="17" t="inlineStr">
+        <is>
+          <t>Endoscopic rhizotomy unproven (CS001.T). AHCCCS fee schedule lists 64772 at $578.79, which is not a coverage decision.</t>
+        </is>
+      </c>
+      <c r="D835" s="17" t="inlineStr">
+        <is>
+          <t>E/I services are not AHCCCS benefits; endoscopic rhizotomy unproven (CS001.T). Moderate sedation by the performing physician not covered. The $578.79 fee-schedule rate is not a coverage decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B836" s="17" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C836" s="17" t="inlineStr">
+        <is>
+          <t>Follows NCD 160.1 / L38801; commercial Ablative policy (endoscopic = unproven) fills gaps.</t>
+        </is>
+      </c>
+      <c r="D836" s="17" t="inlineStr">
+        <is>
+          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); commercial Ablative policy (endoscopic = unproven) may fill gaps. HMO/HMO-POS (incl. D-SNP/C-SNP HMO): PCP referral required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B837" s="17" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C837" s="17" t="inlineStr">
+        <is>
+          <t>Follows Medicare</t>
+        </is>
+      </c>
+      <c r="D837" s="17" t="inlineStr">
+        <is>
+          <t>None (excluded from Humana PA list); Medicare decides</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B838" s="17" t="inlineStr">
+        <is>
+          <t>A26:F26</t>
+        </is>
+      </c>
+      <c r="C838" s="17" t="inlineStr"/>
+      <c r="D838" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: AHCCCS FFS (AIHP, Tribal ALTCS, TRBHA, DDD THP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B839" s="17" t="inlineStr">
+        <is>
+          <t>A27:F27</t>
+        </is>
+      </c>
+      <c r="C839" s="17" t="inlineStr"/>
+      <c r="D839" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: AARP Medicare Supplement (UHC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B840" s="17" t="inlineStr">
+        <is>
+          <t>A28:F28</t>
+        </is>
+      </c>
+      <c r="C840" s="17" t="inlineStr"/>
+      <c r="D840" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: UHC West (California)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B841" s="17" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+      <c r="C841" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Use a diagnosis from the A58403 covered list: M47.812-M47.817, M47.892-M47.897 (spondylosis), M48.12-M48.17, M53.82-M53.87. No M54 (low back pain) code is on it, and M54.5 is a non-billable header.</t>
+        </is>
+      </c>
+      <c r="D841" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Use a diagnosis from the A58403 list that supports DENERVATION: M47.812-M47.817, M47.892-M47.897 (spondylosis) or M48.12-M48.17. M53.82-M53.87 are on the article only for facet-cyst procedures, not ablation. No M54 (low back pain) code is on it, and M54.5 is a non-billable header.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B842" s="17" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
+      </c>
+      <c r="C842" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Two diagnostic medial branch blocks under fluoroscopy/CT, each with &gt;=80% relief of index pain, documented as DIAGNOSTIC (not therapeutic).</t>
+        </is>
+      </c>
+      <c r="D842" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Two diagnostic medial branch blocks under fluoroscopy/CT, at least 2 weeks apart, each with &gt;=80% relief of index pain (Medicare/MCG; UHC commercial defines a positive block as &gt;=50%), documented as DIAGNOSTIC (not therapeutic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B843" s="17" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="C843" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Operative note: approach (endoscopic/open), extradural, each nerve transected named and lateralized (one unit per nerve), imaging used.</t>
+        </is>
+      </c>
+      <c r="D843" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Operative note: approach (endoscopic/open), extradural, each nerve transected named and lateralized (one unit per nerve), imaging used. Record the anaesthesia level: local or moderate sedation with documented need - routine MAC/GA is not reasonable and necessary under L38801.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B844" s="17" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="C844" s="17" t="inlineStr"/>
+      <c r="D844" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Referral on file where the plan requires one (UHC MA HMO/HMO-POS incl. D-SNP/C-SNP, Optum-delegated HMO - PCP submits it; UHC gated commercial; UHC AZ Exchange; Dual Complete).</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B845" s="17" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="C845" s="17" t="inlineStr"/>
+      <c r="D845" s="17" t="inlineStr">
+        <is>
+          <t>- Dr. Luke's procedure claims in 2026 S1 were billed at ASAP Surgery Centers North Valley LLC (ASC); confirm the ASC is contracted with each payer and obtain the ASC's own authorization where the payer requires a facility PA (AHCCCS FFS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B846" s="17" t="inlineStr">
+        <is>
+          <t>A49</t>
+        </is>
+      </c>
+      <c r="C846" s="17" t="inlineStr"/>
+      <c r="D846" s="17" t="inlineStr">
+        <is>
+          <t>- No 64772, 64999 or facet (64490-64495 / 64633-64636) claims appear in the 2026 S1 claims files - there is no payment history yet; track the first claims per payer closely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B847" s="17" t="inlineStr">
+        <is>
+          <t>A39:D39</t>
+        </is>
+      </c>
+      <c r="C847" s="17" t="inlineStr"/>
+      <c r="D847" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: AHCCCS AMPM 320-B (experimental services)</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B848" s="17" t="inlineStr">
+        <is>
+          <t>A40:D40</t>
+        </is>
+      </c>
+      <c r="C848" s="17" t="inlineStr"/>
+      <c r="D848" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B849" s="17" t="inlineStr">
+        <is>
+          <t>A41:D41</t>
+        </is>
+      </c>
+      <c r="C849" s="17" t="inlineStr"/>
+      <c r="D849" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: AHCCCS AMPM 810 FFS Utilization Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B850" s="17" t="inlineStr">
+        <is>
+          <t>A42:D42</t>
+        </is>
+      </c>
+      <c r="C850" s="17" t="inlineStr"/>
+      <c r="D850" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: AHCCCS AMPM 820 FFS Prior Authorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B851" s="17" t="inlineStr">
+        <is>
+          <t>A43:D43</t>
+        </is>
+      </c>
+      <c r="C851" s="17" t="inlineStr"/>
+      <c r="D851" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: LCD Facet Joint Interventions (retired version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B852" s="17" t="inlineStr">
+        <is>
+          <t>A44:D44</t>
+        </is>
+      </c>
+      <c r="C852" s="17" t="inlineStr"/>
+      <c r="D852" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: Response to Comments: Facet Joint Interventions</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B853" s="17" t="inlineStr">
+        <is>
+          <t>A45:D45</t>
+        </is>
+      </c>
+      <c r="C853" s="17" t="inlineStr"/>
+      <c r="D853" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: 2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B854" s="17" t="inlineStr">
+        <is>
+          <t>A46:D46</t>
+        </is>
+      </c>
+      <c r="C854" s="17" t="inlineStr"/>
+      <c r="D854" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: UHC 2026 Individual Exchange plans - Quick reference guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B855" s="17" t="inlineStr">
+        <is>
+          <t>A47:D47</t>
+        </is>
+      </c>
+      <c r="C855" s="17" t="inlineStr"/>
+      <c r="D855" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: UHC Community Plan AZ member handbook excerpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B856" s="17" t="inlineStr">
+        <is>
+          <t>A48:D48</t>
+        </is>
+      </c>
+      <c r="C856" s="17" t="inlineStr"/>
+      <c r="D856" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B857" s="17" t="inlineStr">
+        <is>
+          <t>A49:D49</t>
+        </is>
+      </c>
+      <c r="C857" s="17" t="inlineStr"/>
+      <c r="D857" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: Humana Commercial PA list (stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B858" s="17" t="inlineStr">
+        <is>
+          <t>A50:D50</t>
+        </is>
+      </c>
+      <c r="C858" s="17" t="inlineStr"/>
+      <c r="D858" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: UHC Complete PA requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B859" s="17" t="inlineStr">
+        <is>
+          <t>A51:D51</t>
+        </is>
+      </c>
+      <c r="C859" s="17" t="inlineStr"/>
+      <c r="D859" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: UHC MA PA requirements - prior edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B860" s="17" t="inlineStr">
+        <is>
+          <t>A52:D52</t>
+        </is>
+      </c>
+      <c r="C860" s="17" t="inlineStr"/>
+      <c r="D860" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B861" s="17" t="inlineStr">
+        <is>
+          <t>A53:D53</t>
+        </is>
+      </c>
+      <c r="C861" s="17" t="inlineStr"/>
+      <c r="D861" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B862" s="17" t="inlineStr">
+        <is>
+          <t>A54:D54</t>
+        </is>
+      </c>
+      <c r="C862" s="17" t="inlineStr"/>
+      <c r="D862" s="17" t="inlineStr">
+        <is>
+          <t>NEW SOURCE: Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B863" s="17" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C863" s="17" t="inlineStr">
+        <is>
+          <t>Rates eff. 10/1/2025</t>
+        </is>
+      </c>
+      <c r="D863" s="17" t="inlineStr">
+        <is>
+          <t>File eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B864" s="17" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="C864" s="17" t="inlineStr">
+        <is>
+          <t>UHC West commercial PA</t>
+        </is>
+      </c>
+      <c r="D864" s="17" t="inlineStr">
+        <is>
+          <t>UHC West commercial PA (California product - not applicable in AZ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -602,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -641,7 +640,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5. Arizona WISeR does NOT reach 64772 (NCD 160.1 WISeR codes = 64605/64610 only).</t>
+          <t>5. Medicare Part B: the Noridian Auth Tool shows no prior authorization required for 64772.</t>
         </is>
       </c>
     </row>
@@ -652,7 +651,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -710,12 +708,12 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>Case-by-case under NCD 160.1. Document to L38801 facet-RFA criteria (dual MBB &gt;=80%, frequency limits). Not in WISeR.</t>
+          <t>Case-by-case under NCD 160.1. Document to L38801 facet-RFA criteria (dual MBB &gt;=80%, frequency limits).</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>Noridian PA Lookup screenshot</t>
+          <t>Noridian Auth Tool screenshot (no auth required)</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -1322,7 +1320,6 @@
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A31:F31"/>
@@ -1333,6 +1330,7 @@
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7869,27 +7867,27 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Noridian JF Part B Prior Authorization Lookup Tool (WISeR codes are loaded) - save a dated screenshot to the patient file</t>
+          <t>Noridian Auth Tool - result for 64772: no prior authorization required. Save a dated screenshot to the patient file.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>No standing Part B PA program covers 64772. WISeR Model Provider &amp; Supplier Operational Guide (Arizona is a WISeR state; Noridian JF)</t>
+          <t>None - Medicare Part B has no prior-authorization requirement for 64772 (confirmed with the Noridian Auth Tool)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>WISeR Guide v7.0 - Appendix A Table A2; Appendix C Table C2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>v7.0, 24 Jul 2026 (model runs 1 Jan 2026 - 31 Dec 2031)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>NO - the NCD 160.1 WISeR code set is 64605 and 64610 only (trigeminal). Associated codes (C2): 61790, 64605, 64610, 70450, 76000, 77002, 00222, 01991.</t>
+          <t>n/a - no PA list applies</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
@@ -7922,8 +7920,7 @@
           <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
 L38801 / A58403 (Noridian JF, Arizona contracts 03101/03102) do not list 64772, but they govern facet denervation and a reviewer can apply them by analogy - DOCUMENT TO THEM: two diagnostic MBBs each with &gt;=80% relief of index pain; &gt;=3 months pain; failed conservative care; second block &gt;=2 weeks after the first; CT or fluoroscopic guidance only; one spinal region and 1-2 levels per session; max 2 RF sessions per spinal region per rolling 12 months; repeat only after &gt;=50% relief for &gt;=6 months; if &gt;=2 years since the last RFA, repeat the diagnostic blocks. Sedation (L38801 / A58403): routine moderate sedation, MAC, deep sedation or general anaesthesia for facet denervation is NOT reasonable and necessary; moderate sedation only case by case with documented necessity. L38801 lists as NOT reasonable &amp; necessary: non-thermal denervation (chemical, &lt;80 C, laser, cryoablation), prolotherapy, intra-facet implants. CORRECTION (round 2): the LCD is NOT silent on the endoscopic technique - L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation." Endoscopic MBT is therefore outside the LCD's covered indications (thermal RF only) and is exposed to a not-reasonable-and-necessary denial on review. A58403: non-thermal denervation is reported with 64999 and is non-covered. A58403 ICD-10 list: for DENERVATION use M47.812-M47.817, M47.892-M47.897 or M48.12-M48.17 only - M53.82-M53.87 are flagged for facet cyst procedures, not ablation.
 NCCI (PTP v323r0, eff. 1 Oct 2026): 64772 is column 1 over 64490-64495, 62320-62327, 64479-64484 and 64400-64505 nerve blocks with modifier indicator 0 (no bypass) - same-session blocks are not separately payable. No PTP edit with 64633-64636 or 64625.
-RVU indicators: mult proc 2 (100/50/50 reduction for additional units/procedures), bilateral 0 (no 150% - report each nerve as a unit, RT/LT), assistant surgeon 2 (payable), co-surgeon 1 (with documentation), team 0.
-WISeR: 64772 is NOT a WISeR code (see N).</t>
+RVU indicators: mult proc 2 (100/50/50 reduction for additional units/procedures), bilateral 0 (no 150% - report each nerve as a unit, RT/LT), assistant surgeon 2 (payable), co-surgeon 1 (with documentation), team 0.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -7982,7 +7979,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>No PA program. WISeR does not apply: the WISeR Guide states Railroad Medicare and Medicare Advantage beneficiaries are not impacted.</t>
+          <t>None - no prior-authorization program for 64772</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -9581,7 +9578,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
   </sheetData>
   <autoFilter ref="A1:V2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9594,7 +9590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9610,6 +9606,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -9701,34 +9698,34 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>WISeR Model Provider &amp; Supplier Operational Guide</t>
+          <t>Practitioner PTP edits for 64772</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v323r0</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>24 Jul 2026</t>
+          <t>Eff. 1 Oct 2026</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>cms.gov/priorities/innovation/files/wiser-provider-supplier-guide.pdf</t>
+          <t>Code Research/.../Medicare</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Practitioner PTP edits for 64772</t>
+          <t>Practitioner MUE 64772</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>v323r0</t>
+          <t>MUE 6 / MAI 3</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -9738,134 +9735,134 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare</t>
+          <t>Code Research/.../Medicare/MUE 64772 CMS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Practitioner MUE 64772</t>
+          <t>National PFS RVU file / ASC Addendum AA extracts</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>MUE 6 / MAI 3</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Oct 2026</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare/MUE 64772 CMS</t>
+          <t>Code Research/.../Medicare</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>National PFS RVU file / ASC Addendum AA extracts</t>
+          <t>AHCCCS FFS Physician Fee Schedule</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FFY26</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>File eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare</t>
+          <t>Code Research/.../FY26_Final_PhysicianFeeSchedule.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS FFS Physician Fee Schedule</t>
+          <t>AZ Blue PA Requirements Code Lists</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>FFY26</t>
+          <t>All tabs incl. hidden</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>File eff. 07/01/2026 (64772 rate date 10/1/2025)</t>
+          <t>Updated 09/01/2026</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../FY26_Final_PhysicianFeeSchedule.xlsx</t>
+          <t>Payer's Prior Authorizations Articles/az-blue-prior-auth-code-lists.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists</t>
+          <t>AZ Blue and TPA Jointly Administered Plans</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>All tabs incl. hidden</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Updated 09/01/2026</t>
+          <t>As of 07/2026</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Payer's Prior Authorizations Articles/az-blue-prior-auth-code-lists.xlsx</t>
+          <t>Plan Guides / PA Articles</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>AZ Blue and TPA Jointly Administered Plans</t>
+          <t>AZ Blue eviCore Programs FAQ</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01-2024</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>As of 07/2026</t>
+          <t>Jan 2024</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides / PA Articles</t>
+          <t>Code Research/.../BCBS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>AZ Blue eviCore Programs FAQ</t>
+          <t>AZ Blue Ablation of Peripheral Nerves to Treat Pain</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>01-2024</t>
+          <t>O983.11</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Jan 2024</t>
+          <t>Eff. 06/03/2026</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -9877,56 +9874,56 @@
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>AZ Blue Ablation of Peripheral Nerves to Treat Pain</t>
+          <t>MCG A-0218 / A-0695 / R-0056 / R-0058 working summaries</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>O983.11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Eff. 06/03/2026</t>
+          <t>Accessed 09/22/2026</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../BCBS</t>
+          <t>Code Research/.../BCBS (paraphrased summaries)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>MCG A-0218 / A-0695 / R-0056 / R-0058 working summaries</t>
+          <t>OptumCare Network of AZ - BCBS PA requirements</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OHNC-1-25-00929_09032026</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Accessed 09/22/2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../BCBS (paraphrased summaries)</t>
+          <t>PA Articles / Code Research/.../Optum</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>OptumCare Network of AZ - BCBS PA requirements</t>
+          <t>OptumCare Network of AZ - UHC MA PA and referral requirements</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00928_08262026</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -9943,34 +9940,34 @@
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>OptumCare Network of AZ - UHC MA PA and referral requirements</t>
+          <t>OptumCare Network of AZ Provider Administrative Guide (delegation page)</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00910_06182026</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>PA Articles / Code Research/.../Optum</t>
+          <t>Plan Guides/AZ_Optum Optum delegation.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>OptumCare Network of AZ Provider Administrative Guide (delegation page)</t>
+          <t>UHC QRG - Optum Care Arizona</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00910_06182026</t>
+          <t>PCA-4-26-00582-M&amp;R-QRG_05132026</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -9980,36 +9977,36 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides/AZ_Optum Optum delegation.pdf</t>
+          <t>Code Research/.../Optum</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>UHC QRG - Optum Care Arizona</t>
+          <t>SCAN MA PA requirements</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>PCA-4-26-00582-M&amp;R-QRG_05132026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Rev. 1 Aug 2026</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Optum</t>
+          <t>PA Articles</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>SCAN MA PA requirements</t>
+          <t>SCAN BCG0100 / BCG0111 / CCP0207 / CRP0420</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -10019,73 +10016,73 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Rev. 1 Aug 2026</t>
+          <t>5/28/2026; 5/6/2026; 11/20/2025; 5/28/2026</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>PA Articles</t>
+          <t>Code Research/.../Optum</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>SCAN BCG0100 / BCG0111 / CCP0207 / CRP0420</t>
+          <t>Humana MA &amp; D-SNP PA and Notification List</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>790807ALL0725-C GHHMXVMEN</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>5/28/2026; 5/6/2026; 11/20/2025; 5/28/2026</t>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Optum</t>
+          <t>PA Articles</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Humana MA &amp; D-SNP PA and Notification List</t>
+          <t>Humana Neuroablative Techniques for Chronic Pain (MA)</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>790807ALL0725-C GHHMXVMEN</t>
+          <t>HUM-1168-008</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+          <t>Eff. 08/06/2026</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>PA Articles</t>
+          <t>Code Research/.../Humana</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Humana Neuroablative Techniques for Chronic Pain (MA)</t>
+          <t>Humana Injections for Pain Conditions (MA)</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>HUM-1168-008</t>
+          <t>HUM-1137-010</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>Eff. 08/06/2026</t>
+          <t>Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -10097,34 +10094,34 @@
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>Humana Injections for Pain Conditions (MA)</t>
+          <t>UHC MA / Peoples Health PA requirements</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>HUM-1137-010</t>
+          <t>PCA-4-26-00416-Clinical-QRG_03022026</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Eff. 09/01/2026</t>
+          <t>Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Humana</t>
+          <t>PA Articles</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>UHC MA / Peoples Health PA requirements</t>
+          <t>UHC Commercial advance notification / PA</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>PCA-4-26-00416-Clinical-QRG_03022026</t>
+          <t>PCA-1-26-00657-Clinical-QRG_04232026</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -10141,12 +10138,12 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>UHC Commercial advance notification / PA</t>
+          <t>UHC Individual Exchange PA</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>PCA-1-26-00657-Clinical-QRG_04232026</t>
+          <t>PCA-5-26-00416-Clinical-QRG_03022026</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -10163,12 +10160,12 @@
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>UHC Individual Exchange PA</t>
+          <t>UHC Community Plan AZ - ACC / DD / ALTCS PA</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>PCA-5-26-00416-Clinical-QRG_03022026</t>
+          <t>PCA-5/2/1-24-03748</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -10185,12 +10182,12 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>UHC Community Plan AZ - ACC / DD / ALTCS PA</t>
+          <t>Surest PA requirements</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>PCA-5/2/1-24-03748</t>
+          <t>PCA-1-24-01406</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
@@ -10207,17 +10204,17 @@
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>Surest PA requirements</t>
+          <t>UHC West commercial PA (California product - not applicable in AZ)</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>PCA-1-24-01406</t>
+          <t>PCA-5-24-01315</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Sep 2026</t>
+          <t>Eff. 1 Apr 2026</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -10229,39 +10226,39 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>UHC West commercial PA (California product - not applicable in AZ)</t>
+          <t>UHC Ablative Treatment for Spinal Pain (Commercial/IE)</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>PCA-5-24-01315</t>
+          <t>2026T0107II</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Apr 2026</t>
+          <t>Eff. 1 Feb 2026</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>PA Articles</t>
+          <t>Code Research/.../UHC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>UHC Ablative Treatment for Spinal Pain (Commercial/IE)</t>
+          <t>UHC Ablative Treatment for Spinal Pain (Community Plan)</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>2026T0107II</t>
+          <t>CS001.T</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Feb 2026</t>
+          <t>Eff. 1 Mar 2026</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -10273,17 +10270,17 @@
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>UHC Ablative Treatment for Spinal Pain (Community Plan)</t>
+          <t>UHC Facet Joint and MBB Injections (Commercial/IE)</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>CS001.T</t>
+          <t>2026T0004WW</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Mar 2026</t>
+          <t>Eff. 10 Sep 2026</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -10295,17 +10292,17 @@
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>UHC Facet Joint and MBB Injections (Commercial/IE)</t>
+          <t>UHC Pain Management (MA)</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>2026T0004WW</t>
+          <t>MMP070.12</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>Eff. 10 Sep 2026</t>
+          <t>Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -10317,105 +10314,105 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>UHC Pain Management (MA)</t>
+          <t>AZ UHC Dual Complete / Dual Complete One Provider Manual</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>MMP070.12</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Sep 2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../UHC</t>
+          <t>Plan Guides</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>AZ UHC Dual Complete / Dual Complete One Provider Manual</t>
+          <t>NPPES record - Timothy A. Luke, MD</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>NPI 1437125846</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Last updated 2020-01-20</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides</t>
+          <t>NPPES registry</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>NPPES record - Timothy A. Luke, MD</t>
+          <t>AMA CPT Knowledge Base - endoscopic rhizotomy Q&amp;As (64999 / 64772)</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>NPI 1437125846</t>
+          <t>Paywalled</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Last updated 2020-01-20</t>
+          <t>Nov 2019</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>NPPES registry</t>
+          <t>findacode.com/newsletters/ama-cpt-kb/ (previews only)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>AMA CPT Knowledge Base - endoscopic rhizotomy Q&amp;As (64999 / 64772)</t>
+          <t>AHCCCS AMPM 320-B (experimental services)</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Paywalled</t>
+          <t>320-B</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Eff. 10/01/2022</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>findacode.com/newsletters/ama-cpt-kb/ (previews only)</t>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 320-B (experimental services)</t>
+          <t>AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>320-B</t>
+          <t>Exhibit 300-1</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Eff. 10/01/2022</t>
+          <t>Rev. 07/09/2026</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -10427,17 +10424,17 @@
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
+          <t>AHCCCS AMPM 810 FFS Utilization Management</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>Exhibit 300-1</t>
+          <t>810</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>Rev. 07/09/2026</t>
+          <t>Eff. 06/17/2026</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -10449,17 +10446,17 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 810 FFS Utilization Management</t>
+          <t>AHCCCS AMPM 820 FFS Prior Authorization</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Eff. 06/17/2026</t>
+          <t>Eff. 07/16/2026</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -10471,73 +10468,73 @@
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 820 FFS Prior Authorization</t>
+          <t>LCD Facet Joint Interventions (retired version)</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>L38803</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Eff. 07/16/2026</t>
+          <t>Rev. eff. 07/17/2025 (retired)</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+          <t>Code Research/.../Medicare - text identical to L38801</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>LCD Facet Joint Interventions (retired version)</t>
+          <t>Response to Comments: Facet Joint Interventions</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>L38803</t>
+          <t>A59795</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Rev. eff. 07/17/2025 (retired)</t>
+          <t>Orig. eff. 07/07/2024</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare - text identical to L38801</t>
+          <t>Code Research/.../Medicare</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Response to Comments: Facet Joint Interventions</t>
+          <t>2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>A59795</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>Orig. eff. 07/07/2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare</t>
+          <t>Plan Guides</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
+          <t>UHC 2026 Individual Exchange plans - Quick reference guide</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
@@ -10559,29 +10556,29 @@
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>UHC 2026 Individual Exchange plans - Quick reference guide</t>
+          <t>UHC Community Plan AZ member handbook excerpt</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides</t>
+          <t>Plan Guides/AZ_Medicaid_Handbook.pdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>UHC Community Plan AZ member handbook excerpt</t>
+          <t>HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -10591,51 +10588,51 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Network update 09/18/2026</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides/AZ_Medicaid_Handbook.pdf</t>
+          <t>Plan Guides</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
+          <t>Humana Commercial PA list (stale)</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>399806ALL0224-A GCHM8R6EN</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>Network update 09/18/2026</t>
+          <t>Eff. 07/01/2024, rev. 12/10/2024</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides</t>
+          <t>PA Articles</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Humana Commercial PA list (stale)</t>
+          <t>UHC Complete PA requirements</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>399806ALL0224-A GCHM8R6EN</t>
+          <t>PCA-1-25-02057</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Eff. 07/01/2024, rev. 12/10/2024</t>
+          <t>Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -10647,17 +10644,17 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>UHC Complete PA requirements</t>
+          <t>UHC MA PA requirements - prior edition</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>PCA-1-25-02057</t>
+          <t>PCA-4-26-00416</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Sep 2026</t>
+          <t>Eff. 1 Aug 2026</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -10669,17 +10666,17 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>UHC MA PA requirements - prior edition</t>
+          <t>Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>PCA-4-26-00416</t>
+          <t>BH00798-2-24-QRG_01012025</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Aug 2026</t>
+          <t>Eff. 1 Jan 2026</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -10691,17 +10688,17 @@
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
+          <t>Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>BH00798-2-24-QRG_01012025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026</t>
+          <t>Aug-Sep 2026</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -10713,7 +10710,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
+          <t>Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -10723,32 +10720,10 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Aug-Sep 2026</t>
+          <t>DOS 01/2026-06/2026</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>PA Articles</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>DOS 01/2026-06/2026</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Repository root / Specialty Claims 2026-S1</t>
         </is>
@@ -10765,7 +10740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29577,6 +29552,257 @@
         </is>
       </c>
     </row>
+    <row r="866">
+      <c r="A866" s="15" t="inlineStr">
+        <is>
+          <t>Round 3 - WISeR references removed (user correction: WISeR does not apply to 64772; Noridian Auth Tool = no auth), 23 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B867" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C867" s="17" t="inlineStr">
+        <is>
+          <t>Noridian JF Part B Prior Authorization Lookup Tool (WISeR codes are loaded) - save a dated screenshot to the patient file</t>
+        </is>
+      </c>
+      <c r="D867" s="17" t="inlineStr">
+        <is>
+          <t>Noridian Auth Tool - result for 64772: no prior authorization required. Save a dated screenshot to the patient file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B868" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C868" s="17" t="inlineStr">
+        <is>
+          <t>No standing Part B PA program covers 64772. WISeR Model Provider &amp; Supplier Operational Guide (Arizona is a WISeR state; Noridian JF)</t>
+        </is>
+      </c>
+      <c r="D868" s="17" t="inlineStr">
+        <is>
+          <t>None - Medicare Part B has no prior-authorization requirement for 64772 (confirmed with the Noridian Auth Tool)</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B869" s="17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C869" s="17" t="inlineStr">
+        <is>
+          <t>WISeR Guide v7.0 - Appendix A Table A2; Appendix C Table C2</t>
+        </is>
+      </c>
+      <c r="D869" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B870" s="17" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C870" s="17" t="inlineStr">
+        <is>
+          <t>v7.0, 24 Jul 2026 (model runs 1 Jan 2026 - 31 Dec 2031)</t>
+        </is>
+      </c>
+      <c r="D870" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B871" s="17" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C871" s="17" t="inlineStr">
+        <is>
+          <t>NO - the NCD 160.1 WISeR code set is 64605 and 64610 only (trigeminal). Associated codes (C2): 61790, 64605, 64610, 70450, 76000, 77002, 00222, 01991.</t>
+        </is>
+      </c>
+      <c r="D871" s="17" t="inlineStr">
+        <is>
+          <t>n/a - no PA list applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B872" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C872" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
+L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D872" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
+L38801 / A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B873" s="17" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C873" s="17" t="inlineStr">
+        <is>
+          <t>No PA program. WISeR does not apply: the WISeR Guide states Railroad Medicare and Medicare Advantage beneficiaries are not impacted.</t>
+        </is>
+      </c>
+      <c r="D873" s="17" t="inlineStr">
+        <is>
+          <t>None - no prior-authorization program for 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B874" s="17" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C874" s="17" t="inlineStr">
+        <is>
+          <t>5. Arizona WISeR does NOT reach 64772 (NCD 160.1 WISeR codes = 64605/64610 only).</t>
+        </is>
+      </c>
+      <c r="D874" s="17" t="inlineStr">
+        <is>
+          <t>5. Medicare Part B: the Noridian Auth Tool shows no prior authorization required for 64772.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B875" s="17" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="C875" s="17" t="inlineStr">
+        <is>
+          <t>Case-by-case under NCD 160.1. Document to L38801 facet-RFA criteria (dual MBB &gt;=80%, frequency limits). Not in WISeR.</t>
+        </is>
+      </c>
+      <c r="D875" s="17" t="inlineStr">
+        <is>
+          <t>Case-by-case under NCD 160.1. Document to L38801 facet-RFA criteria (dual MBB &gt;=80%, frequency limits).</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B876" s="17" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C876" s="17" t="inlineStr">
+        <is>
+          <t>Noridian PA Lookup screenshot</t>
+        </is>
+      </c>
+      <c r="D876" s="17" t="inlineStr">
+        <is>
+          <t>Noridian Auth Tool screenshot (no auth required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B877" s="17" t="inlineStr">
+        <is>
+          <t>A7:D7</t>
+        </is>
+      </c>
+      <c r="C877" s="17" t="inlineStr">
+        <is>
+          <t>WISeR Model Provider &amp; Supplier Operational Guide</t>
+        </is>
+      </c>
+      <c r="D877" s="17" t="inlineStr">
+        <is>
+          <t>ROW REMOVED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BCBS'!$A$1:$V$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Optum'!$A$1:$V$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UnitedHealthcare'!$A$1:$V$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'UnitedHealthcare'!$A$1:$V$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Medicare'!$A$1:$U$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Humana'!$A$1:$V$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHCCCS FFS'!$A$1:$V$2</definedName>
@@ -762,7 +762,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>AZ Blue MA list 09/01/2026; Optum BCBS list OHNC-1-25-00929</t>
+          <t>AZ Blue MA list 09/01/2026; Optum BCBS list OHNC-1-25-00929 only for Optum-direct providers</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>None (excluded from Humana PA list); Medicare decides</t>
+          <t>None - not subject to PA; Medicare decides</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928 (eff. 1 Jan 2026, upd. 1 Sep 2026)</t>
+          <t>OHNC-1-25-00928 if Optum-direct; otherwise UHC MA list PCA-4-26-00416</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>PCA-1-26-00657; PCA-5-26-00416; 2026T0107II</t>
+          <t>PCA-1-26-00657 (Commercial); PCA-5-26-00416 (Exchange); PCA-1-25-02057 (UHC Complete); PCA-1-24-01406 (Surest); 2026T0107II</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>PCA-x-24-03748; CS001.T; PCA-4-26-00416</t>
+          <t>ACC PCA-5-24-003748; DD PCA-2-24-03748; ALTCS PCA-1-24-03748; Dual Complete PCA-4-26-00416; CS001.T</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>NO - not listed. Pain Management section lists 62350-62362, 64490-64495, 64628/64629, 64633-64636 - not 64772</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>NO - not listed (facet family 64490-64495 / 64633-64636 is listed)</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>NO - not listed (facet family 64490-64495 / 64633-64636 is listed)</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -3448,22 +3448,22 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
@@ -3672,22 +3672,22 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -3784,22 +3784,22 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
@@ -4008,22 +4008,22 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -4120,22 +4120,22 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -4232,22 +4232,22 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -4344,22 +4344,22 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -4456,22 +4456,22 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -4568,22 +4568,22 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -4680,22 +4680,22 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -4792,22 +4792,22 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00928_08262026</t>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -4904,22 +4904,22 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>NO - absent (facet family is listed)</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -5016,22 +5016,22 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>OHNC-1-25-00929_09032026</t>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>NO - absent (facet family is listed)</t>
+          <t>NO - absent from both lists</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6987,7 +6987,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Navigate, Charter, Compass, NexusACO R / RB / RP, Freedom Granite Advantage-Saver EPO, UHC Complete</t>
+          <t>Navigate, Charter, Compass, NexusACO R / RB / RP, Freedom Granite Advantage-Saver EPO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. REFERRAL: gated plans need an ELECTRONIC PCP referral before the specialist visit (2026 UHC Administrative Guide, commercial chapter). UHC Complete has its own PA list (PCA-1-25-02057, eff. 1 Sep 2026): 64772 absent, but ALL unlisted codes incl. 64999 need PA and there is no non-emergent out-of-network coverage. Commercial "positive block" = &gt;=50% relief (2026T0004WW), not 80%.</t>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. REFERRAL: gated plans need an ELECTRONIC PCP referral before the specialist visit (2026 UHC Administrative Guide, commercial chapter). UHC Complete now has its own row (own PA list). Commercial "positive block" = &gt;=50% relief (2026T0004WW), not 80%.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>UHC Community Plan - ACC, ACC-CRS, DD, DD-CRS, KidsCare, ALTCS-EPD</t>
+          <t>UHC Community Plan - AHCCCS Complete Care (ACC, incl. CRS-designated members)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7307,22 +7307,22 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>NO - not on lists</t>
+          <t>NO - not on list</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal</t>
+          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>UHC Community Plan of AZ PA requirements - ACC, Developmental Disabilities, Long Term Care</t>
+          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid - UnitedHealthcare Community Plan of Arizona</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>PCA-5-24-03748 (ACC); PCA-2-24-03748 (DD); PCA-1-24-03748 (ALTCS)</t>
+          <t>PCA-5-24-003748-Clinical-QRG_05192023</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all three. 64490/64493 require PA (pain injections)</t>
+          <t>NO - absent. 64490 and 64493 require PA (pain injections &amp; management)</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary. KidsCare: no separate KidsCare PA list is on file - confirm which list UHC applies.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -7379,7 +7379,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Surest (formerly BIND), UMR / UHSS, UHC Level Funded, UnitedHealthOne (Golden Rule grp 705214), Student Resources, Empire Plan, Sierra / Health Plan of Nevada</t>
+          <t>UMR / UHSS, UHC Level Funded, UnitedHealthOne (Golden Rule grp 705214), Student Resources, Empire Plan, Sierra / Health Plan of Nevada</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Surest runs a different benefit and PA model from standard UHC Commercial. Empire Plan has an Arizona concentration. SUREST: 64772 is not on the Surest PA list (PCA-1-24-01406, eff. 1 Sep 2026) - Surest itself is NO; the rest of this row stays TO CONFIRM by group.</t>
+          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Empire Plan has an Arizona concentration. Surest now has its own row (own PA list).</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -7680,8 +7680,404 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Complete</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Gated (referral required)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare internal UM</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for UnitedHealthcare Complete</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>PCA-1-25-02057-Clinical-QRG_09172025</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain management section includes 64490, 64493, 64633, 64635. ALL unlisted codes incl. 64999 require PA</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>64772 is not on the UHC Complete list. Members have no non-emergent out-of-network coverage and no coverage outside the service area. Gated plan: electronic PCP referral required before the specialist visit (2026 UHC Administrative Guide). If the procedure is billed as 64999, PA is required. Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 per CMS; this payer may apply its own unit edits</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Surest (formerly Bind) / Surest Flex</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Surest</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare (Surest)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Prior Authorization Requirements for Surest</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>PCA-1-24-01406-Clinical-QRG_05202024</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent. No facet codes on this list; pain management = 62320-62327, 62350-62362, 64451, 64484, 64520, 64620, 64640, E0782-E0786</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>64772 is not on the Surest list and is not a Surest Flex "flexible coverage activation" service (activation must be done &gt;=3 business days before the listed services). Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 per CMS; this payer may apply its own unit edits</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>UHC Community Plan - Developmental Disabilities (DD, incl. DD-CRS)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Medicaid (AHCCCS) - Medicaid and separate-supplement books</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Medicaid</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Community Plan</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Developmental Disabilities - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>PCA-2-24-03748-Clinical-QRG_12302024</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent. 64490 and 64493 require PA (pain injections &amp; management)</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>NO for 64772; endoscopic rhizotomy is UNPROVEN under CS001.T</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>CS001.T; AMPM 320-B; AMPM Exhibit 300-1</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>CS001.T eff. 03/01/2026; 320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named in CS001.T or the AMPM (it appears only on the AHCCCS FFS fee schedule, which is not a coverage document)</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 (CMS); AHCCCS applies its own edits</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS publishes a NON-FACILITY rate where Medicare shows NA - the office is theoretically payable on AHCCCS but not on Medicare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>UHC Community Plan - Arizona Long Term Care (ALTCS-EPD)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Medicaid (AHCCCS) - Medicaid and separate-supplement books</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Medicaid</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Community Plan</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Long Term Care - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>PCA-1-24-03748-Clinical-QRG_12302024</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>NO - absent. 64490 and 64493 require PA (pain injections &amp; management)</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>NO for 64772; endoscopic rhizotomy is UNPROVEN under CS001.T</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>CS001.T; AMPM 320-B; AMPM Exhibit 300-1</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>CS001.T eff. 03/01/2026; 320-B eff. 10/01/2022; Exh. 300-1 rev. 07/09/2026</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named in CS001.T or the AMPM (it appears only on the AHCCCS FFS fee schedule, which is not a coverage document)</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>6 / MAI 3 (CMS); AHCCCS applies its own edits</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>AHCCCS publishes a NON-FACILITY rate where Medicare shows NA - the office is theoretically payable on AHCCCS but not on Medicare.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V16"/>
+  <autoFilter ref="A1:V20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9032,22 +9428,22 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>n/a - Medicare Supplement is excluded from the list</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -9077,7 +9473,7 @@
       </c>
       <c r="T9" s="10" t="inlineStr">
         <is>
-          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card.</t>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card. (The Humana MA/D-SNP PA list 790807ALL0725-C states it "does not apply to policy holders of a Humana Medicare Supplement plan".)</t>
         </is>
       </c>
       <c r="U9" s="10" t="inlineStr">
@@ -9144,22 +9540,22 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>n/a - Medicare Supplement is excluded from the list</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -9256,22 +9652,22 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>n/a - Medicare Supplement is excluded from the list</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -9606,7 +10002,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -10740,7 +11135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29803,6 +30198,2263 @@
         </is>
       </c>
     </row>
+    <row r="879">
+      <c r="A879" s="15" t="inlineStr">
+        <is>
+          <t>Round 4 - PA documents re-matched to the correct payer/plan (user correction), 23 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B880" s="17" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C880" s="17" t="inlineStr">
+        <is>
+          <t>Navigate, Charter, Compass, NexusACO R / RB / RP, Freedom Granite Advantage-Saver EPO, UHC Complete</t>
+        </is>
+      </c>
+      <c r="D880" s="17" t="inlineStr">
+        <is>
+          <t>Navigate, Charter, Compass, NexusACO R / RB / RP, Freedom Granite Advantage-Saver EPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B881" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C881" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is</t>
+        </is>
+      </c>
+      <c r="D881" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B882" s="17" t="inlineStr">
+        <is>
+          <t>A17:V17</t>
+        </is>
+      </c>
+      <c r="C882" s="17" t="inlineStr"/>
+      <c r="D882" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: UnitedHealthcare Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B883" s="17" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="C883" s="17" t="inlineStr">
+        <is>
+          <t>Surest (formerly BIND), UMR / UHSS, UHC Level Funded, UnitedHealthOne (Golden Rule grp 705214), Student Resources, Empire Plan, Sierra / Health Plan of Nevada</t>
+        </is>
+      </c>
+      <c r="D883" s="17" t="inlineStr">
+        <is>
+          <t>UMR / UHSS, UHC Level Funded, UnitedHealthOne (Golden Rule grp 705214), Student Resources, Empire Plan, Sierra / Health Plan of Nevada</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B884" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C884" s="17" t="inlineStr">
+        <is>
+          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Surest runs a different benefit and PA model from standard UHC Commercial. Empire Plan has an Arizona concentration. SUREST: 64772 is not on the Surest PA list (PCA-1-24-01406, eff. 1 Sep 2026) - Surest itself is NO; the rest of this row stays TO CONFIRM by group.</t>
+        </is>
+      </c>
+      <c r="D884" s="17" t="inlineStr">
+        <is>
+          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Empire Plan has an Arizona concentration. Surest now has its own row (own PA list).</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B885" s="17" t="inlineStr">
+        <is>
+          <t>A18:V18</t>
+        </is>
+      </c>
+      <c r="C885" s="17" t="inlineStr"/>
+      <c r="D885" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: Surest (formerly Bind) / Surest Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B886" s="17" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="C886" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan - ACC, ACC-CRS, DD, DD-CRS, KidsCare, ALTCS-EPD</t>
+        </is>
+      </c>
+      <c r="D886" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan - AHCCCS Complete Care (ACC, incl. CRS-designated members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B887" s="17" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C887" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan of AZ PA requirements - ACC, Developmental Disabilities, Long Term Care</t>
+        </is>
+      </c>
+      <c r="D887" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B888" s="17" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="C888" s="17" t="inlineStr">
+        <is>
+          <t>PCA-5-24-03748 (ACC); PCA-2-24-03748 (DD); PCA-1-24-03748 (ALTCS)</t>
+        </is>
+      </c>
+      <c r="D888" s="17" t="inlineStr">
+        <is>
+          <t>PCA-5-24-003748-Clinical-QRG_05192023</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B889" s="17" t="inlineStr">
+        <is>
+          <t>N13</t>
+        </is>
+      </c>
+      <c r="C889" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all three. 64490/64493 require PA (pain injections)</t>
+        </is>
+      </c>
+      <c r="D889" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. 64490 and 64493 require PA (pain injections &amp; management)</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B890" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C890" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal</t>
+        </is>
+      </c>
+      <c r="D890" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B891" s="17" t="inlineStr">
+        <is>
+          <t>A19:V19</t>
+        </is>
+      </c>
+      <c r="C891" s="17" t="inlineStr"/>
+      <c r="D891" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: UHC Community Plan - Developmental Disabilities (DD, incl. DD-CRS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B892" s="17" t="inlineStr">
+        <is>
+          <t>A20:V20</t>
+        </is>
+      </c>
+      <c r="C892" s="17" t="inlineStr"/>
+      <c r="D892" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW: UHC Community Plan - Arizona Long Term Care (ALTCS-EPD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B893" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C893" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D893" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B894" s="17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C894" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D894" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B895" s="17" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C895" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D895" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B896" s="17" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C896" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D896" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B897" s="17" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C897" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D897" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B898" s="17" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C898" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D898" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B899" s="17" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C899" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D899" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B900" s="17" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C900" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D900" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B901" s="17" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C901" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D901" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B902" s="17" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="C902" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D902" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B903" s="17" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C903" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D903" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B904" s="17" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C904" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D904" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B905" s="17" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C905" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D905" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B906" s="17" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="C906" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D906" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B907" s="17" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C907" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D907" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B908" s="17" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C908" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D908" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B909" s="17" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C909" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D909" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B910" s="17" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="C910" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D910" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B911" s="17" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="C911" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D911" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B912" s="17" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="C912" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D912" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B913" s="17" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="C913" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D913" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B914" s="17" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="C914" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D914" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B915" s="17" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C915" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D915" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B916" s="17" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="C916" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D916" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B917" s="17" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C917" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D917" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B918" s="17" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="C918" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D918" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B919" s="17" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="C919" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D919" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B920" s="17" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="C920" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D920" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B921" s="17" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C921" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D921" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B922" s="17" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="C922" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D922" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B923" s="17" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="C923" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D923" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B924" s="17" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="C924" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D924" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B925" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C925" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D925" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B926" s="17" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="C926" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D926" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B927" s="17" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C927" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D927" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B928" s="17" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="C928" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D928" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B929" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C929" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D929" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B930" s="17" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="C930" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D930" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B931" s="17" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C931" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D931" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B932" s="17" t="inlineStr">
+        <is>
+          <t>N11</t>
+        </is>
+      </c>
+      <c r="C932" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D932" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B933" s="17" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C933" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D933" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B934" s="17" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="C934" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D934" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B935" s="17" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="C935" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D935" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B936" s="17" t="inlineStr">
+        <is>
+          <t>N12</t>
+        </is>
+      </c>
+      <c r="C936" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D936" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B937" s="17" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C937" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D937" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B938" s="17" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="C938" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D938" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B939" s="17" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="C939" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D939" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B940" s="17" t="inlineStr">
+        <is>
+          <t>N13</t>
+        </is>
+      </c>
+      <c r="C940" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D940" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B941" s="17" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+      <c r="C941" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UHC Medicare Advantage prior authorization and referral requirements</t>
+        </is>
+      </c>
+      <c r="D941" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B942" s="17" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="C942" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026</t>
+        </is>
+      </c>
+      <c r="D942" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928_08262026 (Optum-direct); PCA-4-26-00416-Clinical-QRG_03022026 (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B943" s="17" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="C943" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D943" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 1 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B944" s="17" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="C944" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent. Pain Management lists 0627T-0630T, 62350-62362, 64490-64495, 64628/64629, 64633-64636</t>
+        </is>
+      </c>
+      <c r="D944" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B945" s="17" t="inlineStr">
+        <is>
+          <t>K15</t>
+        </is>
+      </c>
+      <c r="C945" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D945" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B946" s="17" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="C946" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026</t>
+        </is>
+      </c>
+      <c r="D946" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B947" s="17" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="C947" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D947" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B948" s="17" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="C948" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (facet family is listed)</t>
+        </is>
+      </c>
+      <c r="D948" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B949" s="17" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="C949" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D949" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B950" s="17" t="inlineStr">
+        <is>
+          <t>L16</t>
+        </is>
+      </c>
+      <c r="C950" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026</t>
+        </is>
+      </c>
+      <c r="D950" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B951" s="17" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="C951" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D951" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B952" s="17" t="inlineStr">
+        <is>
+          <t>N16</t>
+        </is>
+      </c>
+      <c r="C952" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent (facet family is listed)</t>
+        </is>
+      </c>
+      <c r="D952" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B953" s="17" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C953" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D953" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B954" s="17" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="C954" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026</t>
+        </is>
+      </c>
+      <c r="D954" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B955" s="17" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="C955" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D955" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B956" s="17" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="C956" s="17" t="inlineStr">
+        <is>
+          <t>NO - not listed. Pain Management section lists 62350-62362, 64490-64495, 64628/64629, 64633-64636 - not 64772</t>
+        </is>
+      </c>
+      <c r="D956" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B957" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C957" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D957" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B958" s="17" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="C958" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026</t>
+        </is>
+      </c>
+      <c r="D958" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B959" s="17" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C959" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D959" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B960" s="17" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="C960" s="17" t="inlineStr">
+        <is>
+          <t>NO - not listed (facet family 64490-64495 / 64633-64636 is listed)</t>
+        </is>
+      </c>
+      <c r="D960" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B961" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C961" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D961" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B962" s="17" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="C962" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026</t>
+        </is>
+      </c>
+      <c r="D962" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00929_09032026 (Optum-direct); AZ Blue 2026 Medicare Advantage List (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B963" s="17" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C963" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, updated 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D963" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jan 2026, upd. 1 Sep 2026; Eff. 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B964" s="17" t="inlineStr">
+        <is>
+          <t>N11</t>
+        </is>
+      </c>
+      <c r="C964" s="17" t="inlineStr">
+        <is>
+          <t>NO - not listed (facet family 64490-64495 / 64633-64636 is listed)</t>
+        </is>
+      </c>
+      <c r="D964" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from both lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B965" s="17" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C965" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+      <c r="D965" s="17" t="inlineStr">
+        <is>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B966" s="17" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="C966" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+      <c r="D966" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B967" s="17" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="C967" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D967" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B968" s="17" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="C968" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+      <c r="D968" s="17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B969" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C969" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+      <c r="D969" s="17" t="inlineStr">
+        <is>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B970" s="17" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="C970" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+      <c r="D970" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B971" s="17" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C971" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D971" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B972" s="17" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="C972" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+      <c r="D972" s="17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B973" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C973" s="17" t="inlineStr">
+        <is>
+          <t>None - the Humana PA list states Medicare Supplement plans are not subject to it</t>
+        </is>
+      </c>
+      <c r="D973" s="17" t="inlineStr">
+        <is>
+          <t>None - Medicare Supplement is not subject to prior authorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B974" s="17" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="C974" s="17" t="inlineStr">
+        <is>
+          <t>790807ALL0725-C GHHMXVMEN (exclusion note)</t>
+        </is>
+      </c>
+      <c r="D974" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B975" s="17" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C975" s="17" t="inlineStr">
+        <is>
+          <t>Eff. 1 Jul 2026, rev. 1 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D975" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B976" s="17" t="inlineStr">
+        <is>
+          <t>N11</t>
+        </is>
+      </c>
+      <c r="C976" s="17" t="inlineStr">
+        <is>
+          <t>n/a - Medicare Supplement is excluded from the list</t>
+        </is>
+      </c>
+      <c r="D976" s="17" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B977" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C977" s="17" t="inlineStr">
+        <is>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card.</t>
+        </is>
+      </c>
+      <c r="D977" s="17" t="inlineStr">
+        <is>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card. (The Humana MA/D-SNP PA list 790807ALL0725-C states it "does not apply to policy holders of a Humana Medicare Supplement plan".)</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B978" s="17" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="C978" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue MA list 09/01/2026; Optum BCBS list OHNC-1-25-00929</t>
+        </is>
+      </c>
+      <c r="D978" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue MA list 09/01/2026; Optum BCBS list OHNC-1-25-00929 only for Optum-direct providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B979" s="17" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C979" s="17" t="inlineStr">
+        <is>
+          <t>None (excluded from Humana PA list); Medicare decides</t>
+        </is>
+      </c>
+      <c r="D979" s="17" t="inlineStr">
+        <is>
+          <t>None - not subject to PA; Medicare decides</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B980" s="17" t="inlineStr">
+        <is>
+          <t>B21</t>
+        </is>
+      </c>
+      <c r="C980" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928 (eff. 1 Jan 2026, upd. 1 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D980" s="17" t="inlineStr">
+        <is>
+          <t>OHNC-1-25-00928 if Optum-direct; otherwise UHC MA list PCA-4-26-00416</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B981" s="17" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="C981" s="17" t="inlineStr">
+        <is>
+          <t>PCA-1-26-00657; PCA-5-26-00416; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D981" s="17" t="inlineStr">
+        <is>
+          <t>PCA-1-26-00657 (Commercial); PCA-5-26-00416 (Exchange); PCA-1-25-02057 (UHC Complete); PCA-1-24-01406 (Surest); 2026T0107II</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B982" s="17" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="C982" s="17" t="inlineStr">
+        <is>
+          <t>PCA-x-24-03748; CS001.T; PCA-4-26-00416</t>
+        </is>
+      </c>
+      <c r="D982" s="17" t="inlineStr">
+        <is>
+          <t>ACC PCA-5-24-003748; DD PCA-2-24-03748; ALTCS PCA-1-24-03748; Dual Complete PCA-4-26-00416; CS001.T</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -626,7 +626,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>3. Coding: AMA CPT Knowledge Base entries (Nov 2019) point endoscopic medial branch rhizotomy to 64999 (unlisted). Industry sources read CMS's Jan 2026 MUE increase for 64772 (2 -&gt; 6 units) as acceptance of the code for MBT, but no CMS or AMA document on file says so. The operative note must describe an extradural transection or avulsion of a named spinal nerve (the medial branch). 64999 is non-covered on Medicare for non-thermal facet denervation (A58403), needs PA on Humana and cannot be paid in an ASC.</t>
+          <t>3. Coding: no document on file addresses whether an endoscopic MBT should be coded 64772 or 64999 (unlisted). Have the coding team confirm from the operative note before the first claim. If 64999 is used: Humana, UHC Exchange and UHC Complete require PA, and an ASC cannot be paid for 64999 under Medicare.</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL (TPA / BCBS SC / home plan)</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>LIKELY NO - CONFIRM</t>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL BANNER</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>- Optum SCAN PA list and Optum AZ web pages (business.optum.com is blocked from this environment) - confirm SCAN rows with Optum 877-370-2845.</t>
+          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1273,14 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository - their rows were not re-verified.</t>
+          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository; those rows rely on your portal checks.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>- AMA CPT Knowledge Base answers on endoscopic rhizotomy (Nov 2019) are paywalled - pull the full text (AMA CPT Network) before finalizing the code.</t>
+          <t>- Code selection (64772 vs 64999) for endoscopic MBT: confirm with the coding team from the operative note.</t>
         </is>
       </c>
     </row>
@@ -1558,11 +1558,9 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the 2026 STANDARD Code List (1,909 rows, updated 09/01/2026). BUT on the same list facet RFA 64633/64635 DOES require AZ Blue PA (Gold Card eligible for cervical/lumbar). eviCore MSK/interventional pain is Medicare Advantage only (AZ Blue eviCore FAQ 01-2024) - commercial pain PA is requested from AZ Blue directly.
-Since 7/1/2026: a required PA that is not obtained = claim line not reimbursed and the member cannot be billed. AZ Blue also 'reserves the right to require prior authorization for ... newly released and changed items even though the lists have not yet been updated'.
-Hidden legacy tabs in the AZ Blue workbook: 'CommercialMR' flags 64772 ON and 'Denied2019' shows 20 denials for 64772 - undated/historical, but a sign 64772 has been routed to medical review before.
-NOT GOVERNING: AZ Blue O983.11 Ablation of Peripheral Nerves (eff. 06/03/2026) covers peripheral sites distant from the spine, lists only 64624/64640/64628/64629/C9809/G0571 and expressly carves out facet joint pain - it does not govern 64772. No AZ Blue facet-denervation medical policy is in the repository. MCG A-0218 allows a repeat neurotomy after &gt;=50% relief for &gt;=3 months (Medicare LCD: &gt;=6 months).
-RECOMMEND: written predetermination before scheduling; build the chart to MCG A-0218 / A-0695 (dual MBB &gt;=80%, 3+ months pain, failed conservative care, imaging excluding other causes).</t>
+          <t>PA: NOT required - 64772 is not on the 2026 Standard list (09/01/2026). Facet RFA 64633-64636 IS on it (AZ Blue PA).
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -1603,7 +1601,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL BCBS SC</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1628,12 +1626,12 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1658,7 +1656,9 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Per AZ Blue code lists Introduction (09/01/2026): prefixes AOZ, AZI, AZK, IVR - BCBS South Carolina handles UM. Not checked with BCBS SC. CONFLICT TO RESOLVE: IVR is ALSO printed in the STANDARD Code List's applicable-prefix header - confirm which applies.</t>
+          <t>PA: decided by BCBS South Carolina (AZ Blue code-list Introduction). No BCBS SC list on file.
+Note: IVR also appears in the Standard list prefix header.
+Action: call BCBS SC 800-868-1032 before scheduling; record name, date and reference #.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL AHG</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1758,7 +1758,8 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Per AZ Blue and TPA Jointly Administered Plans (as of 07/2026): the group may customize PA requirements; the TPA or its vendor runs UM and medical policy. Claims go to AZ Blue (EDI #53589). Not checked with AHG.</t>
+          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue TPA document, 07/2026). No AHG list on file.
+Action: call AHG 800-847-7605 before scheduling; record reference #. Claims still go to AZ Blue (EDI 53589).</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1803,7 +1804,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL AMERIBEN</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1828,12 +1829,12 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1858,7 +1859,8 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Round 2: the MCG reference previously in L ("MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG") could not be found in any repository document and was removed - ask AmeriBen which criteria set it applies.</t>
+          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue TPA document, 07/2026). No AmeriBen list on file.
+Action: call the AmeriBen line for the prefix (column J) before scheduling; record reference #. Claims go to AZ Blue (EDI 53589).</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1899,7 +1901,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL TPA</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1924,12 +1926,12 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1954,7 +1956,8 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Not established.</t>
+          <t>PA: decided by the TPA on the ID card (AZ Blue code-list Introduction). No list on file.
+Action: call the number on the ID card before scheduling; record reference #.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -2045,12 +2048,14 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the list. On the same list 64490-64495, 64625 and 64633-64636 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the 2026 AZ Blue MA list (09/01/2026); AZ Blue PA Lookup also returned not required (your check). Facet codes 64490-64495, 64625, 64633-64636 ARE on it (eviCore).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: if the MBT is endoscopic, request a pre-service organization determination from AZ Blue.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -2141,12 +2146,14 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>64772 is not listed in Optum's BCBS PA requirements. The list applies to providers with Optum DIRECT contracts; other providers follow the plan's own requirements. All out-of-network services require Optum PA.</t>
+          <t>PA: NOT required - 64772 is not on the Optum BCBS list (Optum-direct providers) or the AZ Blue MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: check the ID card for the administrator; if endoscopic, request a pre-service organization determination.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -2237,12 +2244,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>This is a list of services that do NOT require authorisation. 64772 is absent, so absence means authorisation IS required. Inverted-list reasoning is conservative in the right direction but worth one confirming call. (The AZPC attachment is not in this repository - not re-verified.)</t>
+          <t>PA: REQUIRED - AZPC Attachment A lists services that do NOT need auth; 64772 is not on it (eff. 8/21/2026; document not in the repository).
+Action: submit the auth on the AZ CONNECT portal before scheduling.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -2295,7 +2303,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2345,12 +2353,14 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>FULL delegation to Optum (OptumCare Network of AZ Provider Administrative Guide, OHNC-1-25-00910_06182026). Optum's BCBS PA list, now on file (Sept 2026), omits 64772. It applies to Optum direct-contracted providers; if Dr. Luke is not Optum-direct, use the AZ Blue MA requirements (row 7). MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>PA: NOT required - 64772 is not on the Optum BCBS list or the AZ Blue MA list. Plan is fully delegated to Optum (Optum AZ admin guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: any request goes through optumproportal.com; if endoscopic, request a pre-service decision.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -2403,7 +2413,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2453,12 +2463,12 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>As above.</t>
+          <t>Same as Blue Best Life Classic (row 10).</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -2554,7 +2564,9 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool. Related codes that ARE on the 2026 FEP List: 63185 / 63190 (laminectomy with rhizotomy) - AZ Blue PA, FEP Standard and Basic only.</t>
+          <t>PA: NOT required - 64772 is not on the 2026 FEP list; AZ Blue PA Lookup and Availity returned not required (your checks).
+Related: 63185/63190 (laminectomy with rhizotomy) DO require PA on FEP Standard/Basic.
+Action: keep the lookup screenshots.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -2645,12 +2657,13 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion'. Payment 'may be made... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no conservative-care prerequisite, no covered-dx table. INHERITED RISK: if Medicare denies on medical review, the Medigap plan pays nothing. 'NO auth required' is true and still not the same as 'safe'.</t>
+          <t>PA: none - Medigap has no prior authorization.
+Coverage: pays only after Medicare pays; if Medicare denies, Medigap pays nothing. See Medicare tab.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2746,7 +2759,8 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+          <t>PA: NOT required - not on the Health Choice grid; portal submission returned not required (your check).
+Action: keep the portal result.</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2837,12 +2851,14 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+          <t>PA: NOT required - not on the Health Choice Pathway grid; portal submission returned not required (your check).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: keep the portal result.</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -2938,7 +2954,9 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>Not on the grid. An auth was filed on the portal and none was required. AHCCCS-wide: 64772 is on the FFY26 fee schedule at $578.79 non-facility AND facility, but AHCCCS states a listed code and rate is 'not an indication of coverage, nor a guarantee of payment' - coverage lives in the AMPM. (The Health Choice PA grids are not in this repository - not re-verified.)</t>
+          <t>PA: NOT required - not on the Health Choice grid; portal submission returned not required (your check).
+Coverage: AHCCCS does not cover experimental services (AMPM 320-B); moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). 64772 is on the AHCCCS fee schedule ($578.79), which is not a coverage decision.
+Action: keep the portal result; do not bill 99152/99153 for the surgeon's own sedation.</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2960,7 +2978,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Varies by home plan</t>
+          <t>Per home plan</t>
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
@@ -2979,7 +2997,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>VARIES BY HOME PLAN</t>
+          <t>CALL HOME PLAN</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3004,12 +3022,12 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>Home plan decides - see T</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>Home plan decides - see T</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3034,7 +3052,8 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Not established - differs by home plan.</t>
+          <t>PA: decided by the member's home Blue plan. Claim still files to AZ Blue.
+Action: use the BlueCard Medical Policy Router in Availity to reach the home plan's PA rules before scheduling.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -3079,7 +3098,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -3134,7 +3153,9 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the list. 64490-64495 and 64633-64636 DO require AZ Blue PA for this group (site-of-service review: No). All non-emergency admissions (except maternity) need PA. Group is delegated for eviCore (imaging, lab, oncology, radiation - not MSK on commercial).</t>
+          <t>PA: NOT required - 64772 is not on the 2026 State of AZ list (09/01/2026). 64490-64495 and 64633-64636 DO require AZ Blue PA for this group.
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -3179,7 +3200,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3234,7 +3255,9 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the list, and no facet codes are on it either.</t>
+          <t>PA: NOT required - 64772 is not on the 2026 Teamsters list (09/01/2026).
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3438,7 +3461,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3473,27 +3496,30 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -3550,7 +3576,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3585,27 +3611,30 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -3662,7 +3691,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3697,27 +3726,30 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (H5253-035 is exempt).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -3774,7 +3806,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3809,27 +3841,30 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -3886,7 +3921,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -3921,27 +3956,30 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -3998,7 +4036,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -4033,27 +4071,30 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -4110,7 +4151,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -4145,27 +4186,30 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -4222,7 +4266,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -4257,27 +4301,30 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -4334,7 +4381,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -4369,27 +4416,30 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -4446,7 +4496,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -4481,27 +4531,30 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -4558,7 +4611,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -4593,27 +4646,30 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -4670,7 +4726,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -4705,27 +4761,30 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -4782,7 +4841,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -4817,27 +4876,30 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new technology are not covered unless Optum Care has found they meet coverage requirements AND PA was obtained - relevant if the MBT is endoscopic. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -4894,7 +4956,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -4944,12 +5006,12 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>See BCBS tab rows 10-11. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>Same as BCBS tab rows 10-11.</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -5006,7 +5068,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -5056,12 +5118,12 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>See BCBS tab rows 10-11. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+          <t>Same as BCBS tab rows 10-11.</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -5116,14 +5178,14 @@
           <t>Optum Health Networks - full delegation (per Optum AZ administrative guide)</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>LIKELY NO - CONFIRM</t>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+          <t>optumproportal.com / 877-370-2845</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -5168,12 +5230,14 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -5228,14 +5292,14 @@
           <t>Optum Health Networks - full delegation (per Optum AZ administrative guide)</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>LIKELY NO - CONFIRM</t>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+          <t>optumproportal.com / 877-370-2845</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -5280,12 +5344,14 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -5340,14 +5406,14 @@
           <t>Optum Health Networks - full delegation (per Optum AZ administrative guide)</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>LIKELY NO - CONFIRM</t>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+          <t>optumproportal.com / 877-370-2845</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -5392,12 +5458,14 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -5452,14 +5520,14 @@
           <t>Optum Health Networks - full delegation (per Optum AZ administrative guide)</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>LIKELY NO - CONFIRM</t>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+          <t>optumproportal.com / 877-370-2845</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -5504,12 +5572,14 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -5564,14 +5634,14 @@
           <t>Optum Health Networks - full delegation (per Optum AZ administrative guide)</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>LIKELY NO - CONFIRM</t>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+          <t>optumproportal.com / 877-370-2845</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -5616,12 +5686,14 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not covered under Medicare" and the member pays in full if they proceed - the likely SCAN position on endoscopic MBT given the L38801 evidence statement.</t>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -5670,7 +5742,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL PLAN ON CARD</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -5725,7 +5797,8 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Optum publishes two delegation tiers. FULL delegation means Optum decides PA. CARE MANAGEMENT delegation does not - authority stays with the plan.</t>
+          <t>PA: Optum has care-management delegation only; PA stays with the plan on the ID card (Optum AZ admin guide).
+Action: use that plan's row in this workbook.</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -5774,7 +5847,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL IPA</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -5799,12 +5872,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -5829,7 +5902,8 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>Per UHC: 'if you are a network provider who is contracted directly with a delegated medical group/IPA, then you must follow the delegate's protocols' - delegates use their own systems and forms.</t>
+          <t>PA: the delegated IPA's own rules apply (UHC MA PA list: providers contracted with a delegated IPA must follow its protocols). No IPA list on file.
+Action: call the IPA before scheduling; record reference #.</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -5886,7 +5960,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL BANNER</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -5911,12 +5985,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -5941,7 +6015,8 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Routing guard. Shares contracts and PBPs with the Optum rows but different group numbers - H0609-026 group 91038 is Optum, 91037 is Banner. Banner group list confirmed in the UHC MA PA requirements (PCA-4-26-00416, eff. 1 Sep 2026). The Banner QRG is not in this repository.</t>
+          <t>PA: these group numbers are delegated to Banner (UHC MA PA list, eff. 9/1/2026). Banner's list is not on file.
+Action: call Banner (number on the ID card) before scheduling; do not use optumproportal.com.</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -5998,7 +6073,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>NO - treat as Optum</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -6028,7 +6103,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -6053,7 +6128,8 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Group 96001 (H0609-027-000) IS listed as delegated to OptumCare in both the UHC MA PA requirements (eff. 1 Sep 2026) and the UHC QRG PCA-4-26-00582. It is still missing from the Optum administrative guide's plan table (H0609 Plan 2 = 00329/00330/00340). Two UHC sources outweigh the omission - route to Optum; confirm the plan name with the Optum rep.</t>
+          <t>PA: NOT required - group 96001 (H0609-027) is listed as Optum-delegated in the UHC MA PA list and QRG PCA-4-26-00582; 64772 is not on the Optum or UHC MA lists.
+Action: treat as Optum (rows above).</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -6243,7 +6319,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -6278,27 +6354,30 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -6339,7 +6418,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -6374,27 +6453,30 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -6435,7 +6517,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -6470,27 +6552,30 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -6531,7 +6616,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -6566,27 +6651,30 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL (2026 UHC Administrative Guide, Medicare chapter): MA HMO and HMO-POS members - including D-SNP and C-SNP HMO/HMO-POS and Group MA HMO - need a PCP referral on file before the specialist visit. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -6627,7 +6715,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -6662,27 +6750,30 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -6723,7 +6814,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -6758,27 +6849,30 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). ERICKSON: the UHC MA PA list requires Erickson PA for experimental and investigational services - if the MBT is endoscopic, obtain Erickson PA. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, call the Erickson PA number on the ID card - Erickson requires PA for experimental/investigational services.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -6819,7 +6913,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -6854,27 +6948,30 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403) (Medicare benefit); AHCCCS AMPM 320-B for the Medicaid wrap (experimental services not covered)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; AMPM 320-B</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; 320-B eff. 10/01/2022</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted. The Dual Complete provider manual (2026) is the source of these rules but is not a coverage policy. Members must coordinate with their PCP before seeing a specialist; non-contracted providers need a referral form and PA. QMB members: $0 cost share - do not bill the member. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Referral: members must coordinate with their PCP; non-contracted providers need a referral form and PA (Dual Complete manual).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS benefits.
+Action: PA line 800-445-1638 if needed. QMB members owe $0 - do not bill the member.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -6915,7 +7012,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -6950,27 +7047,30 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a voluntary pre-service organization determination through the PA&amp;N tool. Check the group number first: AZ groups delegated to OptumCare or Banner are on the Optum tab. REFERRAL: not required for this plan type (2026 UHC Administrative Guide). L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation."</t>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -7011,7 +7111,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -7046,27 +7146,30 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+          <t>2026T0107II; 2026T0004WW</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+          <t>1 Feb 2026; 10 Sep 2026</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all four</t>
+          <t>NO - 64772 not listed in either</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. REFERRAL: gated plans need an ELECTRONIC PCP referral before the specialist visit (2026 UHC Administrative Guide, commercial chapter). UHC Complete now has its own row (own PA list). Commercial "positive block" = &gt;=50% relief (2026T0004WW), not 80%.</t>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: REQUIRED - electronic PCP referral before the visit.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -7076,7 +7179,7 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7210,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -7142,27 +7245,30 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+          <t>2026T0107II; 2026T0004WW</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+          <t>1 Feb 2026; 10 Sep 2026</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all four</t>
+          <t>NO - 64772 not listed in either</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. Open-access plans: no PCP referral. Commercial "positive block" = &gt;=50% relief (2026T0004WW).</t>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: NOT required.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -7172,7 +7278,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7317,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -7246,27 +7352,30 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service (Individual Exchange follows the commercial policies)</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+          <t>2026T0107II; 2026T0004WW</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+          <t>1 Feb 2026; 10 Sep 2026</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all four</t>
+          <t>NO - 64772 not listed in either</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is NOT coverage. ARIZONA EXCHANGE REQUIRES PCP REFERRALS - UHC will not accept a PA without a referral on file (2026 Individual Exchange QRG / Administrative Guide ch. 4). No out-of-network or out-of-area coverage. Unlisted codes incl. 64999 require PA on the Exchange list.</t>
+          <t>PA: NOT required - 64772 is not on the Individual Exchange list (eff. 9/1/2026). 64999 WOULD need PA. 64490, 64493, 64633, 64635 need PA + site-of-service review.
+Referral: REQUIRED in Arizona - UHC will not accept a PA without a referral on file. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -7276,7 +7385,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification.</t>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7416,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -7362,7 +7471,9 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary. KidsCare: no separate KidsCare PA list is on file - confirm which list UHC applies.</t>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -7403,7 +7514,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>CALL TPA</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -7428,12 +7539,12 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No list on file - call (see T)</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -7453,12 +7564,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>TO CONFIRM</t>
+          <t>No policy on file</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Empire Plan has an Arizona concentration. Surest now has its own row (own PA list).</t>
+          <t>PA: set by each group's plan document and TPA supplement - no list on file.
+Action: check the member's ID card / portal (UMR: umr.com) and call before scheduling; record reference #.</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -7499,7 +7611,7 @@
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>N/A - NOT AN AZ PRODUCT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -7554,7 +7666,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION (round 2): this row was added in round 1 because the West list footer names "UnitedHealthcare of Arizona, Inc." - but that footer is the standard multi-entity footer that also appears on the national Commercial list, so it is not evidence. The 2026 UHC Administrative Guide (Others, ch. 1) defines UHC West as UnitedHealthcare of California (CA), and states PacifiCare of Arizona is now UnitedHealthcare Benefits of Texas. Arizona commercial members use the national Commercial rows above. Kept only as a routing guard: if a card shows a West/California product, verify on the portal. 64772 is not on the West list.</t>
+          <t>Not used for Arizona members - UHC West is UnitedHealthcare of California (2026 UHC Administrative Guide).</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -7646,27 +7758,29 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>No PA. The supplement follows Medicare's determination: if Medicare denies 64772 on medical review (see the Medicare tab, incl. the L38801 endoscopic-evidence statement), the supplement pays nothing. Medicare Select plans may require use of network hospitals for Part A services.</t>
+          <t>PA: none (2026 UHC Administrative Guide).
+Coverage: pays only after Medicare pays - see Medicare tab.
+Claims: payer ID 36273.</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -7742,27 +7856,30 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+          <t>2026T0107II; 2026T0004WW</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+          <t>1 Feb 2026; 10 Sep 2026</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all four</t>
+          <t>NO - 64772 not listed in either</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the UHC Complete list. Members have no non-emergent out-of-network coverage and no coverage outside the service area. Gated plan: electronic PCP referral required before the specialist visit (2026 UHC Administrative Guide). If the procedure is billed as 64999, PA is required. Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+          <t>PA: NOT required - 64772 is not on the UHC Complete list (eff. 9/1/2026). 64999 WOULD need PA.
+Referral: REQUIRED - electronic PCP referral. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -7772,7 +7889,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
         </is>
       </c>
     </row>
@@ -7850,27 +7967,29 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+          <t>2026T0107II; 2026T0004WW</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+          <t>1 Feb 2026; 10 Sep 2026</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>NO - absent from all four</t>
+          <t>NO - 64772 not listed in either</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>64772 is not on the Surest list and is not a Surest Flex "flexible coverage activation" service (activation must be done &gt;=3 business days before the listed services). Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+          <t>PA: NOT required - 64772 is not on the Surest list (eff. 9/1/2026) and is not a Surest Flex activation service.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -7880,7 +7999,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
         </is>
       </c>
     </row>
@@ -7911,7 +8030,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -7966,7 +8085,9 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -8007,7 +8128,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>NO - not on list</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -8062,7 +8183,9 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for any service considered E/I (AMPM 320-B). Combined with CS001.T (endoscopic rhizotomy unproven), an endoscopic MBT is not a covered AHCCCS benefit. AMPM Exhibit 300-1: moderate sedation given by the physician performing the procedure is NOT covered. Fee schedule file is "Effective 7/01/2026" (64772 rate date 10/1/2025). PA phone: ACC/DD 800-445-1638; ALTCS 877-842-3210. Every rendering provider must be AHCCCS-registered. UHC Community Plan policy CS001.T (Arizona is not on its state-exclusion list) lists endoscopic RFA / endoscopic rhizotomy, pulsed, cooled, chemical, laser and cryoablation as unproven and not medically necessary.</t>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 877-842-3210.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -8308,15 +8431,16 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
-L38801 / A58403 (Noridian JF, Arizona contracts 03101/03102) do not list 64772, but they govern facet denervation and a reviewer can apply them by analogy - DOCUMENT TO THEM: two diagnostic MBBs each with &gt;=80% relief of index pain; &gt;=3 months pain; failed conservative care; second block &gt;=2 weeks after the first; CT or fluoroscopic guidance only; one spinal region and 1-2 levels per session; max 2 RF sessions per spinal region per rolling 12 months; repeat only after &gt;=50% relief for &gt;=6 months; if &gt;=2 years since the last RFA, repeat the diagnostic blocks. Sedation (L38801 / A58403): routine moderate sedation, MAC, deep sedation or general anaesthesia for facet denervation is NOT reasonable and necessary; moderate sedation only case by case with documented necessity. L38801 lists as NOT reasonable &amp; necessary: non-thermal denervation (chemical, &lt;80 C, laser, cryoablation), prolotherapy, intra-facet implants. CORRECTION (round 2): the LCD is NOT silent on the endoscopic technique - L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsal ramus rhizotomy) has also been proposed. There is insufficient evidence in the published medical literature to determine the safety and efficacy of these emerging alternative modalities or approaches compared to thermal radiofrequency denervation." Endoscopic MBT is therefore outside the LCD's covered indications (thermal RF only) and is exposed to a not-reasonable-and-necessary denial on review. A58403: non-thermal denervation is reported with 64999 and is non-covered. A58403 ICD-10 list: for DENERVATION use M47.812-M47.817, M47.892-M47.897 or M48.12-M48.17 only - M53.82-M53.87 are flagged for facet cyst procedures, not ablation.
-NCCI (PTP v323r0, eff. 1 Oct 2026): 64772 is column 1 over 64490-64495, 62320-62327, 64479-64484 and 64400-64505 nerve blocks with modifier indicator 0 (no bypass) - same-session blocks are not separately payable. No PTP edit with 64633-64636 or 64625.
-RVU indicators: mult proc 2 (100/50/50 reduction for additional units/procedures), bilateral 0 (no 150% - report each nerve as a unit, RT/LT), assistant surgeon 2 (payable), co-surgeon 1 (with documentation), team 0.</t>
+          <t>PA: NOT required - Noridian Auth Tool (your check).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Also in L38801: CT/fluoro guidance only; 1-2 levels per session, one region; repeat only after &gt;=50% relief for &gt;=6 months; routine MAC/general anesthesia not covered.
+Billing: dx M47.812-M47.817, M47.892-M47.897 or M48.12-M48.17 (A58403). MBB/ESI/nerve blocks same session are bundled into 64772 (NCCI, modifier indicator 0). Multiple-procedure rule 2 (50% on additional); no bilateral 150%.
+Action: keep the Noridian screenshot; document every L38801 criterion before scheduling.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -8415,12 +8539,14 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Railroad Medicare is administered nationally by Palmetto GBA but applies the LCD/LCA of the MAC in whose jurisdiction the service is rendered, so L38801 / A58403 still govern and the NCD 160.1 case-by-case result is unchanged.</t>
+          <t>PA: NOT required.
+Coverage: same as Traditional Part B - Palmetto GBA applies Noridian L38801/A58403 for Arizona services.
+Action: same as Traditional Part B.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -8631,7 +8757,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Availity and Cohere both returned NO AUTHORIZATION REQUIRED for 64772. Because the Humana policy excludes endoscopic rhizotomy, request an Advance Coverage Determination (ACD): phone 800-523-0023, fax 800-266-3022, or mail Humana Correspondence, P.O. Box 14601, Lexington, KY 40512-4601</t>
+          <t>Availity / Cohere - both returned NOT required (your check). ACD: 800-523-0023, fax 800-266-3022</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -8681,10 +8807,9 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION - a Humana policy DOES address this procedure. HUM-1168-008 Coverage Limitations: 'Endoscopic radiofrequency ablation/rhizotomy for any indication including, but not limited to, the facet joint/nerve' will not be considered medically reasonable and necessary (Hayes brief, 10 Jun 2024). It also excludes cooled RF, pulsed RF, laser, cryoneurolysis, SI-joint (64625) and DRG ablation 'regardless of the type of neuroablative technique used'. For facet denervation 64633-64636 it defers to NCD 160.1 and, in Arizona, Noridian L38801 / A58403.
-PA list (eff. 1 Jul 2026, rev. 1 Sep 2026): the facet family (64490-64495, 64633-64636, 64999, 0213T-0218T), epidural codes and 64625 need PA through Cohere - 64772 does not. Services without PA remain 'subject to retrospective medical necessity review'.
-RISK: an endoscopic MBT billed as 64772 will likely be denied on post-payment review under HUM-1168-008, and a contracted provider cannot bill the member without a pre-service denial. Get an ACD first. If the procedure is coded 64999 instead, PA through Cohere IS required.
-OTHER PA-LIST RULES: HMO members assigned to a delegated IPA/risk network follow the IPA's rules; PFFS plans have no PA (ACD available); an ACD is available for any investigational/experimental service. HUM-1137-010: facet injections/MBB follow L38801/A58403; moderate sedation 99152/99153 is in its coding table.</t>
+          <t>PA: NOT required - 64772 is not on the Humana MA/D-SNP list (eff. 7/1/2026, rev. 9/1/2026); Availity and Cohere returned not required (your check). 64999 and facet codes 64490-64495, 64633-64636 DO need PA through Cohere.
+Coverage: HUM-1168-008 - endoscopic RF ablation/rhizotomy for any indication, including the facet nerve, is NOT reasonable and necessary. Conventional facet RFA follows L38801/A58403.
+Action: request an Advance Coverage Determination before scheduling (800-523-0023 / fax 800-266-3022 / PO Box 14601, Lexington KY 40512-4601). Without it, a post-payment denial is likely and the member cannot be billed.</t>
         </is>
       </c>
       <c r="U2" s="10" t="inlineStr">
@@ -8797,7 +8922,7 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U3" s="10" t="inlineStr">
@@ -8911,7 +9036,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U4" s="10" t="inlineStr">
@@ -9024,7 +9149,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U5" s="10" t="inlineStr">
@@ -9137,7 +9262,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U6" s="10" t="inlineStr">
@@ -9249,7 +9374,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U7" s="10" t="inlineStr">
@@ -9361,7 +9486,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Same as row 2.</t>
         </is>
       </c>
       <c r="U8" s="10" t="inlineStr">
@@ -9473,7 +9598,9 @@
       </c>
       <c r="T9" s="10" t="inlineStr">
         <is>
-          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card. (The Humana MA/D-SNP PA list 790807ALL0725-C states it "does not apply to policy holders of a Humana Medicare Supplement plan".)</t>
+          <t>PA: none - Medigap has no prior authorization.
+Coverage: pays only after Medicare pays - see Medicare tab.
+Note: HumanaMS.pdf names the plans "Humana Plan F / Plan N"; "VALUE"/"ACHIEVE" is not in any document on file - check the ID card.</t>
         </is>
       </c>
       <c r="U9" s="10" t="inlineStr">
@@ -9585,7 +9712,7 @@
       </c>
       <c r="T10" s="10" t="inlineStr">
         <is>
-          <t>As row 9 (name "ACHIEVE" not found in HumanaMS.pdf - confirm against the member card).</t>
+          <t>Same as row 9.</t>
         </is>
       </c>
       <c r="U10" s="10" t="inlineStr">
@@ -9697,7 +9824,7 @@
       </c>
       <c r="T11" s="10" t="inlineStr">
         <is>
-          <t>As row 9. HumanaMS.pdf lists A, B, C, F, G, F-HD, G-HD, K, L and N for Maricopa 85023.</t>
+          <t>Same as row 9.</t>
         </is>
       </c>
       <c r="U11" s="10" t="inlineStr">
@@ -9960,7 +10087,9 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>NEW ROW (round 2) - this book was missing. AMPM 820 U: FFS surgeons "shall obtain a separate and distinct AHCCCS PA number ... prior to providing elective/non-emergency surgeries"; AMPM 820 T: the ASC must obtain its own PA for all outpatient surgeries; L.3.b: hospital outpatient surgery needs authorization. Assistant surgeons and anaesthesiologists do not need a separate PA. No PA needed when the provider/facility is IHS or a 638 tribal facility, for emergencies, when AHCCCS is not primary, or for retro-eligibility. A PA "does not guarantee payment". Standard decision 14 days, expedited 72 hours. Experimental services are not covered (320-B); moderate sedation by the performing physician is not covered (Exh. 300-1). Put member name/DOB/ID on every page submitted.</t>
+          <t>PA: REQUIRED - elective outpatient surgery needs a surgeon PA AND a separate ASC/hospital PA (AMPM 820). Not needed if IHS/638 facility, emergency, or AHCCCS not primary.
+Coverage: experimental services not covered (AMPM 320-B); moderate sedation by the performing physician not covered (Exh. 300-1).
+Action: submit both PAs on AHCCCS Online (fax 602-256-6591; phone 602-417-4400) before scheduling; put member name/DOB/ID on every page.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -9986,7 +10115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10753,39 +10882,39 @@
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>AMA CPT Knowledge Base - endoscopic rhizotomy Q&amp;As (64999 / 64772)</t>
+          <t>AHCCCS AMPM 320-B (experimental services)</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Paywalled</t>
+          <t>320-B</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Nov 2019</t>
+          <t>Eff. 10/01/2022</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>findacode.com/newsletters/ama-cpt-kb/ (previews only)</t>
+          <t>Code Research/Criteria and Coverage Policies - Articles</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 320-B (experimental services)</t>
+          <t>AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>320-B</t>
+          <t>Exhibit 300-1</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>Eff. 10/01/2022</t>
+          <t>Rev. 07/09/2026</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -10797,17 +10926,17 @@
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM Exhibit 300-1 (covered services, special circumstances)</t>
+          <t>AHCCCS AMPM 810 FFS Utilization Management</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Exhibit 300-1</t>
+          <t>810</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Rev. 07/09/2026</t>
+          <t>Eff. 06/17/2026</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -10819,17 +10948,17 @@
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 810 FFS Utilization Management</t>
+          <t>AHCCCS AMPM 820 FFS Prior Authorization</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>820</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>Eff. 06/17/2026</t>
+          <t>Eff. 07/16/2026</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -10841,73 +10970,73 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 820 FFS Prior Authorization</t>
+          <t>LCD Facet Joint Interventions (retired version)</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>L38803</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Eff. 07/16/2026</t>
+          <t>Rev. eff. 07/17/2025 (retired)</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>Code Research/Criteria and Coverage Policies - Articles</t>
+          <t>Code Research/.../Medicare - text identical to L38801</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>LCD Facet Joint Interventions (retired version)</t>
+          <t>Response to Comments: Facet Joint Interventions</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>L38803</t>
+          <t>A59795</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Rev. eff. 07/17/2025 (retired)</t>
+          <t>Orig. eff. 07/07/2024</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare - text identical to L38801</t>
+          <t>Code Research/.../Medicare</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>Response to Comments: Facet Joint Interventions</t>
+          <t>2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>A59795</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Orig. eff. 07/07/2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>Code Research/.../Medicare</t>
+          <t>Plan Guides</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>2026 UHC Care Provider Administrative Guide (Commercial, Exchange, MA chapters; Others ch. 1; Individual Exchange ch. 4)</t>
+          <t>UHC 2026 Individual Exchange plans - Quick reference guide</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
@@ -10929,29 +11058,29 @@
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>UHC 2026 Individual Exchange plans - Quick reference guide</t>
+          <t>UHC Community Plan AZ member handbook excerpt</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides</t>
+          <t>Plan Guides/AZ_Medicaid_Handbook.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>UHC Community Plan AZ member handbook excerpt</t>
+          <t>HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
@@ -10961,51 +11090,51 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Network update 09/18/2026</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides/AZ_Medicaid_Handbook.pdf</t>
+          <t>Plan Guides</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>HumanaMA.pdf / HumanaMS.pdf (Maricopa 85023 plan lists)</t>
+          <t>Humana Commercial PA list (stale)</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>399806ALL0224-A GCHM8R6EN</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Network update 09/18/2026</t>
+          <t>Eff. 07/01/2024, rev. 12/10/2024</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Plan Guides</t>
+          <t>PA Articles</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Humana Commercial PA list (stale)</t>
+          <t>UHC Complete PA requirements</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>399806ALL0224-A GCHM8R6EN</t>
+          <t>PCA-1-25-02057</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>Eff. 07/01/2024, rev. 12/10/2024</t>
+          <t>Eff. 1 Sep 2026</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -11017,17 +11146,17 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>UHC Complete PA requirements</t>
+          <t>UHC MA PA requirements - prior edition</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>PCA-1-25-02057</t>
+          <t>PCA-4-26-00416</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Sep 2026</t>
+          <t>Eff. 1 Aug 2026</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -11039,17 +11168,17 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>UHC MA PA requirements - prior edition</t>
+          <t>Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>PCA-4-26-00416</t>
+          <t>BH00798-2-24-QRG_01012025</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Aug 2026</t>
+          <t>Eff. 1 Jan 2026</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -11061,17 +11190,17 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Optum Behavioral Health - AZ Exchange PA list (not relevant to 64772)</t>
+          <t>Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>BH00798-2-24-QRG_01012025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Eff. 1 Jan 2026</t>
+          <t>Aug-Sep 2026</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -11083,7 +11212,7 @@
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Non-Arizona lists read and set aside: Oxford (NY/NJ/CT), NHP (FL), Mid-Atlantic (MD/DC/VA), UHC Community Plan FL, SCAN VillageHealth (CA)</t>
+          <t>Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -11093,32 +11222,10 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>Aug-Sep 2026</t>
+          <t>DOS 01/2026-06/2026</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>PA Articles</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Claims history: ALL Claims 2026-S1 - Master + monthly files; Job_Responsibilities_Inventory; code and timely-filing references</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>DOS 01/2026-06/2026</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Repository root / Specialty Claims 2026-S1</t>
         </is>
@@ -11135,7 +11242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D982"/>
+  <dimension ref="A1:D1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -32455,6 +32562,6415 @@
         </is>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" s="15" t="inlineStr">
+        <is>
+          <t>Round 5 - every row rewritten to PA / Referral / Coverage / Action format; unsourced content removed, 23 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B985" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C985" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D985" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B986" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C986" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D986" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B987" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C987" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion' for 'chronic or acute pain arising from conditions such as terminal cancer or lumbar degenerative arthritis'; payment 'may be made ... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no covered-dx table. 'NO auth required' = no pre-service gate; it does NOT mean the claim is safe - every 64772 claim is exposed to medical review.
+L38801 / A58403</t>
+        </is>
+      </c>
+      <c r="D987" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Noridian Auth Tool (your check).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Also in L38801: CT/fluoro guidance only; 1-2 levels per session, one region; repeat only after &gt;=50% relief for &gt;=6 months; routine MAC/general anesthesia not covered.
+Billing: dx M47.812-M47.817, M47.892-M47.897 or M48.12-M48.17 (</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B988" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C988" s="17" t="inlineStr">
+        <is>
+          <t>Railroad Medicare is administered nationally by Palmetto GBA but applies the LCD/LCA of the MAC in whose jurisdiction the service is rendered, so L38801 / A58403 still govern and the NCD 160.1 case-by-case result is unchanged.</t>
+        </is>
+      </c>
+      <c r="D988" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required.
+Coverage: same as Traditional Part B - Palmetto GBA applies Noridian L38801/A58403 for Arizona services.
+Action: same as Traditional Part B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B989" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C989" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64772 is not on the 2026 STANDARD Code List (1,909 rows, updated 09/01/2026). BUT on the same list facet RFA 64633/64635 DOES require AZ Blue PA (Gold Card eligible for cervical/lumbar). eviCore MSK/interventional pain is Medicare Advantage only (AZ Blue eviCore FAQ 01-2024) - commercial pain PA is requested from AZ Blue directly.
+Since 7/1/2026: a required PA that is not obtained = claim line not reimbursed and the member cannot be billed. AZ Blue also 'reserves the right to require prior authorization for ... newly released and changed items even though the lists have not yet been updated'.
+</t>
+        </is>
+      </c>
+      <c r="D989" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the 2026 Standard list (09/01/2026). Facet RFA 64633-64636 IS on it (AZ Blue PA).
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B990" s="17" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C990" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D990" s="17" t="inlineStr">
+        <is>
+          <t>CALL BCBS SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B991" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C991" s="17" t="inlineStr">
+        <is>
+          <t>Per AZ Blue code lists Introduction (09/01/2026): prefixes AOZ, AZI, AZK, IVR - BCBS South Carolina handles UM. Not checked with BCBS SC. CONFLICT TO RESOLVE: IVR is ALSO printed in the STANDARD Code List's applicable-prefix header - confirm which applies.</t>
+        </is>
+      </c>
+      <c r="D991" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by BCBS South Carolina (AZ Blue code-list Introduction). No BCBS SC list on file.
+Note: IVR also appears in the Standard list prefix header.
+Action: call BCBS SC 800-868-1032 before scheduling; record name, date and reference #.</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B992" s="17" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C992" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D992" s="17" t="inlineStr">
+        <is>
+          <t>CALL AHG</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B993" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C993" s="17" t="inlineStr">
+        <is>
+          <t>Per AZ Blue and TPA Jointly Administered Plans (as of 07/2026): the group may customize PA requirements; the TPA or its vendor runs UM and medical policy. Claims go to AZ Blue (EDI #53589). Not checked with AHG.</t>
+        </is>
+      </c>
+      <c r="D993" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue TPA document, 07/2026). No AHG list on file.
+Action: call AHG 800-847-7605 before scheduling; record reference #. Claims still go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B994" s="17" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C994" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D994" s="17" t="inlineStr">
+        <is>
+          <t>CALL AMERIBEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B995" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C995" s="17" t="inlineStr">
+        <is>
+          <t>UM handled by the TPA. The SPD governs the benefit; the TPA's criteria set governs medical necessity. Claims go to AZ Blue (EDI #53589). Round 2: the MCG reference previously in L ("MCG article GRG: SG-NS (ISC GRG) Neurosurgery or Procedure GRG") could not be found in any repository document and was removed - ask AmeriBen which criteria set it applies.</t>
+        </is>
+      </c>
+      <c r="D995" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue TPA document, 07/2026). No AmeriBen list on file.
+Action: call the AmeriBen line for the prefix (column J) before scheduling; record reference #. Claims go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B996" s="17" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C996" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D996" s="17" t="inlineStr">
+        <is>
+          <t>CALL TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B997" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C997" s="17" t="inlineStr">
+        <is>
+          <t>Not established.</t>
+        </is>
+      </c>
+      <c r="D997" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by the TPA on the ID card (AZ Blue code-list Introduction). No list on file.
+Action: call the number on the ID card before scheduling; record reference #.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B998" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C998" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. On the same list 64490-64495, 64625 and 64633-64636 require PA through eviCore. 64772 therefore routes to AZ Blue internal UM with no PA requirement; AZ Blue PA Lookup also returned 'not required'. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. Consider a voluntary pre-service organization determination given the MCG A-0218 method mismatch. L38801 (Analysis of Evidence): "An alternative method of denervation using an endoscopic approach (i.e., endoscopic dorsa</t>
+        </is>
+      </c>
+      <c r="D998" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the 2026 AZ Blue MA list (09/01/2026); AZ Blue PA Lookup also returned not required (your check). Facet codes 64490-64495, 64625, 64633-64636 ARE on it (eviCore).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: if the MBT is endoscopic, request a pre-service organization determination fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B999" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C999" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not listed in Optum's BCBS PA requirements. The list applies to providers with Optum DIRECT contracts; other providers follow the plan's own requirements. All out-of-network services require Optum PA.</t>
+        </is>
+      </c>
+      <c r="D999" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum BCBS list (Optum-direct providers) or the AZ Blue MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: check the ID card for the administrator; if endoscopic, request a pre-service organization determination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1000" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1000" s="17" t="inlineStr">
+        <is>
+          <t>This is a list of services that do NOT require authorisation. 64772 is absent, so absence means authorisation IS required. Inverted-list reasoning is conservative in the right direction but worth one confirming call. (The AZPC attachment is not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+      <c r="D1000" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED - AZPC Attachment A lists services that do NOT need auth; 64772 is not on it (eff. 8/21/2026; document not in the repository).
+Action: submit the auth on the AZ CONNECT portal before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1001" s="17" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="C1001" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1001" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1002" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1002" s="17" t="inlineStr">
+        <is>
+          <t>FULL delegation to Optum (OptumCare Network of AZ Provider Administrative Guide, OHNC-1-25-00910_06182026). Optum's BCBS PA list, now on file (Sept 2026), omits 64772. It applies to Optum direct-contracted providers; if Dr. Luke is not Optum-direct, use the AZ Blue MA requirements (row 7). MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D1002" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum BCBS list or the AZ Blue MA list. Plan is fully delegated to Optum (Optum AZ admin guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: any request goes through optumproportal.com; if endoscopic, request a pre-service decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1003" s="17" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="C1003" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1003" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1004" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1004" s="17" t="inlineStr">
+        <is>
+          <t>As above.</t>
+        </is>
+      </c>
+      <c r="D1004" s="17" t="inlineStr">
+        <is>
+          <t>Same as Blue Best Life Classic (row 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1005" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1005" s="17" t="inlineStr">
+        <is>
+          <t>Not on the 2026 FEP List or the FEP Blue Focus list. Confirmed twice - by AZ Blue PA Lookup and by the Availity auth tool. Related codes that ARE on the 2026 FEP List: 63185 / 63190 (laminectomy with rhizotomy) - AZ Blue PA, FEP Standard and Basic only.</t>
+        </is>
+      </c>
+      <c r="D1005" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the 2026 FEP list; AZ Blue PA Lookup and Availity returned not required (your checks).
+Related: 63185/63190 (laminectomy with rhizotomy) DO require PA on FEP Standard/Basic.
+Action: keep the lookup screenshots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1006" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1006" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 covers lesions produced by 'surgical cutting of the nerve (rhizolysis), chemical destruction of the nerve, or by creation of a radio-frequency lesion'. Payment 'may be made... when used in selected cases (concurred in by the Medicare Administrative Contractor's medical staff)'. No criteria list, no frequency limit, no conservative-care prerequisite, no covered-dx table. INHERITED RISK: if Medicare denies on medical review, the Medigap plan pays nothing. 'NO auth required' is true and still not the same as 'safe'.</t>
+        </is>
+      </c>
+      <c r="D1006" s="17" t="inlineStr">
+        <is>
+          <t>PA: none - Medigap has no prior authorization.
+Coverage: pays only after Medicare pays; if Medicare denies, Medigap pays nothing. See Medicare tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1007" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1007" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+      <c r="D1007" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - not on the Health Choice grid; portal submission returned not required (your check).
+Action: keep the portal result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1008" s="17" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C1008" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required. (The Health Choice PA grid is not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+      <c r="D1008" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - not on the Health Choice Pathway grid; portal submission returned not required (your check).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy.
+Action: keep the portal result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1009" s="17" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C1009" s="17" t="inlineStr">
+        <is>
+          <t>Not on the grid. An auth was filed on the portal and none was required. AHCCCS-wide: 64772 is on the FFY26 fee schedule at $578.79 non-facility AND facility, but AHCCCS states a listed code and rate is 'not an indication of coverage, nor a guarantee of payment' - coverage lives in the AMPM. (The Health Choice PA grids are not in this repository - not re-verified.)</t>
+        </is>
+      </c>
+      <c r="D1009" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - not on the Health Choice grid; portal submission returned not required (your check).
+Coverage: AHCCCS does not cover experimental services (AMPM 320-B); moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). 64772 is on the AHCCCS fee schedule ($578.79), which is not a coverage decision.
+Action: keep the portal result; do not bill 99152/99153 for the surgeon's own sedation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1010" s="17" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="C1010" s="17" t="inlineStr">
+        <is>
+          <t>VARIES BY HOME PLAN</t>
+        </is>
+      </c>
+      <c r="D1010" s="17" t="inlineStr">
+        <is>
+          <t>CALL HOME PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1011" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C1011" s="17" t="inlineStr">
+        <is>
+          <t>Not established - differs by home plan.</t>
+        </is>
+      </c>
+      <c r="D1011" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by the member's home Blue plan. Claim still files to AZ Blue.
+Action: use the BlueCard Medical Policy Router in Availity to reach the home plan's PA rules before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1012" s="17" t="inlineStr">
+        <is>
+          <t>I18</t>
+        </is>
+      </c>
+      <c r="C1012" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1012" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1013" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C1013" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list. 64490-64495 and 64633-64636 DO require AZ Blue PA for this group (site-of-service review: No). All non-emergency admissions (except maternity) need PA. Group is delegated for eviCore (imaging, lab, oncology, radiation - not MSK on commercial).</t>
+        </is>
+      </c>
+      <c r="D1013" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the 2026 State of AZ list (09/01/2026). 64490-64495 and 64633-64636 DO require AZ Blue PA for this group.
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1014" s="17" t="inlineStr">
+        <is>
+          <t>I19</t>
+        </is>
+      </c>
+      <c r="C1014" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1014" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1015" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C1015" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the list, and no facet codes are on it either.</t>
+        </is>
+      </c>
+      <c r="D1015" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the 2026 Teamsters list (09/01/2026).
+Coverage: no AZ Blue policy on file names 64772. MCG A-0218 (facet neurotomy) describes percutaneous RF only and requires 2 fluoroscopic blocks each &gt;=80% relief, &gt;=3 months pain, failed conservative care.
+Action: request a written predetermination from AZ Blue before scheduling (a missing required PA since 7/1/2026 = line not paid, member cannot be billed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1016" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C1016" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1016" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1017" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C1017" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1017" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1018" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C1018" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1018" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1019" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C1019" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1019" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1020" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C1020" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1020" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1021" s="17" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C1021" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1021" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1022" s="17" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C1022" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1022" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1023" s="17" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="C1023" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1023" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1024" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1024" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1024" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1025" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C1025" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1025" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1026" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1026" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1026" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1027" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C1027" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1027" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1028" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C1028" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1028" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1029" s="17" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C1029" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1029" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1030" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1030" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1030" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1031" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C1031" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1031" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1032" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C1032" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1032" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1033" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C1033" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1033" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1034" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C1034" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1034" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1035" s="17" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C1035" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1035" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1036" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1036" s="17" t="inlineStr">
+        <is>
+          <t>Referral NOT required - AARP MA from UHC AZ-0013 (H5253-035) is exempt from the 2026 referral rule. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days bef</t>
+        </is>
+      </c>
+      <c r="D1036" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (H5253-035 is exempt).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file;</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1037" s="17" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C1037" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1037" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1038" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C1038" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1038" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1039" s="17" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C1039" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1039" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1040" s="17" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C1040" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1040" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1041" s="17" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C1041" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1041" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1042" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1042" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1042" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1043" s="17" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C1043" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1043" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1044" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C1044" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1044" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1045" s="17" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C1045" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1045" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1046" s="17" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C1046" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1046" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1047" s="17" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C1047" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1047" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1048" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1048" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1048" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1049" s="17" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C1049" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1049" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1050" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C1050" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1050" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1051" s="17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C1051" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1051" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1052" s="17" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C1052" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1052" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1053" s="17" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="C1053" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1053" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1054" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1054" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1054" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1055" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C1055" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1055" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1056" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C1056" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1056" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1057" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C1057" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1057" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1058" s="17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C1058" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1058" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1059" s="17" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="C1059" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1059" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1060" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1060" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1060" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1061" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C1061" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1061" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1062" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C1062" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1062" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1063" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C1063" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1063" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1064" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C1064" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1064" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1065" s="17" t="inlineStr">
+        <is>
+          <t>I9</t>
+        </is>
+      </c>
+      <c r="C1065" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1065" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1066" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1066" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1066" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1067" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C1067" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1067" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1068" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1068" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1068" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1069" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C1069" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1069" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1070" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C1070" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1070" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1071" s="17" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="C1071" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1071" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1072" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1072" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1072" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1073" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C1073" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1073" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1074" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1074" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1074" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1075" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C1075" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1075" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1076" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C1076" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1076" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1077" s="17" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="C1077" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1077" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1078" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1078" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new </t>
+        </is>
+      </c>
+      <c r="D1078" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1079" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C1079" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1079" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1080" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1080" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1080" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1081" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C1081" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1081" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1082" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C1082" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1082" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1083" s="17" t="inlineStr">
+        <is>
+          <t>I12</t>
+        </is>
+      </c>
+      <c r="C1083" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1083" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1084" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1084" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new </t>
+        </is>
+      </c>
+      <c r="D1084" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1085" s="17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C1085" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1085" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1086" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C1086" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1086" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1087" s="17" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="C1087" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1087" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1088" s="17" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C1088" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1088" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1089" s="17" t="inlineStr">
+        <is>
+          <t>I13</t>
+        </is>
+      </c>
+      <c r="C1089" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1089" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1090" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1090" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPO - no PCP referral. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established. PA LIST NOTE: Optum's own list applies only to providers with an Optum DIRECT contract; the UHC/Optum QRG (PCA-4-26-00582) points everyone else to the UHC MA list (PCA-4-26-00416) - 64772 is absent from both. Submit any PA &gt;=7 days before the date of service. Optum "new technology" rule: services involving new </t>
+        </is>
+      </c>
+      <c r="D1090" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1091" s="17" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C1091" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1091" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1092" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C1092" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1092" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1093" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C1093" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1093" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1094" s="17" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C1094" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1094" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1095" s="17" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="C1095" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1095" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1096" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1096" s="17" t="inlineStr">
+        <is>
+          <t>PCP REFERRAL REQUIRED (UHC MA HMO/HMO-POS delegated to Optum, from 1 Jan 2026): the PCP must submit the referral to Optum BEFORE the specialist visit (the Optum list names ORTHOPAEDIST and NEUROSURGEON as specialties that need a referral; orthopaedic urgent care is exempt); specialists cannot submit it; a missing referral = denied claim, provider liability. The Optum list applies to providers with Optum DIRECT contracts; all out-of-network services need Optum PA. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance i</t>
+        </is>
+      </c>
+      <c r="D1096" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1097" s="17" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C1097" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; MMP070.12 does not list 64772</t>
+        </is>
+      </c>
+      <c r="D1097" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1098" s="17" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C1098" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section)</t>
+        </is>
+      </c>
+      <c r="D1098" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1099" s="17" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C1099" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1099" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1100" s="17" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="C1100" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026</t>
+        </is>
+      </c>
+      <c r="D1100" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1101" s="17" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="C1101" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1101" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1102" s="17" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C1102" s="17" t="inlineStr">
+        <is>
+          <t>See BCBS tab rows 10-11. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D1102" s="17" t="inlineStr">
+        <is>
+          <t>Same as BCBS tab rows 10-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1103" s="17" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="C1103" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1103" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1104" s="17" t="inlineStr">
+        <is>
+          <t>I16</t>
+        </is>
+      </c>
+      <c r="C1104" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1104" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1105" s="17" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C1105" s="17" t="inlineStr">
+        <is>
+          <t>See BCBS tab rows 10-11. MA coverage hierarchy (42 CFR 422.101(b)): NCD 160.1 -&gt; Noridian L38801 / A58403 -&gt; plan internal criteria only where CMS guidance is not fully established.</t>
+        </is>
+      </c>
+      <c r="D1105" s="17" t="inlineStr">
+        <is>
+          <t>Same as BCBS tab rows 10-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1106" s="17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C1106" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1106" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1107" s="17" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="C1107" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1107" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1108" s="17" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="C1108" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+        </is>
+      </c>
+      <c r="D1108" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1109" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C1109" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not cov</t>
+        </is>
+      </c>
+      <c r="D1109" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1110" s="17" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C1110" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+      <c r="D1110" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1111" s="17" t="inlineStr">
+        <is>
+          <t>I18</t>
+        </is>
+      </c>
+      <c r="C1111" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1111" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1112" s="17" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C1112" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+        </is>
+      </c>
+      <c r="D1112" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1113" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C1113" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not cov</t>
+        </is>
+      </c>
+      <c r="D1113" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1114" s="17" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C1114" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+      <c r="D1114" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1115" s="17" t="inlineStr">
+        <is>
+          <t>I19</t>
+        </is>
+      </c>
+      <c r="C1115" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1115" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1116" s="17" t="inlineStr">
+        <is>
+          <t>J19</t>
+        </is>
+      </c>
+      <c r="C1116" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+        </is>
+      </c>
+      <c r="D1116" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1117" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C1117" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not cov</t>
+        </is>
+      </c>
+      <c r="D1117" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1118" s="17" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="C1118" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+      <c r="D1118" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1119" s="17" t="inlineStr">
+        <is>
+          <t>I20</t>
+        </is>
+      </c>
+      <c r="C1119" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1119" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1120" s="17" t="inlineStr">
+        <is>
+          <t>J20</t>
+        </is>
+      </c>
+      <c r="C1120" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+        </is>
+      </c>
+      <c r="D1120" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1121" s="17" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C1121" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not cov</t>
+        </is>
+      </c>
+      <c r="D1121" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1122" s="17" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="C1122" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+      <c r="D1122" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1123" s="17" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="C1123" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1123" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1124" s="17" t="inlineStr">
+        <is>
+          <t>J21</t>
+        </is>
+      </c>
+      <c r="C1124" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 - ask for the Optum SCAN list</t>
+        </is>
+      </c>
+      <c r="D1124" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1125" s="17" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="C1125" s="17" t="inlineStr">
+        <is>
+          <t>SCAN applies NCD/LCD first and its internal criteria (MCG/InterQual, other MAO policies) only when CMS guidance is not fully established (BCG0100). CCP0207: 64772 is on the CMS ASC Covered Procedures List, so SCAN expects the ASC; HOPD needs documented clinical justification. If billed as 64999, CRP0420 requires full records and a beneficiary notice when coverage is uncertain. Optum's own prior-auth pages (business.optum.com) could not be reached from this environment - confirm with Optum. BCG0111: experimental/investigational items outside a CMS-approved trial are "Deny if requested - Not cov</t>
+        </is>
+      </c>
+      <c r="D1125" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1126" s="17" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C1126" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; the SCAN policies are general and name no procedure codes</t>
+        </is>
+      </c>
+      <c r="D1126" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1127" s="17" t="inlineStr">
+        <is>
+          <t>I22</t>
+        </is>
+      </c>
+      <c r="C1127" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1127" s="17" t="inlineStr">
+        <is>
+          <t>CALL PLAN ON CARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1128" s="17" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="C1128" s="17" t="inlineStr">
+        <is>
+          <t>Optum publishes two delegation tiers. FULL delegation means Optum decides PA. CARE MANAGEMENT delegation does not - authority stays with the plan.</t>
+        </is>
+      </c>
+      <c r="D1128" s="17" t="inlineStr">
+        <is>
+          <t>PA: Optum has care-management delegation only; PA stays with the plan on the ID card (Optum AZ admin guide).
+Action: use that plan's row in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1129" s="17" t="inlineStr">
+        <is>
+          <t>I23</t>
+        </is>
+      </c>
+      <c r="C1129" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1129" s="17" t="inlineStr">
+        <is>
+          <t>CALL IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1130" s="17" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="C1130" s="17" t="inlineStr">
+        <is>
+          <t>Per UHC: 'if you are a network provider who is contracted directly with a delegated medical group/IPA, then you must follow the delegate's protocols' - delegates use their own systems and forms.</t>
+        </is>
+      </c>
+      <c r="D1130" s="17" t="inlineStr">
+        <is>
+          <t>PA: the delegated IPA's own rules apply (UHC MA PA list: providers contracted with a delegated IPA must follow its protocols). No IPA list on file.
+Action: call the IPA before scheduling; record reference #.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1131" s="17" t="inlineStr">
+        <is>
+          <t>I24</t>
+        </is>
+      </c>
+      <c r="C1131" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1131" s="17" t="inlineStr">
+        <is>
+          <t>CALL BANNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1132" s="17" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="C1132" s="17" t="inlineStr">
+        <is>
+          <t>Routing guard. Shares contracts and PBPs with the Optum rows but different group numbers - H0609-026 group 91038 is Optum, 91037 is Banner. Banner group list confirmed in the UHC MA PA requirements (PCA-4-26-00416, eff. 1 Sep 2026). The Banner QRG is not in this repository.</t>
+        </is>
+      </c>
+      <c r="D1132" s="17" t="inlineStr">
+        <is>
+          <t>PA: these group numbers are delegated to Banner (UHC MA PA list, eff. 9/1/2026). Banner's list is not on file.
+Action: call Banner (number on the ID card) before scheduling; do not use optumproportal.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1133" s="17" t="inlineStr">
+        <is>
+          <t>I25</t>
+        </is>
+      </c>
+      <c r="C1133" s="17" t="inlineStr">
+        <is>
+          <t>NO - treat as Optum</t>
+        </is>
+      </c>
+      <c r="D1133" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1134" s="17" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="C1134" s="17" t="inlineStr">
+        <is>
+          <t>Group 96001 (H0609-027-000) IS listed as delegated to OptumCare in both the UHC MA PA requirements (eff. 1 Sep 2026) and the UHC QRG PCA-4-26-00582. It is still missing from the Optum administrative guide's plan table (H0609 Plan 2 = 00329/00330/00340). Two UHC sources outweigh the omission - route to Optum; confirm the plan name with the Optum rep.</t>
+        </is>
+      </c>
+      <c r="D1134" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - group 96001 (H0609-027) is listed as Optum-delegated in the UHC MA PA list and QRG PCA-4-26-00582; 64772 is not on the Optum or UHC MA lists.
+Action: treat as Optum (rows above).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1135" s="17" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="C1135" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1135" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1136" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1136" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1136" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1137" s="17" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C1137" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1137" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1138" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1138" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1138" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1139" s="17" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C1139" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1139" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1140" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1140" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1141" s="17" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C1141" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1141" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1142" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1142" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1142" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1143" s="17" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C1143" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1143" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1144" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1144" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1144" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1145" s="17" t="inlineStr">
+        <is>
+          <t>I9</t>
+        </is>
+      </c>
+      <c r="C1145" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1145" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1146" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1146" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1146" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1147" s="17" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="C1147" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1147" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1148" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1148" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION: the MMP070.12 wording 'Medicare does not have a National Coverage Determination... LCDs/LCAs exist and compliance... is required' is the SACROILIAC-joint-denervation section, not a statement about 64772. 64772 is not in MMP070.12. For facet denervation UHC MA follows NCD 160.1 and Noridian L38801 / A58403. Where MMP070.12 finds no LCD for a technique it sends the reviewer to the commercial policy 'Ablative Treatment for Spinal Pain' (2026T0107II), which lists endoscopic RFA / endoscopic rhizotomy as UNPROVEN - expect that position if an endoscopic MBT is reviewed. Consider a volunt</t>
+        </is>
+      </c>
+      <c r="D1148" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, call the Erickson PA number on the ID car</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1149" s="17" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="C1149" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1149" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1150" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1150" s="17" t="inlineStr">
+        <is>
+          <t>MANUAL'S OWN CAVEAT, verbatim: 'The presence or absence of a procedure or service on the list does not define whether coverage or benefits exist for that procedure or service.' So absence from the PA list settles nothing on this book. All out-of-network services are denied unless prior authorisation was obtained or the service was emergent. PA is always required when the rendering provider is non-contracted. The Dual Complete provider manual (2026) is the source of these rules but is not a coverage policy. Members must coordinate with their PCP before seeing a specialist; non-contracted provid</t>
+        </is>
+      </c>
+      <c r="D1150" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Referral: members must coordinate with their PCP; non-contracted providers need a referral form and PA (Dual Complete manual).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's </t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1151" s="17" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="C1151" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1151" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1152" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1152" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is</t>
+        </is>
+      </c>
+      <c r="D1152" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: REQUIRED - electronic PCP referral before the visit.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a p</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1153" s="17" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="C1153" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1153" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1154" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1154" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is</t>
+        </is>
+      </c>
+      <c r="D1154" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: NOT required.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1155" s="17" t="inlineStr">
+        <is>
+          <t>I12</t>
+        </is>
+      </c>
+      <c r="C1155" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1155" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1156" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1156" s="17" t="inlineStr">
+        <is>
+          <t>64772 is absent from all four. But related techniques are AFFIRMATIVELY unproven and not medically necessary: pulsed RFA, endoscopic RFA / endoscopic rhizotomy, cryoablation, cooled RFA, chemical ablation, laser ablation. 'Ablation for treating sacroiliac pain is unproven and not medically necessary' - so 64625 is not covered commercially. Facet diagnostic block covered only when: facet loading pain on exam; no significant improvement (pain still &gt;=3/10) after &gt;=4 weeks conservative care; imaging excludes other causes; segment not fused; AND an RFA is being considered. Absence from a policy is</t>
+        </is>
+      </c>
+      <c r="D1156" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Individual Exchange list (eff. 9/1/2026). 64999 WOULD need PA. 64490, 64493, 64633, 64635 need PA + site-of-service review.
+Referral: REQUIRED in Arizona - UHC will not accept a PA without a referral on file. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1157" s="17" t="inlineStr">
+        <is>
+          <t>I13</t>
+        </is>
+      </c>
+      <c r="C1157" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1157" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1158" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1158" s="17" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for an</t>
+        </is>
+      </c>
+      <c r="D1158" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1159" s="17" t="inlineStr">
+        <is>
+          <t>I19</t>
+        </is>
+      </c>
+      <c r="C1159" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1159" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1160" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C1160" s="17" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for an</t>
+        </is>
+      </c>
+      <c r="D1160" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1161" s="17" t="inlineStr">
+        <is>
+          <t>I20</t>
+        </is>
+      </c>
+      <c r="C1161" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on list</t>
+        </is>
+      </c>
+      <c r="D1161" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1162" s="17" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C1162" s="17" t="inlineStr">
+        <is>
+          <t>64772 'TRANSECTION OR AVULSION OF OTHER SPINAL NERVE, EXTRADURAL' at $578.79 non-facility AND facility (rate parity); lower tier $405.15. 64999 is 'BR - by report'. COVERAGE CAVEAT, verbatim: 'the appearance on this website of a code and rate is not an indication of coverage, nor a guarantee of payment.' Coverage is established in the AMPM, not the fee schedule, and AHCCCS contractor plans apply their own prior authorization. No AMPM section names 64772, BUT all three UHC Community Plan AZ PA lists state "Experimental and investigational services are not covered benefits" and require PA for an</t>
+        </is>
+      </c>
+      <c r="D1162" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 877-842-3210.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1163" s="17" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="C1163" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1163" s="17" t="inlineStr">
+        <is>
+          <t>CALL TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1164" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1164" s="17" t="inlineStr">
+        <is>
+          <t>For self-funded and level-funded groups the SPD governs the benefit and the TPA's criteria set governs medical necessity, so the answer varies BY GROUP and cannot be resolved at network level. Empire Plan has an Arizona concentration. Surest now has its own row (own PA list).</t>
+        </is>
+      </c>
+      <c r="D1164" s="17" t="inlineStr">
+        <is>
+          <t>PA: set by each group's plan document and TPA supplement - no list on file.
+Action: check the member's ID card / portal (UMR: umr.com) and call before scheduling; record reference #.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1165" s="17" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="C1165" s="17" t="inlineStr">
+        <is>
+          <t>N/A - NOT AN AZ PRODUCT</t>
+        </is>
+      </c>
+      <c r="D1165" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1166" s="17" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C1166" s="17" t="inlineStr">
+        <is>
+          <t>CORRECTION (round 2): this row was added in round 1 because the West list footer names "UnitedHealthcare of Arizona, Inc." - but that footer is the standard multi-entity footer that also appears on the national Commercial list, so it is not evidence. The 2026 UHC Administrative Guide (Others, ch. 1) defines UHC West as UnitedHealthcare of California (CA), and states PacifiCare of Arizona is now UnitedHealthcare Benefits of Texas. Arizona commercial members use the national Commercial rows above. Kept only as a routing guard: if a card shows a West/California product, verify on the portal. 6477</t>
+        </is>
+      </c>
+      <c r="D1166" s="17" t="inlineStr">
+        <is>
+          <t>Not used for Arizona members - UHC West is UnitedHealthcare of California (2026 UHC Administrative Guide).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1167" s="17" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C1167" s="17" t="inlineStr">
+        <is>
+          <t>No PA. The supplement follows Medicare's determination: if Medicare denies 64772 on medical review (see the Medicare tab, incl. the L38801 endoscopic-evidence statement), the supplement pays nothing. Medicare Select plans may require use of network hospitals for Part A services.</t>
+        </is>
+      </c>
+      <c r="D1167" s="17" t="inlineStr">
+        <is>
+          <t>PA: none (2026 UHC Administrative Guide).
+Coverage: pays only after Medicare pays - see Medicare tab.
+Claims: payer ID 36273.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1168" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C1168" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the UHC Complete list. Members have no non-emergent out-of-network coverage and no coverage outside the service area. Gated plan: electronic PCP referral required before the specialist visit (2026 UHC Administrative Guide). If the procedure is billed as 64999, PA is required. Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+        </is>
+      </c>
+      <c r="D1168" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Complete list (eff. 9/1/2026). 64999 WOULD need PA.
+Referral: REQUIRED - electronic PCP referral. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1169" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C1169" s="17" t="inlineStr">
+        <is>
+          <t>64772 is not on the Surest list and is not a Surest Flex "flexible coverage activation" service (activation must be done &gt;=3 business days before the listed services). Coverage policy: commercial Ablative Treatment for Spinal Pain (2026T0107II) - endoscopic RFA/rhizotomy unproven.</t>
+        </is>
+      </c>
+      <c r="D1169" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Surest list (eff. 9/1/2026) and is not a Surest Flex activation service.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1170" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1170" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="D1170" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1171" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C1171" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="D1171" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1172" s="17" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C1172" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D1172" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1173" s="17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C1173" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="D1173" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed in either</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1174" s="17" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="C1174" s="17" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+      <c r="D1174" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1175" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1175" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="D1175" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1176" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C1176" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="D1176" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1177" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C1177" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D1177" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1178" s="17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C1178" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="D1178" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed in either</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1179" s="17" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="C1179" s="17" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+      <c r="D1179" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1180" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C1180" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service (Individual Exchange follows the commercial policies)</t>
+        </is>
+      </c>
+      <c r="D1180" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1181" s="17" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="C1181" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="D1181" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1182" s="17" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C1182" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D1182" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1183" s="17" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C1183" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="D1183" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed in either</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1184" s="17" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
+      <c r="C1184" s="17" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification.</t>
+        </is>
+      </c>
+      <c r="D1184" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1185" s="17" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C1185" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="D1185" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1186" s="17" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C1186" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="D1186" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1187" s="17" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="C1187" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D1187" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1188" s="17" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C1188" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="D1188" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed in either</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1189" s="17" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
+      <c r="C1189" s="17" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+      <c r="D1189" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1190" s="17" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C1190" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and MBB; Office-Based Procedures - Site of Service; Outpatient Surgical - Site of Service</t>
+        </is>
+      </c>
+      <c r="D1190" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1191" s="17" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="C1191" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW; MP.12.22 (not in repo); MP.11.27 (not in repo)</t>
+        </is>
+      </c>
+      <c r="D1191" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II; 2026T0004WW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1192" s="17" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="C1192" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026; 1 Jul 2026; 1 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D1192" s="17" t="inlineStr">
+        <is>
+          <t>1 Feb 2026; 10 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1193" s="17" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="C1193" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent from all four</t>
+        </is>
+      </c>
+      <c r="D1193" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed in either</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1194" s="17" t="inlineStr">
+        <is>
+          <t>V18</t>
+        </is>
+      </c>
+      <c r="C1194" s="17" t="inlineStr">
+        <is>
+          <t>Header note on 2026T0107II: 'Conventional (Thermal) Radiofrequency Ablation requires site of service review.' MP.12.22 covers 64633/64635 but not 64772; it allows ASC only for named exceptions and EXPRESSLY excludes 'surgeon-preferred or proprietary instruments' as justification. NOTE: MP.12.22 and MP.11.27 are not in this repository - their numbers and dates were not re-verified.</t>
+        </is>
+      </c>
+      <c r="D1194" s="17" t="inlineStr">
+        <is>
+          <t>2026T0107II: RFA requires site-of-service review - plan for the ASC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1195" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1195" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1195" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1196" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C1196" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1196" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1197" s="17" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C1197" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1197" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1198" s="17" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C1198" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1198" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1199" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C1199" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1199" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1200" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C1200" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1200" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1201" s="17" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C1201" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1201" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1202" s="17" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C1202" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1202" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1203" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C1203" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1203" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1204" s="17" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C1204" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1204" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1205" s="17" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C1205" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1205" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1206" s="17" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C1206" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1206" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1207" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C1207" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1207" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1208" s="17" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C1208" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1208" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1209" s="17" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C1209" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1209" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1210" s="17" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C1210" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1210" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1211" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C1211" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1211" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1212" s="17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C1212" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1212" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1213" s="17" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C1213" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1213" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1214" s="17" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C1214" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1214" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1215" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C1215" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1215" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1216" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C1216" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1216" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1217" s="17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C1217" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1217" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1218" s="17" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C1218" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1218" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1219" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C1219" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403) (Medicare benefit); AHCCCS AMPM 320-B for the Medicaid wrap (experimental services not covered)</t>
+        </is>
+      </c>
+      <c r="D1219" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1220" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C1220" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; AMPM 320-B</t>
+        </is>
+      </c>
+      <c r="D1220" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1221" s="17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C1221" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; 320-B eff. 10/01/2022</t>
+        </is>
+      </c>
+      <c r="D1221" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1222" s="17" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C1222" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1222" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1223" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1223" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); UHC MA Pain Management MMP070.12 (no facet or endoscopic section); where Medicare is silent UHC may apply commercial Ablative Treatment for Spinal Pain</t>
+        </is>
+      </c>
+      <c r="D1223" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1224" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C1224" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; MMP070.12; 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1224" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1225" s="17" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C1225" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026; MMP070.12 eff. 09/01/2026; 2026T0107II eff. 02/01/2026</t>
+        </is>
+      </c>
+      <c r="D1225" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1226" s="17" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C1226" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636; not in MMP070.12 or 2026T0107II</t>
+        </is>
+      </c>
+      <c r="D1226" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1227" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C1227" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1227" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1228" s="17" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="C1228" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1228" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1229" s="17" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="C1229" s="17" t="inlineStr">
+        <is>
+          <t>NCD longstanding; L38801 rev. eff. 04/16/2026; A58403 rev. eff. 09/17/2026</t>
+        </is>
+      </c>
+      <c r="D1229" s="17" t="inlineStr">
+        <is>
+          <t>L38801 rev. 04/16/2026; A58403 rev. 09/17/2026; MMP070.12 eff. 9/1/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1230" s="17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C1230" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 is not named. NCD 160.1 is narrative (it describes "surgical cutting of the nerve (rhizolysis)" but has no code list); L38801 / A58403 list only 64490-64495 and 64633-64636</t>
+        </is>
+      </c>
+      <c r="D1230" s="17" t="inlineStr">
+        <is>
+          <t>NO - 64772 not listed (L38801/A58403 list 64490-64495, 64633-64636 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1231" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1231" s="17" t="inlineStr">
+        <is>
+          <t>Availity and Cohere both returned NO AUTHORIZATION REQUIRED for 64772. Because the Humana policy excludes endoscopic rhizotomy, request an Advance Coverage Determination (ACD): phone 800-523-0023, fax 800-266-3022, or mail Humana Correspondence, P.O. Box 14601, Lexington, KY 40512-4601</t>
+        </is>
+      </c>
+      <c r="D1231" s="17" t="inlineStr">
+        <is>
+          <t>Availity / Cohere - both returned NOT required (your check). ACD: 800-523-0023, fax 800-266-3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1232" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1232" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORRECTION - a Humana policy DOES address this procedure. HUM-1168-008 Coverage Limitations: 'Endoscopic radiofrequency ablation/rhizotomy for any indication including, but not limited to, the facet joint/nerve' will not be considered medically reasonable and necessary (Hayes brief, 10 Jun 2024). It also excludes cooled RF, pulsed RF, laser, cryoneurolysis, SI-joint (64625) and DRG ablation 'regardless of the type of neuroablative technique used'. For facet denervation 64633-64636 it defers to NCD 160.1 and, in Arizona, Noridian L38801 / A58403.
+PA list (eff. 1 Jul 2026, rev. 1 Sep 2026): the </t>
+        </is>
+      </c>
+      <c r="D1232" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Humana MA/D-SNP list (eff. 7/1/2026, rev. 9/1/2026); Availity and Cohere returned not required (your check). 64999 and facet codes 64490-64495, 64633-64636 DO need PA through Cohere.
+Coverage: HUM-1168-008 - endoscopic RF ablation/rhizotomy for any indication, including the facet nerve, is NOT reasonable and necessary. Conventional facet RFA follows L38801/A58403.
+Action: request an Advance Coverage Determination before scheduling (800-523-0023 / fax 800-266-3022 / PO Box 14601, Lexington KY 40512-4601). Without it, a post-payment denial is likely and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1233" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1233" s="17" t="inlineStr">
+        <is>
+          <t>No PA. Humana Medigap pays after Medicare's decision - if Medicare denies on review, Humana pays nothing. NAME CHECK: HumanaMS.pdf (Maricopa 85023 plan list) names the plans "Humana Plan F", "Humana Plan N" etc.; the labels "VALUE" / "ACHIEVE" do not appear in any repository document - confirm against the member card. (The Humana MA/D-SNP PA list 790807ALL0725-C states it "does not apply to policy holders of a Humana Medicare Supplement plan".)</t>
+        </is>
+      </c>
+      <c r="D1233" s="17" t="inlineStr">
+        <is>
+          <t>PA: none - Medigap has no prior authorization.
+Coverage: pays only after Medicare pays - see Medicare tab.
+Note: HumanaMS.pdf names the plans "Humana Plan F / Plan N"; "VALUE"/"ACHIEVE" is not in any document on file - check the ID card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1234" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1234" s="17" t="inlineStr">
+        <is>
+          <t>As row 9 (name "ACHIEVE" not found in HumanaMS.pdf - confirm against the member card).</t>
+        </is>
+      </c>
+      <c r="D1234" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1235" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1235" s="17" t="inlineStr">
+        <is>
+          <t>As row 9. HumanaMS.pdf lists A, B, C, F, G, F-HD, G-HD, K, L and N for Maricopa 85023.</t>
+        </is>
+      </c>
+      <c r="D1235" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1236" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1236" s="17" t="inlineStr">
+        <is>
+          <t>NEW ROW (round 2) - this book was missing. AMPM 820 U: FFS surgeons "shall obtain a separate and distinct AHCCCS PA number ... prior to providing elective/non-emergency surgeries"; AMPM 820 T: the ASC must obtain its own PA for all outpatient surgeries; L.3.b: hospital outpatient surgery needs authorization. Assistant surgeons and anaesthesiologists do not need a separate PA. No PA needed when the provider/facility is IHS or a 638 tribal facility, for emergencies, when AHCCCS is not primary, or for retro-eligibility. A PA "does not guarantee payment". Standard decision 14 days, expedited 72 ho</t>
+        </is>
+      </c>
+      <c r="D1236" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED - elective outpatient surgery needs a surgeon PA AND a separate ASC/hospital PA (AMPM 820). Not needed if IHS/638 facility, emergency, or AHCCCS not primary.
+Coverage: experimental services not covered (AMPM 320-B); moderate sedation by the performing physician not covered (Exh. 300-1).
+Action: submit both PAs on AHCCCS Online (fax 602-256-6591; phone 602-417-4400) before scheduling; put member name/DOB/ID on every page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1237" s="17" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C1237" s="17" t="inlineStr">
+        <is>
+          <t>3. Coding: AMA CPT Knowledge Base entries (Nov 2019) point endoscopic medial branch rhizotomy to 64999 (unlisted). Industry sources read CMS's Jan 2026 MUE increase for 64772 (2 -&gt; 6 units) as acceptance of the code for MBT, but no CMS or AMA document on file says so. The operative note must describe an extradural transection or avulsion of a named spinal nerve (the medial branch). 64999 is non-covered on Medicare for non-thermal facet denervation (A58403), needs PA on Humana and cannot be paid in an ASC.</t>
+        </is>
+      </c>
+      <c r="D1237" s="17" t="inlineStr">
+        <is>
+          <t>3. Coding: no document on file addresses whether an endoscopic MBT should be coded 64772 or 64999 (unlisted). Have the coding team confirm from the operative note before the first claim. If 64999 is used: Humana, UHC Exchange and UHC Complete require PA, and an ASC cannot be paid for 64999 under Medicare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1238" s="17" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="C1238" s="17" t="inlineStr">
+        <is>
+          <t>- Optum SCAN PA list and Optum AZ web pages (business.optum.com is blocked from this environment) - confirm SCAN rows with Optum 877-370-2845.</t>
+        </is>
+      </c>
+      <c r="D1238" s="17" t="inlineStr">
+        <is>
+          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1239" s="17" t="inlineStr">
+        <is>
+          <t>A46</t>
+        </is>
+      </c>
+      <c r="C1239" s="17" t="inlineStr">
+        <is>
+          <t>- AMA CPT Knowledge Base answers on endoscopic rhizotomy (Nov 2019) are paywalled - pull the full text (AMA CPT Network) before finalizing the code.</t>
+        </is>
+      </c>
+      <c r="D1239" s="17" t="inlineStr">
+        <is>
+          <t>- Code selection (64772 vs 64999) for endoscopic MBT: confirm with the coding team from the operative note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="17" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B1240" s="17" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+      <c r="C1240" s="17" t="inlineStr">
+        <is>
+          <t>AMA CPT Knowledge Base - endoscopic rhizotomy Q&amp;As (64999 / 64772)</t>
+        </is>
+      </c>
+      <c r="D1240" s="17" t="inlineStr">
+        <is>
+          <t>ROW REMOVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1241" s="17" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C1241" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1241" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1242" s="17" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="C1242" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1242" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1243" s="17" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C1243" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1243" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1244" s="17" t="inlineStr">
+        <is>
+          <t>O4</t>
+        </is>
+      </c>
+      <c r="C1244" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1244" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1245" s="17" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C1245" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1245" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1246" s="17" t="inlineStr">
+        <is>
+          <t>O5</t>
+        </is>
+      </c>
+      <c r="C1246" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1246" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1247" s="17" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="C1247" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1247" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1248" s="17" t="inlineStr">
+        <is>
+          <t>O6</t>
+        </is>
+      </c>
+      <c r="C1248" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1248" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1249" s="17" t="inlineStr">
+        <is>
+          <t>N23</t>
+        </is>
+      </c>
+      <c r="C1249" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1249" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1250" s="17" t="inlineStr">
+        <is>
+          <t>O23</t>
+        </is>
+      </c>
+      <c r="C1250" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1250" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1251" s="17" t="inlineStr">
+        <is>
+          <t>N24</t>
+        </is>
+      </c>
+      <c r="C1251" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1251" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1252" s="17" t="inlineStr">
+        <is>
+          <t>O24</t>
+        </is>
+      </c>
+      <c r="C1252" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1252" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1253" s="17" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="C1253" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1253" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1254" s="17" t="inlineStr">
+        <is>
+          <t>O14</t>
+        </is>
+      </c>
+      <c r="C1254" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1254" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1255" s="17" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C1255" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1255" s="17" t="inlineStr">
+        <is>
+          <t>No policy on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1256" s="17" t="inlineStr">
+        <is>
+          <t>O25</t>
+        </is>
+      </c>
+      <c r="C1256" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1256" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1257" s="17" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C1257" s="17" t="inlineStr">
+        <is>
+          <t>Varies by home plan</t>
+        </is>
+      </c>
+      <c r="D1257" s="17" t="inlineStr">
+        <is>
+          <t>Per home plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1258" s="17" t="inlineStr">
+        <is>
+          <t>N17</t>
+        </is>
+      </c>
+      <c r="C1258" s="17" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="D1258" s="17" t="inlineStr">
+        <is>
+          <t>Home plan decides - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1259" s="17" t="inlineStr">
+        <is>
+          <t>O17</t>
+        </is>
+      </c>
+      <c r="C1259" s="17" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="D1259" s="17" t="inlineStr">
+        <is>
+          <t>Home plan decides - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1260" s="17" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C1260" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1260" s="17" t="inlineStr">
+        <is>
+          <t>CALL (TPA / BCBS SC / home plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1261" s="17" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="C1261" s="17" t="inlineStr">
+        <is>
+          <t>LIKELY NO - CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1261" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1262" s="17" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="C1262" s="17" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="D1262" s="17" t="inlineStr">
+        <is>
+          <t>CALL BANNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1263" s="17" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="C1263" s="17" t="inlineStr">
+        <is>
+          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository - their rows were not re-verified.</t>
+        </is>
+      </c>
+      <c r="D1263" s="17" t="inlineStr">
+        <is>
+          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository; those rows rely on your portal checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1264" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1264" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1264" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1265" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1265" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1265" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1266" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1266" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1266" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1267" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1267" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1267" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1268" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1268" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1268" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1269" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1269" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1269" s="17" t="inlineStr">
+        <is>
+          <t>Same as row 2.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -602,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -651,6 +652,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -900,7 +902,7 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); commercial Ablative policy (endoscopic = unproven) may fill gaps. HMO/HMO-POS (incl. D-SNP/C-SNP HMO): PCP referral required.</t>
+          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); UHC commercial policy calls endoscopic rhizotomy unproven.</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
@@ -932,12 +934,12 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>HMO/HMO-POS: PCP referral to Optum required before the visit (except H5253-035, I-SNP, Erickson).</t>
+          <t>Same coverage position as UHC MA (NCD 160.1 / L38801).</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Referral on file</t>
+          <t>Pre-service decision on optumproportal.com if endoscopic</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -964,7 +966,7 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service. Gated plans need an electronic PCP referral; the AZ Exchange needs a PCP referral before any PA.</t>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN (2026T0107II). AZ Pain Management Program: 64490-64495 need PA in all places of service.</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
@@ -1234,79 +1236,74 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>[ ] Referral on file where the plan requires one (UHC MA HMO/HMO-POS incl. D-SNP/C-SNP, Optum-delegated HMO - PCP submits it; UHC gated commercial; UHC AZ Exchange; Dual Complete).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1"/>
+    <row r="39" ht="30" customHeight="1"/>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Open items</t>
+        </is>
+      </c>
+    </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Open items</t>
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
+          <t>- AZ Blue: resolve the IVR prefix conflict (Strategic Hub vs Standard list); get a written predetermination for the first case.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>- AZ Blue: resolve the IVR prefix conflict (Strategic Hub vs Standard list); get a written predetermination for the first case.</t>
+          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: call and record.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: call and record.</t>
+          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository; those rows rely on your portal checks.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>- AZPC Attachment A and the Health Choice PA grids are not in the repository; those rows rely on your portal checks.</t>
+          <t>- Code selection (64772 vs 64999) for endoscopic MBT: confirm with the coding team from the operative note.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>- Code selection (64772 vs 64999) for endoscopic MBT: confirm with the coding team from the operative note.</t>
+          <t>- Confirm whether Dr. Luke is Optum-direct contracted (the Optum lists apply only to direct contracts).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>- Confirm whether Dr. Luke is Optum-direct contracted (the Optum lists apply only to direct contracts).</t>
+          <t>- Dr. Luke's procedure claims in 2026 S1 were billed at ASAP Surgery Centers North Valley LLC (ASC); confirm the ASC is contracted with each payer and obtain the ASC's own authorization where the payer requires a facility PA (AHCCCS FFS).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>- Dr. Luke's procedure claims in 2026 S1 were billed at ASAP Surgery Centers North Valley LLC (ASC); confirm the ASC is contracted with each payer and obtain the ASC's own authorization where the payer requires a facility PA (AHCCCS FFS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
           <t>- No 64772, 64999 or facet (64490-64495 / 64633-64636) claims appear in the 2026 S1 claims files - there is no payment history yet; track the first claims per payer closely.</t>
         </is>
       </c>
     </row>
+    <row r="49" ht="30" customHeight="1"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="23">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A33:F33"/>
@@ -1325,8 +1322,6 @@
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A6:F6"/>
@@ -3517,9 +3512,8 @@
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -3632,9 +3626,8 @@
       <c r="T3" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -3747,9 +3740,8 @@
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: NOT required (H5253-035 is exempt).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -3862,9 +3854,8 @@
       <c r="T5" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -3977,9 +3968,8 @@
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -4092,9 +4082,8 @@
       <c r="T7" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -4207,9 +4196,8 @@
       <c r="T8" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -4322,9 +4310,8 @@
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -4437,9 +4424,8 @@
       <c r="T10" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -4552,9 +4538,8 @@
       <c r="T11" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: NOT required (PPO).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -4667,9 +4652,8 @@
       <c r="T12" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: NOT required (PPO).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -4782,9 +4766,8 @@
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: NOT required (PPO).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -4897,9 +4880,8 @@
       <c r="T14" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
-Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
-Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com.</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -6375,7 +6357,6 @@
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -6474,7 +6455,6 @@
       <c r="T3" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -6573,7 +6553,6 @@
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: NOT required.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -6672,7 +6651,6 @@
       <c r="T5" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -6771,7 +6749,6 @@
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: NOT required.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -6870,7 +6847,6 @@
       <c r="T7" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: NOT required.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: if the MBT is endoscopic, call the Erickson PA number on the ID card - Erickson requires PA for experimental/investigational services.</t>
         </is>
@@ -6969,7 +6945,6 @@
       <c r="T8" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
-Referral: members must coordinate with their PCP; non-contracted providers need a referral form and PA (Dual Complete manual).
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS benefits.
 Action: PA line 800-445-1638 if needed. QMB members owe $0 - do not bill the member.</t>
         </is>
@@ -7068,7 +7043,6 @@
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
-Referral: NOT required.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
 Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is endoscopic, request a pre-service organization determination (PA&amp;N tool).</t>
         </is>
@@ -7167,7 +7141,6 @@
       <c r="T10" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
-Referral: REQUIRED - electronic PCP referral before the visit.
 Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
 Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
@@ -7266,7 +7239,6 @@
       <c r="T11" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
-Referral: NOT required.
 Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
 Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
@@ -7373,7 +7345,6 @@
       <c r="T12" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the Individual Exchange list (eff. 9/1/2026). 64999 WOULD need PA. 64490, 64493, 64633, 64635 need PA + site-of-service review.
-Referral: REQUIRED in Arizona - UHC will not accept a PA without a referral on file. No out-of-network coverage.
 Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
 Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
@@ -7807,7 +7778,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Gated (referral required)</t>
+          <t>Gated</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -7877,7 +7848,6 @@
       <c r="T17" s="3" t="inlineStr">
         <is>
           <t>PA: NOT required - 64772 is not on the UHC Complete list (eff. 9/1/2026). 64999 WOULD need PA.
-Referral: REQUIRED - electronic PCP referral. No out-of-network coverage.
 Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
 Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
         </is>
@@ -11242,7 +11212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1269"/>
+  <dimension ref="A1:D1315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -38971,6 +38941,1147 @@
         </is>
       </c>
     </row>
+    <row r="1271">
+      <c r="A1271" s="15" t="inlineStr">
+        <is>
+          <t>Round 6 - referral information removed (not requested), 23 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1272" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1272" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1272" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1273" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1273" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1273" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1274" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1274" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (H5253-035 is exempt).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file;</t>
+        </is>
+      </c>
+      <c r="D1274" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1275" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1275" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1275" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1276" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1276" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1276" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1277" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1277" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1277" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1278" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1278" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1278" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1279" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1279" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1279" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1280" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1280" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1280" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1281" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1281" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+      <c r="D1281" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1282" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1282" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+      <c r="D1282" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1283" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1283" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: NOT required (PPO).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is e</t>
+        </is>
+      </c>
+      <c r="D1283" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1284" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1284" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Referral: REQUIRED - the PCP must submit it to Optum before the visit (orthopaedist and neurosurgeon are listed specialties); no referral = claim denied, provider liability, member cannot be billed.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDO</t>
+        </is>
+      </c>
+      <c r="D1284" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1285" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1285" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+      <c r="D1285" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1286" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1286" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+      <c r="D1286" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1287" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1287" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+      <c r="D1287" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1288" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1288" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: REQUIRED - PCP referral on file before the visit (2026 UHC Administrative Guide).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action:</t>
+        </is>
+      </c>
+      <c r="D1288" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1289" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1289" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+      <c r="D1289" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1290" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1290" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, call the Erickson PA number on the ID car</t>
+        </is>
+      </c>
+      <c r="D1290" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, call the Erickson PA number on the ID card - Erickson requires PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1291" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1291" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Referral: members must coordinate with their PCP; non-contracted providers need a referral form and PA (Dual Complete manual).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's </t>
+        </is>
+      </c>
+      <c r="D1291" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1292" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1292" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Referral: NOT required.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the </t>
+        </is>
+      </c>
+      <c r="D1292" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: first check the group # - if delegated to Optum or Banner, use the Optum tab. If the MBT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1293" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1293" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: REQUIRED - electronic PCP referral before the visit.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a p</t>
+        </is>
+      </c>
+      <c r="D1293" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1294" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1294" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Referral: NOT required.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+      <c r="D1294" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Commercial list (eff. 9/1/2026). Arizona Pain Management Program: 64490-64495 need PA in all places of service; 64490/64493/64633/64635 need PA when done in hospital outpatient or ASC.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1295" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1295" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Individual Exchange list (eff. 9/1/2026). 64999 WOULD need PA. 64490, 64493, 64633, 64635 need PA + site-of-service review.
+Referral: REQUIRED in Arizona - UHC will not accept a PA without a referral on file. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination</t>
+        </is>
+      </c>
+      <c r="D1295" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Individual Exchange list (eff. 9/1/2026). 64999 WOULD need PA. 64490, 64493, 64633, 64635 need PA + site-of-service review.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1296" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C1296" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Complete list (eff. 9/1/2026). 64999 WOULD need PA.
+Referral: REQUIRED - electronic PCP referral. No out-of-network coverage.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+      <c r="D1296" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC Complete list (eff. 9/1/2026). 64999 WOULD need PA.
+Coverage: 2026T0107II - conventional (thermal) RFA covered with criteria and site-of-service review; endoscopic RFA/rhizotomy, pulsed, cooled, cryo, chemical and laser are UNPROVEN. 2026T0004WW: a positive diagnostic block = &gt;=50% relief.
+Action: if the MBT is endoscopic, expect a denial as unproven; get a predetermination before scheduling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1297" s="17" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="C1297" s="17" t="inlineStr">
+        <is>
+          <t>[ ] Referral on file where the plan requires one (UHC MA HMO/HMO-POS incl. D-SNP/C-SNP, Optum-delegated HMO - PCP submits it; UHC gated commercial; UHC AZ Exchange; Dual Complete).</t>
+        </is>
+      </c>
+      <c r="D1297" s="17" t="inlineStr">
+        <is>
+          <t>ROW REMOVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1298" s="17" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="C1298" s="17" t="inlineStr">
+        <is>
+          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); commercial Ablative policy (endoscopic = unproven) may fill gaps. HMO/HMO-POS (incl. D-SNP/C-SNP HMO): PCP referral required.</t>
+        </is>
+      </c>
+      <c r="D1298" s="17" t="inlineStr">
+        <is>
+          <t>Follows NCD 160.1 / L38801 (endoscopic evidence "insufficient"); UHC commercial policy calls endoscopic rhizotomy unproven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1299" s="17" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="C1299" s="17" t="inlineStr">
+        <is>
+          <t>HMO/HMO-POS: PCP referral to Optum required before the visit (except H5253-035, I-SNP, Erickson).</t>
+        </is>
+      </c>
+      <c r="D1299" s="17" t="inlineStr">
+        <is>
+          <t>Same coverage position as UHC MA (NCD 160.1 / L38801).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1300" s="17" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="C1300" s="17" t="inlineStr">
+        <is>
+          <t>Referral on file</t>
+        </is>
+      </c>
+      <c r="D1300" s="17" t="inlineStr">
+        <is>
+          <t>Pre-service decision on optumproportal.com if endoscopic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1301" s="17" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="C1301" s="17" t="inlineStr">
+        <is>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN. AZ Pain Management Program: 64490-64495 PA in all places of service. Gated plans need an electronic PCP referral; the AZ Exchange needs a PCP referral before any PA.</t>
+        </is>
+      </c>
+      <c r="D1301" s="17" t="inlineStr">
+        <is>
+          <t>Endoscopic RFA/rhizotomy UNPROVEN (2026T0107II). AZ Pain Management Program: 64490-64495 need PA in all places of service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1302" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1302" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1302" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1303" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1303" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1303" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1304" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1304" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1304" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1305" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1305" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1305" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1306" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1306" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1306" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1307" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1307" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1307" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1308" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1308" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1308" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1309" s="17" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C1309" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1309" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1310" s="17" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C1310" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1310" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1311" s="17" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C1311" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1311" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1312" s="17" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C1312" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1312" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1313" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1313" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1313" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1314" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1314" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: confirm the referral is on file; if the MBT is endoscopic, request a pre-servi</t>
+        </is>
+      </c>
+      <c r="D1314" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Optum UHC MA list (Optum-direct providers) or the UHC MA list (all others).
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. Optum: new technology is not covered unless Optum approves it and PA is obtained.
+Action: if the MBT is endoscopic, request a pre-service decision on optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1315" s="17" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C1315" s="17" t="inlineStr">
+        <is>
+          <t>Gated (referral required)</t>
+        </is>
+      </c>
+      <c r="D1315" s="17" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -602,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -652,7 +651,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -10017,7 +10015,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>AMPM 820 sections L.3.b, T and U; AMPM 810 (FFS UM)</t>
+          <t>AMPM 820 sec. L.3.b and L.5 (p.14); sec. T (p.21-22); sec. U (p.22)</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -10057,9 +10055,11 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PA: REQUIRED - elective outpatient surgery needs a surgeon PA AND a separate ASC/hospital PA (AMPM 820). Not needed if IHS/638 facility, emergency, or AHCCCS not primary.
+          <t>PA: REQUIRED. AMPM 820 L.3.b (p.14): "An Authorization is required ... for all FFS and DDD THP members: ... b. Elective and urgent outpatient surgical procedures". Sec. U (p.22): FFS surgeons "shall obtain a separate and distinct AHCCCS PA number from that of the facility PA number prior to providing elective/non-emergency surgeries". Sec. T: the ASC "shall obtain PA from AHCCCS DFSM for all outpatient surgeries".
+Applies ONLY to AHCCCS fee-for-service members (AIHP, Tribal ALTCS, TRBHA, DDD THP) - NOT to AHCCCS health plans (UHC Community Plan, Mercy Care, Health Choice, etc.).
+No PA needed (sec. III.1): emergency, AHCCCS not primary, IHS/638 provider or facility, retro eligibility. L.3.b refers to "section FF for exclusions", but the policy on file ends at section DD.
 Coverage: experimental services not covered (AMPM 320-B); moderate sedation by the performing physician not covered (Exh. 300-1).
-Action: submit both PAs on AHCCCS Online (fax 602-256-6591; phone 602-417-4400) before scheduling; put member name/DOB/ID on every page.</t>
+Action: submit surgeon PA and ASC PA to AHCCCS DFSM (AHCCCS Online; fax 602-256-6591; phone 602-417-4400) before scheduling.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -11212,7 +11212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1315"/>
+  <dimension ref="A1:D1317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -40082,6 +40082,54 @@
         </is>
       </c>
     </row>
+    <row r="1316">
+      <c r="A1316" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1316" s="17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C1316" s="17" t="inlineStr">
+        <is>
+          <t>AMPM 820 sections L.3.b, T and U; AMPM 810 (FFS UM)</t>
+        </is>
+      </c>
+      <c r="D1316" s="17" t="inlineStr">
+        <is>
+          <t>AMPM 820 sec. L.3.b and L.5 (p.14); sec. T (p.21-22); sec. U (p.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1317" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1317" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED - elective outpatient surgery needs a surgeon PA AND a separate ASC/hospital PA (AMPM 820). Not needed if IHS/638 facility, emergency, or AHCCCS not primary.
+Coverage: experimental services not covered (AMPM 320-B); moderate sedation by the performing physician not covered (Exh. 300-1).
+Action: submit both PAs on AHCCCS Online (fax 602-256-6591; phone 602-417-4400) before scheduling; put member name/DOB/ID on every page.</t>
+        </is>
+      </c>
+      <c r="D1317" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED. AMPM 820 L.3.b (p.14): "An Authorization is required ... for all FFS and DDD THP members: ... b. Elective and urgent outpatient surgical procedures". Sec. U (p.22): FFS surgeons "shall obtain a separate and distinct AHCCCS PA number from that of the facility PA number prior to providing elective/non-emergency surgeries". Sec. T: the ASC "shall obtain PA from AHCCCS DFSM for all outpatient surgeries".
+Applies ONLY to AHCCCS fee-for-service members (AIHP, Tribal ALTCS, TRBHA, DDD THP) - NOT to AHCCCS health plans (UHC Community Plan, Mercy Care, Health Choice, etc.).
+No PA needed (</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -602,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -651,6 +652,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -1021,19 +1023,19 @@
           <t>SCAN MA PA list rev. 1 Aug 2026; BCG0100; CCP0207</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>NO - not on any list on file</t>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>No Optum SCAN list on file; 64772 is absent from SCAN's and both Optum lists. ASC expected (CCP0207).</t>
+          <t>Availity auth tool: not required (your check). SCAN denies experimental/investigational services (BCG0111).</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>Confirm with Optum</t>
+          <t>Keep Availity result</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -1243,11 +1245,7 @@
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
-        </is>
-      </c>
+      <c r="A41" s="14" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
@@ -1501,12 +1499,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists &gt; 2026 STANDARD Code List tab</t>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 STANDARD Code List"</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -1531,7 +1529,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks)</t>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -1599,7 +1597,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>BCBS South Carolina UM, 800-868-1032 (per AZ Blue code-list Introduction)</t>
+          <t>No online tool on file - call BCBS South Carolina 800-868-1032</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1701,12 +1699,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>AHG 800-847-7605. Claims still file to AZ Blue (EDI #53589)</t>
+          <t>No online tool on file - call American Health Group 800-847-7605</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>The group's Summary Plan Description (SPD)</t>
+          <t>AZ Blue and TPA Jointly Administered Plans (as of 07/2026) - PA set by the group/TPA</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1807,7 +1805,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>The group's Summary Plan Description (benefit) + AmeriBen's UM criteria (medical necessity)</t>
+          <t>AZ Blue and TPA Jointly Administered Plans (as of 07/2026) - PA set by the group/TPA</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -1996,12 +1994,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Lookup / Availity auth tool (eviCore handles only the MSK/pain codes on the MA list; 64772 is not one)</t>
+          <t>Availity auth tool; AZ Blue PA lookup tool: azblue.com/lookup - checked: not required (your check). eviCore (evicore.com/provider or azbluemedicare.com portal) only for eviCore codes on the MA list</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists &gt; 2026 Medicare Advantage List tab</t>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List"</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2026,12 +2024,12 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -2094,12 +2092,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2124,12 +2122,12 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -2222,12 +2220,12 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -2301,12 +2299,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com or 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2331,12 +2329,12 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -2411,12 +2409,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com or 877-370-2845</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2441,12 +2439,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -2507,12 +2505,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Lookup / Availity</t>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup - checked: not required (your check)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists - 2026 FEP List and FEP Blue Focus List tabs</t>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 FEP List"</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -2605,7 +2603,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>n/a - no PA exists. Medigap pays secondary to Medicare's determination.</t>
+          <t>Not applicable - Medigap has no PA</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -2635,12 +2633,12 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -2829,12 +2827,12 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -2927,7 +2925,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 320-B (experimental services not covered); AMPM Exhibit 300-1 (moderate sedation by the performing physician not covered); AHCCCS FFS Physician Fee Schedule</t>
+          <t>320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2995,7 +2993,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>BlueCard Medical Policy Router - medical policy and PA come from the HOME plan -NOTE the asymmetry: the CLAIM still files locally to AZ Blue.</t>
+          <t>Availity &gt; BlueCard Medical Policy Router (home plan PA rules)</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -3096,12 +3094,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists &gt; '2026 State of AZ Grp List' tab</t>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 State of AZ Grp List"</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -3126,12 +3124,12 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>As Standard (MCG A-0218 / A-0695)</t>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A-0218; A-0695</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -3198,12 +3196,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>AZ Blue PA Requirements Code Lists &gt; '2026 Teamsters Group List' tab</t>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Teamsters Group List"</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3228,12 +3226,12 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>As Standard (MCG A-0218 / A-0695)</t>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A-0218; A-0695</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -3459,12 +3457,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -3489,12 +3487,12 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -3573,12 +3571,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3603,12 +3601,12 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -3687,12 +3685,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3717,12 +3715,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -3801,12 +3799,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -3831,12 +3829,12 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -3915,12 +3913,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -3945,12 +3943,12 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -4029,12 +4027,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -4059,12 +4057,12 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -4143,12 +4141,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -4173,12 +4171,12 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -4257,12 +4255,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -4287,12 +4285,12 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -4371,12 +4369,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4401,12 +4399,12 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -4485,12 +4483,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -4515,12 +4513,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -4599,12 +4597,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -4629,12 +4627,12 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -4713,12 +4711,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -4743,12 +4741,12 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -4827,12 +4825,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -4857,12 +4855,12 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403</t>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -4941,12 +4939,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4971,12 +4969,12 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -5053,12 +5051,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5083,12 +5081,12 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -5160,32 +5158,32 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>NO - not on any list on file</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845</t>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+          <t>NO - absent</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -5195,12 +5193,12 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
@@ -5215,9 +5213,9 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
 Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
-Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -5274,32 +5272,32 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>NO - not on any list on file</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845</t>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+          <t>NO - absent</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -5309,12 +5307,12 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -5329,9 +5327,9 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
 Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
-Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
@@ -5388,32 +5386,32 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>NO - not on any list on file</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845</t>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+          <t>NO - absent</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -5423,12 +5421,12 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -5443,9 +5441,9 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
 Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
-Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -5502,32 +5500,32 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>NO - not on any list on file</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845</t>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+          <t>NO - absent</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -5537,12 +5535,12 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -5557,9 +5555,9 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
 Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
-Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -5616,32 +5614,32 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>NO - not on any list on file</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>optumproportal.com / 877-370-2845</t>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+          <t>NO - absent</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -5651,12 +5649,12 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -5671,9 +5669,9 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
 Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
-Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -6304,12 +6302,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -6334,7 +6332,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -6402,12 +6400,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6432,7 +6430,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -6500,12 +6498,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -6530,7 +6528,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -6598,12 +6596,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -6628,7 +6626,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -6696,12 +6694,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -6726,7 +6724,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -6794,12 +6792,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Erickson MSR / prior authorization number on the back of the ID card</t>
+          <t>Erickson MSR / prior authorization number on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -6824,7 +6822,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -6892,12 +6890,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Portal PA&amp;N tool, or the Prior Authorization Department on 1-800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 1-800-445-1638</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>UHC MA / Peoples Health PA requirements - the list names UHC Dual Complete (HMO D-SNP) as an included plan</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -6922,7 +6920,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -6990,12 +6988,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -7020,7 +7018,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -7088,12 +7086,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Commercial advance notification and prior authorization requirements</t>
+          <t>Prior authorization requirements for UnitedHealthcare commercial plans</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -7118,7 +7116,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -7186,12 +7184,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Commercial advance notification and prior authorization requirements</t>
+          <t>Prior authorization requirements for UnitedHealthcare commercial plans</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -7216,7 +7214,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -7292,12 +7290,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>UHCprovider.com/paan - must be submitted electronically</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan) - must be submitted electronically</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Individual Exchange prior authorization requirements</t>
+          <t>Prior authorization requirements for UnitedHealthcare Individual Exchange plans</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -7322,7 +7320,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -7390,12 +7388,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid - UnitedHealthcare Community Plan of Arizona</t>
+          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -7420,7 +7418,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -7585,7 +7583,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal PA&amp;N tool / 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -7697,12 +7695,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>n/a - no PA. Claims: payer ID 36273; P.O. Box 1878, Southampton PA; 1-800-523-5800</t>
+          <t>Not applicable - no PA</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026 UHC Care Provider Administrative Guide - AARP Medicare Supplement section</t>
+          <t>2026 UnitedHealthcare Care Provider Administrative Guide (AARP Medicare Supplement section)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -7727,12 +7725,12 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -7795,7 +7793,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -7825,7 +7823,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -7905,7 +7903,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -7935,7 +7933,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -8003,12 +8001,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Prior authorization requirements for Arizona Developmental Disabilities - UnitedHealthcare Community Plan of Arizona</t>
+          <t>Prior authorization requirements for Arizona Developmental Disabilities</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -8033,7 +8031,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -8101,12 +8099,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Prior authorization requirements for Arizona Long Term Care - UnitedHealthcare Community Plan of Arizona</t>
+          <t>Prior authorization requirements for Arizona Long Term Care</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -8131,7 +8129,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -8354,7 +8352,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Noridian Auth Tool - result for 64772: no prior authorization required. Save a dated screenshot to the patient file.</t>
+          <t>Noridian Medicare Portal - Auth Tool look-up - checked: not required (your check). Save a dated screenshot.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -8384,12 +8382,12 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1 'Induced Lesions of Nerve Tracts', LCD 'Facet Joint Interventions for Pain Management'; LCA 'Billing and Coding'</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-3 sec. 160.1; L38801 (rev. eff. 04/16/2026); A58403 R9 (rev. eff. 09/17/2026)</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -8462,7 +8460,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Palmetto GBA Railroad Medicare (no PA program for 64772)</t>
+          <t>Not applicable - no PA program for 64772</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -8492,12 +8490,12 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>NCD 160.1; L38801 / A58403 (Railroad Medicare applies the LCD/LCA of the MAC where the service is rendered)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -8725,7 +8723,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Availity / Cohere - both returned NOT required (your check). ACD: 800-523-0023, fax 800-266-3022</t>
+          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check). ACD: 800-523-0023 / fax 800-266-3022</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -8755,12 +8753,12 @@
       </c>
       <c r="P2" s="10" t="inlineStr">
         <is>
-          <t>Neuroablative Techniques for Chronic Pain (MA); Injections for Pain Conditions (MA) for the diagnostic blocks; NCD 160.1 and Noridian L38801 / A58403 (referenced by both)</t>
+          <t>Neuroablative Techniques for Chronic Pain; Injections for Pain Conditions; NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>HUM-1168-008; HUM-1137-010; L38801; A58403</t>
+          <t>HUM-1168-008; HUM-1137-010; NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr">
@@ -9516,7 +9514,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>No need - Humana pays secondary</t>
+          <t>Not applicable - Medigap has no PA</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
@@ -9546,12 +9544,12 @@
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R9" s="10" t="inlineStr">
@@ -9630,7 +9628,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Not applicable - Medigap has no PA</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -9660,12 +9658,12 @@
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R10" s="10" t="inlineStr">
@@ -9742,7 +9740,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Ibid</t>
+          <t>Not applicable - Medigap has no PA</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -9772,12 +9770,12 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+          <t>NCD 160.1; L38801; A58403</t>
         </is>
       </c>
       <c r="R11" s="10" t="inlineStr">
@@ -10010,7 +10008,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM Policy 820 - Fee-for-Service Prior Authorization Requirements (and FFS PA Guidelines by code)</t>
+          <t>820 - Fee-For-Service Authorization Requirements (AMPM Chapter 800)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -10035,7 +10033,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations); FFS Physician Fee Schedule</t>
+          <t>320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -11212,7 +11210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1317"/>
+  <dimension ref="A1:D1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -40130,6 +40128,4917 @@
         </is>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" s="15" t="inlineStr">
+        <is>
+          <t>Round 7 - auth look-up tools added per payer; document names set to exact published titles; SCAN = no auth (Availity check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1320" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1320" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+        </is>
+      </c>
+      <c r="D1320" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1321" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C1321" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists &gt; 2026 STANDARD Code List tab</t>
+        </is>
+      </c>
+      <c r="D1321" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 STANDARD Code List"</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1322" s="17" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C1322" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+        </is>
+      </c>
+      <c r="D1322" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1323" s="17" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="C1323" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists &gt; '2026 State of AZ Grp List' tab</t>
+        </is>
+      </c>
+      <c r="D1323" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 State of AZ Grp List"</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1324" s="17" t="inlineStr">
+        <is>
+          <t>J19</t>
+        </is>
+      </c>
+      <c r="C1324" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity Auth tool</t>
+        </is>
+      </c>
+      <c r="D1324" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1325" s="17" t="inlineStr">
+        <is>
+          <t>K19</t>
+        </is>
+      </c>
+      <c r="C1325" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists &gt; '2026 Teamsters Group List' tab</t>
+        </is>
+      </c>
+      <c r="D1325" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Teamsters Group List"</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1326" s="17" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="C1326" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity</t>
+        </is>
+      </c>
+      <c r="D1326" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup - checked: not required (your check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1327" s="17" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C1327" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists - 2026 FEP List and FEP Blue Focus List tabs</t>
+        </is>
+      </c>
+      <c r="D1327" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 FEP List"</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1328" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C1328" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup / Availity auth tool (eviCore handles only the MSK/pain codes on the MA list; 64772 is not one)</t>
+        </is>
+      </c>
+      <c r="D1328" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool; AZ Blue PA lookup tool: azblue.com/lookup - checked: not required (your check). eviCore (evicore.com/provider or azbluemedicare.com portal) only for eviCore codes on the MA list</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1329" s="17" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="C1329" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists &gt; 2026 Medicare Advantage List tab</t>
+        </is>
+      </c>
+      <c r="D1329" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List"</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1330" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1330" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com</t>
+        </is>
+      </c>
+      <c r="D1330" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1331" s="17" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C1331" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+      <c r="D1331" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1332" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1332" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com or 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1332" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1333" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C1333" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+      <c r="D1333" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1334" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1334" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com or 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1334" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1335" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C1335" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+      <c r="D1335" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1336" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1336" s="17" t="inlineStr">
+        <is>
+          <t>BCBS South Carolina UM, 800-868-1032 (per AZ Blue code-list Introduction)</t>
+        </is>
+      </c>
+      <c r="D1336" s="17" t="inlineStr">
+        <is>
+          <t>No online tool on file - call BCBS South Carolina 800-868-1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1337" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1337" s="17" t="inlineStr">
+        <is>
+          <t>AHG 800-847-7605. Claims still file to AZ Blue (EDI #53589)</t>
+        </is>
+      </c>
+      <c r="D1337" s="17" t="inlineStr">
+        <is>
+          <t>No online tool on file - call American Health Group 800-847-7605</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1338" s="17" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C1338" s="17" t="inlineStr">
+        <is>
+          <t>The group's Summary Plan Description (SPD)</t>
+        </is>
+      </c>
+      <c r="D1338" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue and TPA Jointly Administered Plans (as of 07/2026) - PA set by the group/TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1339" s="17" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C1339" s="17" t="inlineStr">
+        <is>
+          <t>The group's Summary Plan Description (benefit) + AmeriBen's UM criteria (medical necessity)</t>
+        </is>
+      </c>
+      <c r="D1339" s="17" t="inlineStr">
+        <is>
+          <t>AZ Blue and TPA Jointly Administered Plans (as of 07/2026) - PA set by the group/TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1340" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C1340" s="17" t="inlineStr">
+        <is>
+          <t>n/a - no PA exists. Medigap pays secondary to Medicare's determination.</t>
+        </is>
+      </c>
+      <c r="D1340" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - Medigap has no PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1341" s="17" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="C1341" s="17" t="inlineStr">
+        <is>
+          <t>BlueCard Medical Policy Router - medical policy and PA come from the HOME plan -NOTE the asymmetry: the CLAIM still files locally to AZ Blue.</t>
+        </is>
+      </c>
+      <c r="D1341" s="17" t="inlineStr">
+        <is>
+          <t>Availity &gt; BlueCard Medical Policy Router (home plan PA rules)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1342" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1342" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection (diagnostic blocks)</t>
+        </is>
+      </c>
+      <c r="D1342" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1343" s="17" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C1343" s="17" t="inlineStr">
+        <is>
+          <t>As Standard (MCG A-0218 / A-0695)</t>
+        </is>
+      </c>
+      <c r="D1343" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1344" s="17" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="C1344" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1344" s="17" t="inlineStr">
+        <is>
+          <t>A-0218; A-0695</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1345" s="17" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C1345" s="17" t="inlineStr">
+        <is>
+          <t>As Standard (MCG A-0218 / A-0695)</t>
+        </is>
+      </c>
+      <c r="D1345" s="17" t="inlineStr">
+        <is>
+          <t>MCG A-0218 Facet Neurotomy; MCG A-0695 Facet Joint Injection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1346" s="17" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="C1346" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1346" s="17" t="inlineStr">
+        <is>
+          <t>A-0218; A-0695</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1347" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C1347" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1347" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1348" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C1348" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1348" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1349" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C1349" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1349" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1350" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C1350" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1350" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1351" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1351" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1351" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1352" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C1352" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1352" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1353" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1353" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1353" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1354" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C1354" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1354" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1355" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1355" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1355" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1356" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C1356" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1356" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1357" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C1357" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1357" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1358" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C1358" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1358" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1359" s="17" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C1359" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1359" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1360" s="17" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="C1360" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1360" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1361" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C1361" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 320-B (experimental services not covered); AMPM Exhibit 300-1 (moderate sedation by the performing physician not covered); AHCCCS FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+      <c r="D1361" s="17" t="inlineStr">
+        <is>
+          <t>320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1362" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1362" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1362" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1363" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C1363" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1363" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1364" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1364" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1364" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1365" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C1365" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1365" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1366" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1366" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1366" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1367" s="17" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C1367" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1367" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1368" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C1368" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1368" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1369" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C1369" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1369" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1370" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1370" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1370" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1371" s="17" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C1371" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1371" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1372" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C1372" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1372" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1373" s="17" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C1373" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1373" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1374" s="17" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C1374" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1374" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1375" s="17" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C1375" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1375" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1376" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C1376" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1376" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1377" s="17" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C1377" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1377" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1378" s="17" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C1378" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1378" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1379" s="17" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C1379" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1379" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1380" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C1380" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1380" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1381" s="17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="C1381" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1381" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1382" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C1382" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1382" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1383" s="17" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="C1383" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1383" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1384" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C1384" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1384" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1385" s="17" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C1385" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1385" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1386" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1386" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1386" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1387" s="17" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C1387" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1387" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1388" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C1388" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1388" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1389" s="17" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C1389" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1389" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1390" s="17" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C1390" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1390" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1391" s="17" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C1391" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1391" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1392" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1392" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1392" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1393" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C1393" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1393" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1394" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1394" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1394" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1395" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C1395" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1395" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1396" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1396" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1396" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1397" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C1397" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1397" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1398" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1398" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1398" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1399" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C1399" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1399" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1400" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1400" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1400" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1401" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C1401" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1401" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1402" s="17" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="C1402" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1402" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1403" s="17" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C1403" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1403" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1404" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C1404" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1404" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1405" s="17" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="C1405" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1405" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1406" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C1406" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1406" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1407" s="17" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C1407" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1407" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1408" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C1408" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1408" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1409" s="17" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C1409" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1409" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1410" s="17" t="inlineStr">
+        <is>
+          <t>J14</t>
+        </is>
+      </c>
+      <c r="C1410" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1410" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1411" s="17" t="inlineStr">
+        <is>
+          <t>K14</t>
+        </is>
+      </c>
+      <c r="C1411" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona UHC MA PA and referral requirements. All other providers: UHC Medicare Advantage PA requirements (per the Optum list header and UHC/Optum QRG PCA-4-26-00582)</t>
+        </is>
+      </c>
+      <c r="D1411" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: UnitedHealthcare Medicare Advantage prior authorization and referral requirements (Optum-direct providers); UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1412" s="17" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C1412" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403</t>
+        </is>
+      </c>
+      <c r="D1412" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1413" s="17" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="C1413" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1413" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1414" s="17" t="inlineStr">
+        <is>
+          <t>J15</t>
+        </is>
+      </c>
+      <c r="C1414" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1414" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1415" s="17" t="inlineStr">
+        <is>
+          <t>K15</t>
+        </is>
+      </c>
+      <c r="C1415" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+      <c r="D1415" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1416" s="17" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C1416" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1416" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1417" s="17" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="C1417" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1417" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1418" s="17" t="inlineStr">
+        <is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="C1418" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845 (TTY 711)</t>
+        </is>
+      </c>
+      <c r="D1418" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1419" s="17" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="C1419" s="17" t="inlineStr">
+        <is>
+          <t>Optum-DIRECT contracted providers: 2026 OptumCare Network of Arizona BCBS PA requirements. All other providers: AZ Blue 2026 Medicare Advantage List (per the Optum list header)</t>
+        </is>
+      </c>
+      <c r="D1419" s="17" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements (Optum-direct providers); AZ Blue Prior Authorization Requirements Code Lists (Updated 09/01/2026) &gt; tab "2026 Medicare Advantage List" (all others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1420" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C1420" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1420" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1421" s="17" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="C1421" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1421" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1422" s="17" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="C1422" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1422" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1423" s="17" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="C1423" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1423" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1424" s="17" t="inlineStr">
+        <is>
+          <t>K17</t>
+        </is>
+      </c>
+      <c r="C1424" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+        </is>
+      </c>
+      <c r="D1424" s="17" t="inlineStr">
+        <is>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1425" s="17" t="inlineStr">
+        <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="C1425" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+      <c r="D1425" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1426" s="17" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="C1426" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1426" s="17" t="inlineStr">
+        <is>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1427" s="17" t="inlineStr">
+        <is>
+          <t>N17</t>
+        </is>
+      </c>
+      <c r="C1427" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D1427" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1428" s="17" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C1428" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D1428" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1429" s="17" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="C1429" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D1429" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1430" s="17" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C1430" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+      <c r="D1430" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1431" s="17" t="inlineStr">
+        <is>
+          <t>I18</t>
+        </is>
+      </c>
+      <c r="C1431" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1431" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1432" s="17" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C1432" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1432" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1433" s="17" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="C1433" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+        </is>
+      </c>
+      <c r="D1433" s="17" t="inlineStr">
+        <is>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1434" s="17" t="inlineStr">
+        <is>
+          <t>L18</t>
+        </is>
+      </c>
+      <c r="C1434" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+      <c r="D1434" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1435" s="17" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="C1435" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1435" s="17" t="inlineStr">
+        <is>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1436" s="17" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C1436" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D1436" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1437" s="17" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C1437" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D1437" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1438" s="17" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="C1438" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D1438" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1439" s="17" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C1439" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+      <c r="D1439" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1440" s="17" t="inlineStr">
+        <is>
+          <t>I19</t>
+        </is>
+      </c>
+      <c r="C1440" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1440" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1441" s="17" t="inlineStr">
+        <is>
+          <t>J19</t>
+        </is>
+      </c>
+      <c r="C1441" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1441" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1442" s="17" t="inlineStr">
+        <is>
+          <t>K19</t>
+        </is>
+      </c>
+      <c r="C1442" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+        </is>
+      </c>
+      <c r="D1442" s="17" t="inlineStr">
+        <is>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1443" s="17" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="C1443" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+      <c r="D1443" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1444" s="17" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="C1444" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1444" s="17" t="inlineStr">
+        <is>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1445" s="17" t="inlineStr">
+        <is>
+          <t>N19</t>
+        </is>
+      </c>
+      <c r="C1445" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D1445" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1446" s="17" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C1446" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D1446" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1447" s="17" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="C1447" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D1447" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1448" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C1448" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+      <c r="D1448" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1449" s="17" t="inlineStr">
+        <is>
+          <t>I20</t>
+        </is>
+      </c>
+      <c r="C1449" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1449" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1450" s="17" t="inlineStr">
+        <is>
+          <t>J20</t>
+        </is>
+      </c>
+      <c r="C1450" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1450" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1451" s="17" t="inlineStr">
+        <is>
+          <t>K20</t>
+        </is>
+      </c>
+      <c r="C1451" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+        </is>
+      </c>
+      <c r="D1451" s="17" t="inlineStr">
+        <is>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1452" s="17" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C1452" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+      <c r="D1452" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1453" s="17" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+      <c r="C1453" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1453" s="17" t="inlineStr">
+        <is>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1454" s="17" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="C1454" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D1454" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1455" s="17" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C1455" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D1455" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1456" s="17" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="C1456" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D1456" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1457" s="17" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C1457" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+      <c r="D1457" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1458" s="17" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="C1458" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1458" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1459" s="17" t="inlineStr">
+        <is>
+          <t>J21</t>
+        </is>
+      </c>
+      <c r="C1459" s="17" t="inlineStr">
+        <is>
+          <t>optumproportal.com / 877-370-2845</t>
+        </is>
+      </c>
+      <c r="D1459" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool - checked: not required (your check). Curo / optumproportal.com also available</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1460" s="17" t="inlineStr">
+        <is>
+          <t>K21</t>
+        </is>
+      </c>
+      <c r="C1460" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN-specific PA list on file. SCAN's own MA PA list (rev. 1 Aug 2026) covers only members assigned to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical; for others it says contact the assigned medical group (here, Optum).</t>
+        </is>
+      </c>
+      <c r="D1460" s="17" t="inlineStr">
+        <is>
+          <t>SCAN Medicare Advantage Prior Authorization Requirements (applies only to CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1461" s="17" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="C1461" s="17" t="inlineStr">
+        <is>
+          <t>No applicable list on file (SCAN MA PA Requirements rev. 1 Aug 2026 does not apply to Optum-delegated members)</t>
+        </is>
+      </c>
+      <c r="D1461" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1462" s="17" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="C1462" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D1462" s="17" t="inlineStr">
+        <is>
+          <t>Effective January 1, 2024; Last Revised: August 1, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1463" s="17" t="inlineStr">
+        <is>
+          <t>N21</t>
+        </is>
+      </c>
+      <c r="C1463" s="17" t="inlineStr">
+        <is>
+          <t>n/a - the SCAN list is limited to 6 named AZ groups; 64772 is absent from it and from both Optum AZ lists</t>
+        </is>
+      </c>
+      <c r="D1463" s="17" t="inlineStr">
+        <is>
+          <t>NO - absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1464" s="17" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="C1464" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403); SCAN BCG0100 (hierarchy); BCG0111 (experimental/investigational); CCP0207 (site of service); CRP0420 (unlisted codes)</t>
+        </is>
+      </c>
+      <c r="D1464" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; BCG0100 – Hierarchy of Guidance for Organization Determinations and Appeals; BCG0111 – Clinical Trials, Experimental Procedures &amp; Items, and Investigational Devices; CCP0207 – Site of Service for Outpatient Surgical Procedures; CRP0420 – Unlisted or Miscellaneous Code Reimbursement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1465" s="17" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="C1465" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+      <c r="D1465" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; BCG0100; BCG0111; CCP0207; CRP0420</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1466" s="17" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="C1466" s="17" t="inlineStr">
+        <is>
+          <t>PA: 64772 is not on the SCAN list or either Optum AZ list. No Optum list specific to SCAN is on file (SCAN's own list covers only CenterWell, Embrace, IntraCare, Phoenix Physicians IPA, Oak Street AZ and Village Medical members).
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: call Optum 877-370-2845 once to confirm no auth for SCAN members and record the reference #. If endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+      <c r="D1466" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - Availity auth tool (your check). 64772 is also absent from the SCAN list and both Optum AZ lists.
+Coverage: SCAN follows NCD/LCD first (BCG0100) - see Medicare tab. Experimental/investigational services are denied (BCG0111). 64772 is an ASC-list code, so SCAN expects the ASC (CCP0207).
+Action: keep the Availity result. If the MBT is endoscopic, expect an experimental/investigational denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1467" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1467" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1467" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1468" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C1468" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1468" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1469" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1469" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1469" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1470" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1470" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1470" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1471" s="17" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C1471" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1471" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1472" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C1472" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1472" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1473" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1473" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1473" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1474" s="17" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C1474" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1474" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1475" s="17" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C1475" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1475" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1476" s="17" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C1476" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1476" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1477" s="17" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C1477" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1477" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1478" s="17" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C1478" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1478" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1479" s="17" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C1479" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1479" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1480" s="17" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C1480" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1480" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1481" s="17" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C1481" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1481" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1482" s="17" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C1482" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal &gt; Prior Authorization and Notification, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1482" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1483" s="17" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="C1483" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1483" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1484" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1484" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1484" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1485" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C1485" s="17" t="inlineStr">
+        <is>
+          <t>Erickson MSR / prior authorization number on the back of the ID card</t>
+        </is>
+      </c>
+      <c r="D1485" s="17" t="inlineStr">
+        <is>
+          <t>Erickson MSR / prior authorization number on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1486" s="17" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="C1486" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Medicare Advantage / Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1486" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1487" s="17" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="C1487" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1487" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1488" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1488" s="17" t="inlineStr">
+        <is>
+          <t>Portal PA&amp;N tool, or the Prior Authorization Department on 1-800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1488" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 1-800-445-1638</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1489" s="17" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="C1489" s="17" t="inlineStr">
+        <is>
+          <t>UHC MA / Peoples Health PA requirements - the list names UHC Dual Complete (HMO D-SNP) as an included plan</t>
+        </is>
+      </c>
+      <c r="D1489" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare® Medicare Advantage/Peoples Health Plans prior authorization requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1490" s="17" t="inlineStr">
+        <is>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="C1490" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1490" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management; Pain Management (UnitedHealthcare Medicare Advantage Medical Policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1491" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1491" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal</t>
+        </is>
+      </c>
+      <c r="D1491" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1492" s="17" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="C1492" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Commercial advance notification and prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1492" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for UnitedHealthcare commercial plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1493" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1493" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal</t>
+        </is>
+      </c>
+      <c r="D1493" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1494" s="17" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="C1494" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Commercial advance notification and prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1494" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for UnitedHealthcare commercial plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1495" s="17" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="C1495" s="17" t="inlineStr">
+        <is>
+          <t>UHCprovider.com/paan - must be submitted electronically</t>
+        </is>
+      </c>
+      <c r="D1495" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan) - must be submitted electronically</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1496" s="17" t="inlineStr">
+        <is>
+          <t>K12</t>
+        </is>
+      </c>
+      <c r="C1496" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Individual Exchange prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="D1496" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for UnitedHealthcare Individual Exchange plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1497" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C1497" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1497" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1498" s="17" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="C1498" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+      <c r="D1498" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for AHCCCS Complete Care (ACC) Medicaid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1499" s="17" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C1499" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+      <c r="D1499" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1500" s="17" t="inlineStr">
+        <is>
+          <t>J19</t>
+        </is>
+      </c>
+      <c r="C1500" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1500" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1501" s="17" t="inlineStr">
+        <is>
+          <t>K19</t>
+        </is>
+      </c>
+      <c r="C1501" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Developmental Disabilities - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+      <c r="D1501" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Developmental Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1502" s="17" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="C1502" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+      <c r="D1502" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1503" s="17" t="inlineStr">
+        <is>
+          <t>J20</t>
+        </is>
+      </c>
+      <c r="C1503" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1503" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1504" s="17" t="inlineStr">
+        <is>
+          <t>K20</t>
+        </is>
+      </c>
+      <c r="C1504" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Long Term Care - UnitedHealthcare Community Plan of Arizona</t>
+        </is>
+      </c>
+      <c r="D1504" s="17" t="inlineStr">
+        <is>
+          <t>Prior authorization requirements for Arizona Long Term Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1505" s="17" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="C1505" s="17" t="inlineStr">
+        <is>
+          <t>UHC Community Plan Ablative Treatment for Spinal Pain; AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations)</t>
+        </is>
+      </c>
+      <c r="D1505" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain (UnitedHealthcare Community Plan Medical Policy); 320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1506" s="17" t="inlineStr">
+        <is>
+          <t>J15</t>
+        </is>
+      </c>
+      <c r="C1506" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool / 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1506" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1507" s="17" t="inlineStr">
+        <is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="C1507" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal</t>
+        </is>
+      </c>
+      <c r="D1507" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1508" s="17" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C1508" s="17" t="inlineStr">
+        <is>
+          <t>UHC Provider Portal PA&amp;N tool, or 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1508" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1509" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1509" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+      <c r="D1509" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1510" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1510" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+      <c r="D1510" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1511" s="17" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C1511" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+      <c r="D1511" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1512" s="17" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C1512" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+      <c r="D1512" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1513" s="17" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C1513" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections</t>
+        </is>
+      </c>
+      <c r="D1513" s="17" t="inlineStr">
+        <is>
+          <t>Ablative Treatment for Spinal Pain; Facet Joint and Medial Branch Block Injections for Spinal Pain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1514" s="17" t="inlineStr">
+        <is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="C1514" s="17" t="inlineStr">
+        <is>
+          <t>n/a - no PA. Claims: payer ID 36273; P.O. Box 1878, Southampton PA; 1-800-523-5800</t>
+        </is>
+      </c>
+      <c r="D1514" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - no PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1515" s="17" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="C1515" s="17" t="inlineStr">
+        <is>
+          <t>2026 UHC Care Provider Administrative Guide - AARP Medicare Supplement section</t>
+        </is>
+      </c>
+      <c r="D1515" s="17" t="inlineStr">
+        <is>
+          <t>2026 UnitedHealthcare Care Provider Administrative Guide (AARP Medicare Supplement section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1516" s="17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C1516" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; Noridian LCD L38801; LCA A58403; UHC MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1516" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1517" s="17" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="C1517" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403; MMP070.12</t>
+        </is>
+      </c>
+      <c r="D1517" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1518" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1518" s="17" t="inlineStr">
+        <is>
+          <t>Noridian Auth Tool - result for 64772: no prior authorization required. Save a dated screenshot to the patient file.</t>
+        </is>
+      </c>
+      <c r="D1518" s="17" t="inlineStr">
+        <is>
+          <t>Noridian Medicare Portal - Auth Tool look-up - checked: not required (your check). Save a dated screenshot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1519" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1519" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 'Induced Lesions of Nerve Tracts', LCD 'Facet Joint Interventions for Pain Management'; LCA 'Billing and Coding'</t>
+        </is>
+      </c>
+      <c r="D1519" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1520" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C1520" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-3 sec. 160.1; L38801 (rev. eff. 04/16/2026); A58403 R9 (rev. eff. 09/17/2026)</t>
+        </is>
+      </c>
+      <c r="D1520" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1521" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1521" s="17" t="inlineStr">
+        <is>
+          <t>Palmetto GBA Railroad Medicare (no PA program for 64772)</t>
+        </is>
+      </c>
+      <c r="D1521" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - no PA program for 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1522" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C1522" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801 / A58403 (Railroad Medicare applies the LCD/LCA of the MAC where the service is rendered)</t>
+        </is>
+      </c>
+      <c r="D1522" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="17" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="B1523" s="17" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C1523" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1523" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1524" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1524" s="17" t="inlineStr">
+        <is>
+          <t>Availity / Cohere - both returned NOT required (your check). ACD: 800-523-0023, fax 800-266-3022</t>
+        </is>
+      </c>
+      <c r="D1524" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check). ACD: 800-523-0023 / fax 800-266-3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1525" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1525" s="17" t="inlineStr">
+        <is>
+          <t>Neuroablative Techniques for Chronic Pain (MA); Injections for Pain Conditions (MA) for the diagnostic blocks; NCD 160.1 and Noridian L38801 / A58403 (referenced by both)</t>
+        </is>
+      </c>
+      <c r="D1525" s="17" t="inlineStr">
+        <is>
+          <t>Neuroablative Techniques for Chronic Pain; Injections for Pain Conditions; NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1526" s="17" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C1526" s="17" t="inlineStr">
+        <is>
+          <t>HUM-1168-008; HUM-1137-010; L38801; A58403</t>
+        </is>
+      </c>
+      <c r="D1526" s="17" t="inlineStr">
+        <is>
+          <t>HUM-1168-008; HUM-1137-010; NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1527" s="17" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C1527" s="17" t="inlineStr">
+        <is>
+          <t>No need - Humana pays secondary</t>
+        </is>
+      </c>
+      <c r="D1527" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - Medigap has no PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1528" s="17" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="C1528" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1528" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1529" s="17" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="C1529" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1529" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1530" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1530" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1530" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - Medigap has no PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1531" s="17" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C1531" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1531" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1532" s="17" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="C1532" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1532" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1533" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1533" s="17" t="inlineStr">
+        <is>
+          <t>Ibid</t>
+        </is>
+      </c>
+      <c r="D1533" s="17" t="inlineStr">
+        <is>
+          <t>Not applicable - Medigap has no PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1534" s="17" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C1534" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; Noridian LCD Facet Joint Interventions (L38801) and Billing &amp; Coding article (A58403)</t>
+        </is>
+      </c>
+      <c r="D1534" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1 Induced Lesions of Nerve Tracts; LCD Facet Joint Interventions for Pain Management; Billing and Coding: Facet Joint Interventions for Pain Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1535" s="17" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="C1535" s="17" t="inlineStr">
+        <is>
+          <t>Pub. 100-03 sec. 160.1; L38801; A58403 R9</t>
+        </is>
+      </c>
+      <c r="D1535" s="17" t="inlineStr">
+        <is>
+          <t>NCD 160.1; L38801; A58403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1536" s="17" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C1536" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM Policy 820 - Fee-for-Service Prior Authorization Requirements (and FFS PA Guidelines by code)</t>
+        </is>
+      </c>
+      <c r="D1536" s="17" t="inlineStr">
+        <is>
+          <t>820 - Fee-For-Service Authorization Requirements (AMPM Chapter 800)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1537" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C1537" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS AMPM 320-B (experimental services); AMPM Exhibit 300-1 (covered services with limitations); FFS Physician Fee Schedule</t>
+        </is>
+      </c>
+      <c r="D1537" s="17" t="inlineStr">
+        <is>
+          <t>320-B - Member Participation in Experimental Services and Clinical Trials; Exhibit 300-1 - AHCCCS Covered Services with Special Circumstances</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1538" s="17" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="C1538" s="17" t="inlineStr">
+        <is>
+          <t>NO - not on any list on file</t>
+        </is>
+      </c>
+      <c r="D1538" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1539" s="17" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="C1539" s="17" t="inlineStr">
+        <is>
+          <t>No Optum SCAN list on file; 64772 is absent from SCAN's and both Optum lists. ASC expected (CCP0207).</t>
+        </is>
+      </c>
+      <c r="D1539" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool: not required (your check). SCAN denies experimental/investigational services (BCG0111).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1540" s="17" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="C1540" s="17" t="inlineStr">
+        <is>
+          <t>Confirm with Optum</t>
+        </is>
+      </c>
+      <c r="D1540" s="17" t="inlineStr">
+        <is>
+          <t>Keep Availity result</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1541" s="17" t="inlineStr">
+        <is>
+          <t>A41</t>
+        </is>
+      </c>
+      <c r="C1541" s="17" t="inlineStr">
+        <is>
+          <t>- SCAN (Optum-delegated): call Optum 877-370-2845 once to confirm no auth; record the reference #.</t>
+        </is>
+      </c>
+      <c r="D1541" s="17" t="inlineStr">
+        <is>
+          <t>cleared</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Code Research/CPT_64772_Routing_2026.xlsx
+++ b/Code Research/CPT_64772_Routing_2026.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>CALL (TPA / BCBS SC / home plan)</t>
+          <t>CHECK TPA / BCBS SC / home plan</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>Call the TPA before scheduling</t>
+          <t>Check the TPA's auth tool before scheduling</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>ACD 800-523-0023 / fax 800-266-3022</t>
+          <t>Request an ACD</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>CALL BANNER</t>
+          <t>CHECK BANNER</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Ask Banner</t>
+          <t>Banner's auth tool</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>AHCCCS Online / fax 602-256-6591</t>
+          <t>AHCCCS Online</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: call and record.</t>
+          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: check each one's auth tool and record the result.</t>
         </is>
       </c>
     </row>
@@ -1587,17 +1587,17 @@
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>BCBS South Carolina (Blue Plan partner) - 800-868-1032</t>
+          <t>BCBS South Carolina (Blue Plan partner)</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>CALL BCBS SC</t>
+          <t>CHECK BCBS SC</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>No online tool on file - call BCBS South Carolina 800-868-1032</t>
+          <t>BCBS South Carolina's auth tool (not on file)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <is>
           <t>PA: decided by BCBS South Carolina (AZ Blue code-list Introduction). No BCBS SC list on file.
 Note: IVR also appears in the Standard list prefix header.
-Action: call BCBS SC 800-868-1032 before scheduling; record name, date and reference #.</t>
+Action: check BCBS SC's auth tool before scheduling; record the result.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>American Health Group (AHG) - PA and medical policy, 800-847-7605</t>
+          <t>American Health Group (AHG) - PA and medical policy</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>CALL AHG</t>
+          <t>CHECK AHG</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>No online tool on file - call American Health Group 800-847-7605</t>
+          <t>American Health Group's auth tool (not on file)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1749,8 +1749,8 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue TPA document, 07/2026). No AHG list on file.
-Action: call AHG 800-847-7605 before scheduling; record reference #. Claims still go to AZ Blue (EDI 53589).</t>
+          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue and TPA Jointly Administered Plans, as of 07/2026). No AHG list on file.
+Action: check AHG's auth tool before scheduling; record the result. Claims still go to AZ Blue (EDI 53589).</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>CALL AMERIBEN</t>
+          <t>CHECK AMERIBEN</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>AmeriBen PA line by group: JCG 855-240-3698; JKS 855-961-5401; JPZ 855-778-9053; K8Y/K8Z 800-388-3193; MKQ 866-947-9522; PTP 833-359-2505</t>
+          <t>AmeriBen's auth tool for the group (not on file)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1850,8 +1850,8 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue TPA document, 07/2026). No AmeriBen list on file.
-Action: call the AmeriBen line for the prefix (column J) before scheduling; record reference #. Claims go to AZ Blue (EDI 53589).</t>
+          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue and TPA Jointly Administered Plans, as of 07/2026). No AmeriBen list on file.
+Action: check AmeriBen's auth tool before scheduling; record the result. Claims go to AZ Blue (EDI 53589).</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>CALL TPA</t>
+          <t>CHECK TPA</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Call the number on the ID card</t>
+          <t>The TPA's auth tool (TPA named on the ID card)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t>PA: decided by the TPA on the ID card (AZ Blue code-list Introduction). No list on file.
-Action: call the number on the ID card before scheduling; record reference #.</t>
+Action: check the TPA's auth tool before scheduling; record the result.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>CALL HOME PLAN</t>
+          <t>CHECK HOME PLAN</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>CALL PLAN ON CARD</t>
+          <t>CHECK PLAN ON CARD</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Care-management delegation does not carry prior-auth authority. Check with the plan on the card.</t>
+          <t>Use the auth tool of the plan on the ID card</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>CALL IPA</t>
+          <t>CHECK IPA</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Each IPA runs its own UM with its own criteria - ask each one separately</t>
+          <t>The IPA's own auth tool (not on file)</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -5881,7 +5881,7 @@
       <c r="T23" s="3" t="inlineStr">
         <is>
           <t>PA: the delegated IPA's own rules apply (UHC MA PA list: providers contracted with a delegated IPA must follow its protocols). No IPA list on file.
-Action: call the IPA before scheduling; record reference #.</t>
+Action: check the IPA's auth tool before scheduling; record the result.</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>CALL BANNER</t>
+          <t>CHECK BANNER</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Per the Banner AZ QRG - NOT optumproportal.com</t>
+          <t>Banner's auth tool (not on file) - not optumproportal.com</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -5994,7 +5994,7 @@
       <c r="T24" s="3" t="inlineStr">
         <is>
           <t>PA: these group numbers are delegated to Banner (UHC MA PA list, eff. 9/1/2026). Banner's list is not on file.
-Action: call Banner (number on the ID card) before scheduling; do not use optumproportal.com.</t>
+Action: check Banner's auth tool before scheduling; do not use optumproportal.com.</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Ask the Optum provider rep which plan carries group 96001</t>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Erickson MSR / prior authorization number on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+          <t>Erickson prior authorization contact on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -6844,7 +6844,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
-Action: if the MBT is endoscopic, call the Erickson PA number on the ID card - Erickson requires PA for experimental/investigational services.</t>
+Action: if the MBT is endoscopic, request PA through the Erickson contact on the ID card - Erickson requires PA for experimental/investigational services.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 1-800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -6942,7 +6942,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
 Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS benefits.
-Action: PA line 800-445-1638 if needed. QMB members owe $0 - do not bill the member.</t>
+Action: QMB members owe $0 - do not bill the member.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -7440,7 +7440,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
 Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
-Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>CALL TPA</t>
+          <t>CHECK TPA</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Per that supplement. UMR: umr.com</t>
+          <t>The TPA's auth tool per the ID card (UMR: umr.com)</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>No list on file - call (see T)</t>
+          <t>No list on file - see T</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -7537,7 +7537,7 @@
       <c r="T14" s="3" t="inlineStr">
         <is>
           <t>PA: set by each group's plan document and TPA supplement - no list on file.
-Action: check the member's ID card / portal (UMR: umr.com) and call before scheduling; record reference #.</t>
+Action: check the TPA's auth tool (UMR: umr.com) before scheduling; record the result.</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
 Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
-Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
 Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
-Action: if the MBT is endoscopic, expect denial as experimental. PA line 877-842-3210.</t>
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check). ACD: 800-523-0023 / fax 800-266-3022</t>
+          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -8775,7 +8775,7 @@
         <is>
           <t>PA: NOT required - 64772 is not on the Humana MA/D-SNP list (eff. 7/1/2026, rev. 9/1/2026); Availity and Cohere returned not required (your check). 64999 and facet codes 64490-64495, 64633-64636 DO need PA through Cohere.
 Coverage: HUM-1168-008 - endoscopic RF ablation/rhizotomy for any indication, including the facet nerve, is NOT reasonable and necessary. Conventional facet RFA follows L38801/A58403.
-Action: request an Advance Coverage Determination before scheduling (800-523-0023 / fax 800-266-3022 / PO Box 14601, Lexington KY 40512-4601). Without it, a post-payment denial is likely and the member cannot be billed.</t>
+Action: request an Advance Coverage Determination before scheduling. Without it, a post-payment denial is likely and the member cannot be billed.</t>
         </is>
       </c>
       <c r="U2" s="10" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>AHCCCS Online provider portal; Medical PA fax 602-256-6591; phone 602-417-4400 / 800-433-0425</t>
+          <t>AHCCCS Online provider portal</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -10057,7 +10057,7 @@
 Applies ONLY to AHCCCS fee-for-service members (AIHP, Tribal ALTCS, TRBHA, DDD THP) - NOT to AHCCCS health plans (UHC Community Plan, Mercy Care, Health Choice, etc.).
 No PA needed (sec. III.1): emergency, AHCCCS not primary, IHS/638 provider or facility, retro eligibility. L.3.b refers to "section FF for exclusions", but the policy on file ends at section DD.
 Coverage: experimental services not covered (AMPM 320-B); moderate sedation by the performing physician not covered (Exh. 300-1).
-Action: submit surgeon PA and ASC PA to AHCCCS DFSM (AHCCCS Online; fax 602-256-6591; phone 602-417-4400) before scheduling.</t>
+Action: submit surgeon PA and ASC PA to AHCCCS DFSM on AHCCCS Online before scheduling.</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1541"/>
+  <dimension ref="A1:D1630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45039,6 +45039,1969 @@
         </is>
       </c>
     </row>
+    <row r="1543">
+      <c r="A1543" s="15" t="inlineStr">
+        <is>
+          <t>Round 8 - phone and fax numbers removed (auths are checked in online tools)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1544" s="17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C1544" s="17" t="inlineStr">
+        <is>
+          <t>BCBS South Carolina (Blue Plan partner) - 800-868-1032</t>
+        </is>
+      </c>
+      <c r="D1544" s="17" t="inlineStr">
+        <is>
+          <t>BCBS South Carolina (Blue Plan partner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1545" s="17" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C1545" s="17" t="inlineStr">
+        <is>
+          <t>CALL BCBS SC</t>
+        </is>
+      </c>
+      <c r="D1545" s="17" t="inlineStr">
+        <is>
+          <t>CHECK BCBS SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1546" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1546" s="17" t="inlineStr">
+        <is>
+          <t>No online tool on file - call BCBS South Carolina 800-868-1032</t>
+        </is>
+      </c>
+      <c r="D1546" s="17" t="inlineStr">
+        <is>
+          <t>BCBS South Carolina's auth tool (not on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1547" s="17" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C1547" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by BCBS South Carolina (AZ Blue code-list Introduction). No BCBS SC list on file.
+Note: IVR also appears in the Standard list prefix header.
+Action: call BCBS SC 800-868-1032 before scheduling; record name, date and reference #.</t>
+        </is>
+      </c>
+      <c r="D1547" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by BCBS South Carolina (AZ Blue code-list Introduction). No BCBS SC list on file.
+Note: IVR also appears in the Standard list prefix header.
+Action: check BCBS SC's auth tool before scheduling; record the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1548" s="17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C1548" s="17" t="inlineStr">
+        <is>
+          <t>American Health Group (AHG) - PA and medical policy, 800-847-7605</t>
+        </is>
+      </c>
+      <c r="D1548" s="17" t="inlineStr">
+        <is>
+          <t>American Health Group (AHG) - PA and medical policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1549" s="17" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C1549" s="17" t="inlineStr">
+        <is>
+          <t>CALL AHG</t>
+        </is>
+      </c>
+      <c r="D1549" s="17" t="inlineStr">
+        <is>
+          <t>CHECK AHG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1550" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1550" s="17" t="inlineStr">
+        <is>
+          <t>No online tool on file - call American Health Group 800-847-7605</t>
+        </is>
+      </c>
+      <c r="D1550" s="17" t="inlineStr">
+        <is>
+          <t>American Health Group's auth tool (not on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1551" s="17" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C1551" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue TPA document, 07/2026). No AHG list on file.
+Action: call AHG 800-847-7605 before scheduling; record reference #. Claims still go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+      <c r="D1551" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by American Health Group; the group may customize PA (AZ Blue and TPA Jointly Administered Plans, as of 07/2026). No AHG list on file.
+Action: check AHG's auth tool before scheduling; record the result. Claims still go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1552" s="17" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="C1552" s="17" t="inlineStr">
+        <is>
+          <t>CALL AMERIBEN</t>
+        </is>
+      </c>
+      <c r="D1552" s="17" t="inlineStr">
+        <is>
+          <t>CHECK AMERIBEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1553" s="17" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C1553" s="17" t="inlineStr">
+        <is>
+          <t>AmeriBen PA line by group: JCG 855-240-3698; JKS 855-961-5401; JPZ 855-778-9053; K8Y/K8Z 800-388-3193; MKQ 866-947-9522; PTP 833-359-2505</t>
+        </is>
+      </c>
+      <c r="D1553" s="17" t="inlineStr">
+        <is>
+          <t>AmeriBen's auth tool for the group (not on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1554" s="17" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C1554" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue TPA document, 07/2026). No AmeriBen list on file.
+Action: call the AmeriBen line for the prefix (column J) before scheduling; record reference #. Claims go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+      <c r="D1554" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by AmeriBen; the group may customize PA (AZ Blue and TPA Jointly Administered Plans, as of 07/2026). No AmeriBen list on file.
+Action: check AmeriBen's auth tool before scheduling; record the result. Claims go to AZ Blue (EDI 53589).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1555" s="17" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="C1555" s="17" t="inlineStr">
+        <is>
+          <t>CALL TPA</t>
+        </is>
+      </c>
+      <c r="D1555" s="17" t="inlineStr">
+        <is>
+          <t>CHECK TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1556" s="17" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C1556" s="17" t="inlineStr">
+        <is>
+          <t>Call the number on the ID card</t>
+        </is>
+      </c>
+      <c r="D1556" s="17" t="inlineStr">
+        <is>
+          <t>The TPA's auth tool (TPA named on the ID card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1557" s="17" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C1557" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by the TPA on the ID card (AZ Blue code-list Introduction). No list on file.
+Action: call the number on the ID card before scheduling; record reference #.</t>
+        </is>
+      </c>
+      <c r="D1557" s="17" t="inlineStr">
+        <is>
+          <t>PA: decided by the TPA on the ID card (AZ Blue code-list Introduction). No list on file.
+Action: check the TPA's auth tool before scheduling; record the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1558" s="17" t="inlineStr">
+        <is>
+          <t>I17</t>
+        </is>
+      </c>
+      <c r="C1558" s="17" t="inlineStr">
+        <is>
+          <t>CALL HOME PLAN</t>
+        </is>
+      </c>
+      <c r="D1558" s="17" t="inlineStr">
+        <is>
+          <t>CHECK HOME PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1559" s="17" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="C1559" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1559" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1560" s="17" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="C1560" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1560" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1561" s="17" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="C1561" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1561" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1562" s="17" t="inlineStr">
+        <is>
+          <t>O4</t>
+        </is>
+      </c>
+      <c r="C1562" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1562" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1563" s="17" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="C1563" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1563" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1564" s="17" t="inlineStr">
+        <is>
+          <t>O5</t>
+        </is>
+      </c>
+      <c r="C1564" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1564" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1565" s="17" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="C1565" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1565" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1566" s="17" t="inlineStr">
+        <is>
+          <t>O6</t>
+        </is>
+      </c>
+      <c r="C1566" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1566" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1567" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1567" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+      <c r="D1567" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1568" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1568" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+      <c r="D1568" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="17" t="inlineStr">
+        <is>
+          <t>BCBS</t>
+        </is>
+      </c>
+      <c r="B1569" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1569" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+      <c r="D1569" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1570" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1570" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1570" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1571" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1571" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1571" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1572" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1572" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1572" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1573" s="17" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C1573" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1573" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1574" s="17" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C1574" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1574" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1575" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C1575" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1575" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1576" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1576" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1576" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1577" s="17" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C1577" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1577" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1578" s="17" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="C1578" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1578" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1579" s="17" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="C1579" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1579" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1580" s="17" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="C1580" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1580" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1581" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C1581" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1581" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1582" s="17" t="inlineStr">
+        <is>
+          <t>J14</t>
+        </is>
+      </c>
+      <c r="C1582" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1582" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1583" s="17" t="inlineStr">
+        <is>
+          <t>J15</t>
+        </is>
+      </c>
+      <c r="C1583" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+      <c r="D1583" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1584" s="17" t="inlineStr">
+        <is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="C1584" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com; phone 877-370-2845 if portal down. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+      <c r="D1584" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com. If not Optum-direct: Availity auth tool (prior auth workflow); AZ Blue PA lookup tool: azblue.com/lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1585" s="17" t="inlineStr">
+        <is>
+          <t>I22</t>
+        </is>
+      </c>
+      <c r="C1585" s="17" t="inlineStr">
+        <is>
+          <t>CALL PLAN ON CARD</t>
+        </is>
+      </c>
+      <c r="D1585" s="17" t="inlineStr">
+        <is>
+          <t>CHECK PLAN ON CARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1586" s="17" t="inlineStr">
+        <is>
+          <t>I23</t>
+        </is>
+      </c>
+      <c r="C1586" s="17" t="inlineStr">
+        <is>
+          <t>CALL IPA</t>
+        </is>
+      </c>
+      <c r="D1586" s="17" t="inlineStr">
+        <is>
+          <t>CHECK IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1587" s="17" t="inlineStr">
+        <is>
+          <t>I24</t>
+        </is>
+      </c>
+      <c r="C1587" s="17" t="inlineStr">
+        <is>
+          <t>CALL BANNER</t>
+        </is>
+      </c>
+      <c r="D1587" s="17" t="inlineStr">
+        <is>
+          <t>CHECK BANNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1588" s="17" t="inlineStr">
+        <is>
+          <t>J22</t>
+        </is>
+      </c>
+      <c r="C1588" s="17" t="inlineStr">
+        <is>
+          <t>Care-management delegation does not carry prior-auth authority. Check with the plan on the card.</t>
+        </is>
+      </c>
+      <c r="D1588" s="17" t="inlineStr">
+        <is>
+          <t>Use the auth tool of the plan on the ID card</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1589" s="17" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="C1589" s="17" t="inlineStr">
+        <is>
+          <t>Each IPA runs its own UM with its own criteria - ask each one separately</t>
+        </is>
+      </c>
+      <c r="D1589" s="17" t="inlineStr">
+        <is>
+          <t>The IPA's own auth tool (not on file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1590" s="17" t="inlineStr">
+        <is>
+          <t>J24</t>
+        </is>
+      </c>
+      <c r="C1590" s="17" t="inlineStr">
+        <is>
+          <t>Per the Banner AZ QRG - NOT optumproportal.com</t>
+        </is>
+      </c>
+      <c r="D1590" s="17" t="inlineStr">
+        <is>
+          <t>Banner's auth tool (not on file) - not optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1591" s="17" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="C1591" s="17" t="inlineStr">
+        <is>
+          <t>PA: the delegated IPA's own rules apply (UHC MA PA list: providers contracted with a delegated IPA must follow its protocols). No IPA list on file.
+Action: call the IPA before scheduling; record reference #.</t>
+        </is>
+      </c>
+      <c r="D1591" s="17" t="inlineStr">
+        <is>
+          <t>PA: the delegated IPA's own rules apply (UHC MA PA list: providers contracted with a delegated IPA must follow its protocols). No IPA list on file.
+Action: check the IPA's auth tool before scheduling; record the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1592" s="17" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="C1592" s="17" t="inlineStr">
+        <is>
+          <t>PA: these group numbers are delegated to Banner (UHC MA PA list, eff. 9/1/2026). Banner's list is not on file.
+Action: call Banner (number on the ID card) before scheduling; do not use optumproportal.com.</t>
+        </is>
+      </c>
+      <c r="D1592" s="17" t="inlineStr">
+        <is>
+          <t>PA: these group numbers are delegated to Banner (UHC MA PA list, eff. 9/1/2026). Banner's list is not on file.
+Action: check Banner's auth tool before scheduling; do not use optumproportal.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1593" s="17" t="inlineStr">
+        <is>
+          <t>J25</t>
+        </is>
+      </c>
+      <c r="C1593" s="17" t="inlineStr">
+        <is>
+          <t>Ask the Optum provider rep which plan carries group 96001</t>
+        </is>
+      </c>
+      <c r="D1593" s="17" t="inlineStr">
+        <is>
+          <t>Curo (Optum auth tool) via Optum Pro portal: optumproportal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1594" s="17" t="inlineStr">
+        <is>
+          <t>N23</t>
+        </is>
+      </c>
+      <c r="C1594" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1594" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1595" s="17" t="inlineStr">
+        <is>
+          <t>O23</t>
+        </is>
+      </c>
+      <c r="C1595" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1595" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1596" s="17" t="inlineStr">
+        <is>
+          <t>N24</t>
+        </is>
+      </c>
+      <c r="C1596" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1596" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="B1597" s="17" t="inlineStr">
+        <is>
+          <t>O24</t>
+        </is>
+      </c>
+      <c r="C1597" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1597" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1598" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1598" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1598" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1599" s="17" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C1599" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1599" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1600" s="17" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="C1600" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1600" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1601" s="17" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="C1601" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1601" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1602" s="17" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="C1602" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1602" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1603" s="17" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="C1603" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 1-800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1603" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1604" s="17" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="C1604" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1604" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1605" s="17" t="inlineStr">
+        <is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="C1605" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1605" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1606" s="17" t="inlineStr">
+        <is>
+          <t>J18</t>
+        </is>
+      </c>
+      <c r="C1606" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1606" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1607" s="17" t="inlineStr">
+        <is>
+          <t>J19</t>
+        </is>
+      </c>
+      <c r="C1607" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 800-445-1638</t>
+        </is>
+      </c>
+      <c r="D1607" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1608" s="17" t="inlineStr">
+        <is>
+          <t>J20</t>
+        </is>
+      </c>
+      <c r="C1608" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan); phone 877-842-3210</t>
+        </is>
+      </c>
+      <c r="D1608" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1609" s="17" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="C1609" s="17" t="inlineStr">
+        <is>
+          <t>Erickson MSR / prior authorization number on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+      <c r="D1609" s="17" t="inlineStr">
+        <is>
+          <t>Erickson prior authorization contact on the back of the ID card; UnitedHealthcare Provider Portal &gt; Prior Authorization and Notification tool (UHCprovider.com/paan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1610" s="17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C1610" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, call the Erickson PA number on the ID card - Erickson requires PA</t>
+        </is>
+      </c>
+      <c r="D1610" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven.
+Action: if the MBT is endoscopic, request PA through the Erickson contact on the ID card - Erickson</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1611" s="17" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C1611" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS b</t>
+        </is>
+      </c>
+      <c r="D1611" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the UHC MA PA list (eff. 9/1/2026); no facet codes are on it either. The list names UHC Dual Complete as included.
+Coverage: NCD 160.1 allows nerve cutting case by case. L38801 criteria for facet denervation: 2 diagnostic MBBs, each &gt;=80% relief, &gt;=2 weeks apart; &gt;=3 months pain; failed conservative care; max 2 sessions per region per 12 months. L38801 states there is insufficient evidence for ENDOSCOPIC dorsal ramus rhizotomy. UHC's commercial policy 2026T0107II lists endoscopic RFA/rhizotomy as unproven. Medicaid wrap: experimental services are not AHCCCS b</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1612" s="17" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C1612" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+        </is>
+      </c>
+      <c r="D1612" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1613" s="17" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="C1613" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 800-445-1638.</t>
+        </is>
+      </c>
+      <c r="D1613" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1614" s="17" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C1614" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental. PA line 877-842-3210.</t>
+        </is>
+      </c>
+      <c r="D1614" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the list (eff. 9/1/2026). 64490 and 64493 need PA. Anything experimental/investigational needs PA and is not a covered AHCCCS benefit.
+Coverage: CS001.T - endoscopic RFA/rhizotomy is unproven. Moderate sedation by the performing physician is not covered (AMPM Exh. 300-1). Provider must be AHCCCS-registered.
+Action: if the MBT is endoscopic, expect denial as experimental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1615" s="17" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="C1615" s="17" t="inlineStr">
+        <is>
+          <t>CALL TPA</t>
+        </is>
+      </c>
+      <c r="D1615" s="17" t="inlineStr">
+        <is>
+          <t>CHECK TPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1616" s="17" t="inlineStr">
+        <is>
+          <t>J14</t>
+        </is>
+      </c>
+      <c r="C1616" s="17" t="inlineStr">
+        <is>
+          <t>Per that supplement. UMR: umr.com</t>
+        </is>
+      </c>
+      <c r="D1616" s="17" t="inlineStr">
+        <is>
+          <t>The TPA's auth tool per the ID card (UMR: umr.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1617" s="17" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C1617" s="17" t="inlineStr">
+        <is>
+          <t>PA: set by each group's plan document and TPA supplement - no list on file.
+Action: check the member's ID card / portal (UMR: umr.com) and call before scheduling; record reference #.</t>
+        </is>
+      </c>
+      <c r="D1617" s="17" t="inlineStr">
+        <is>
+          <t>PA: set by each group's plan document and TPA supplement - no list on file.
+Action: check the TPA's auth tool (UMR: umr.com) before scheduling; record the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1618" s="17" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="C1618" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1618" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="17" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="B1619" s="17" t="inlineStr">
+        <is>
+          <t>O14</t>
+        </is>
+      </c>
+      <c r="C1619" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - call (see T)</t>
+        </is>
+      </c>
+      <c r="D1619" s="17" t="inlineStr">
+        <is>
+          <t>No list on file - see T</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1620" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1620" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check). ACD: 800-523-0023 / fax 800-266-3022</t>
+        </is>
+      </c>
+      <c r="D1620" s="17" t="inlineStr">
+        <is>
+          <t>Availity auth tool and Cohere Health auth tool - both checked: not required (your check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="B1621" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1621" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Humana MA/D-SNP list (eff. 7/1/2026, rev. 9/1/2026); Availity and Cohere returned not required (your check). 64999 and facet codes 64490-64495, 64633-64636 DO need PA through Cohere.
+Coverage: HUM-1168-008 - endoscopic RF ablation/rhizotomy for any indication, including the facet nerve, is NOT reasonable and necessary. Conventional facet RFA follows L38801/A58403.
+Action: request an Advance Coverage Determination before scheduling (800-523-0023 / fax 800-266-3022 / PO Box 14601, Lexington KY 40512-4601). Without it, a post-payment denial is likely and the</t>
+        </is>
+      </c>
+      <c r="D1621" s="17" t="inlineStr">
+        <is>
+          <t>PA: NOT required - 64772 is not on the Humana MA/D-SNP list (eff. 7/1/2026, rev. 9/1/2026); Availity and Cohere returned not required (your check). 64999 and facet codes 64490-64495, 64633-64636 DO need PA through Cohere.
+Coverage: HUM-1168-008 - endoscopic RF ablation/rhizotomy for any indication, including the facet nerve, is NOT reasonable and necessary. Conventional facet RFA follows L38801/A58403.
+Action: request an Advance Coverage Determination before scheduling. Without it, a post-payment denial is likely and the member cannot be billed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1622" s="17" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C1622" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS Online provider portal; Medical PA fax 602-256-6591; phone 602-417-4400 / 800-433-0425</t>
+        </is>
+      </c>
+      <c r="D1622" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS Online provider portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS FFS</t>
+        </is>
+      </c>
+      <c r="B1623" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C1623" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED. AMPM 820 L.3.b (p.14): "An Authorization is required ... for all FFS and DDD THP members: ... b. Elective and urgent outpatient surgical procedures". Sec. U (p.22): FFS surgeons "shall obtain a separate and distinct AHCCCS PA number from that of the facility PA number prior to providing elective/non-emergency surgeries". Sec. T: the ASC "shall obtain PA from AHCCCS DFSM for all outpatient surgeries".
+Applies ONLY to AHCCCS fee-for-service members (AIHP, Tribal ALTCS, TRBHA, DDD THP) - NOT to AHCCCS health plans (UHC Community Plan, Mercy Care, Health Choice, etc.).
+No PA needed (</t>
+        </is>
+      </c>
+      <c r="D1623" s="17" t="inlineStr">
+        <is>
+          <t>PA: REQUIRED. AMPM 820 L.3.b (p.14): "An Authorization is required ... for all FFS and DDD THP members: ... b. Elective and urgent outpatient surgical procedures". Sec. U (p.22): FFS surgeons "shall obtain a separate and distinct AHCCCS PA number from that of the facility PA number prior to providing elective/non-emergency surgeries". Sec. T: the ASC "shall obtain PA from AHCCCS DFSM for all outpatient surgeries".
+Applies ONLY to AHCCCS fee-for-service members (AIHP, Tribal ALTCS, TRBHA, DDD THP) - NOT to AHCCCS health plans (UHC Community Plan, Mercy Care, Health Choice, etc.).
+No PA needed (</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1624" s="17" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C1624" s="17" t="inlineStr">
+        <is>
+          <t>CALL (TPA / BCBS SC / home plan)</t>
+        </is>
+      </c>
+      <c r="D1624" s="17" t="inlineStr">
+        <is>
+          <t>CHECK TPA / BCBS SC / home plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1625" s="17" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="C1625" s="17" t="inlineStr">
+        <is>
+          <t>Call the TPA before scheduling</t>
+        </is>
+      </c>
+      <c r="D1625" s="17" t="inlineStr">
+        <is>
+          <t>Check the TPA's auth tool before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1626" s="17" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="C1626" s="17" t="inlineStr">
+        <is>
+          <t>ACD 800-523-0023 / fax 800-266-3022</t>
+        </is>
+      </c>
+      <c r="D1626" s="17" t="inlineStr">
+        <is>
+          <t>Request an ACD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1627" s="17" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="C1627" s="17" t="inlineStr">
+        <is>
+          <t>CALL BANNER</t>
+        </is>
+      </c>
+      <c r="D1627" s="17" t="inlineStr">
+        <is>
+          <t>CHECK BANNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1628" s="17" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="C1628" s="17" t="inlineStr">
+        <is>
+          <t>Ask Banner</t>
+        </is>
+      </c>
+      <c r="D1628" s="17" t="inlineStr">
+        <is>
+          <t>Banner's auth tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1629" s="17" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="C1629" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS Online / fax 602-256-6591</t>
+        </is>
+      </c>
+      <c r="D1629" s="17" t="inlineStr">
+        <is>
+          <t>AHCCCS Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="17" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B1630" s="17" t="inlineStr">
+        <is>
+          <t>A43</t>
+        </is>
+      </c>
+      <c r="C1630" s="17" t="inlineStr">
+        <is>
+          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: call and record.</t>
+        </is>
+      </c>
+      <c r="D1630" s="17" t="inlineStr">
+        <is>
+          <t>- TPA groups (AHG, AmeriBen), BCBS SC, CHS, BlueCard home plans, Banner, delegated IPAs: check each one's auth tool and record the result.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
